--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -482,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1753,8 +1762,48 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>APAC FP&amp;A Manager</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4462770899/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Commercial Analytics &amp; Operations Associate</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4462778751/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D63"/>
+  <autoFilter ref="A1:D65"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -1818,6 +1867,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -491,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -523,12 +532,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n">
+      <c r="B2" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -536,19 +545,19 @@
           <t>Sr Project Lead - APAC</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461543326/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
+      <c r="B3" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -556,19 +565,19 @@
           <t>SW Development Engineer 2</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460357219/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="13" t="n">
         <v>46267</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -576,19 +585,19 @@
           <t>Intelligence Analyst</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453085191/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -596,19 +605,19 @@
           <t>Senior Manager Corporate Compliance - EMEA (m/w/d)</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461752409/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -616,19 +625,19 @@
           <t>Customer Service Representative - French Speaker</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460500502/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="13" t="n">
         <v>46265</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -636,19 +645,19 @@
           <t>Staff Program Manager</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451501447/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -656,19 +665,19 @@
           <t>Lead Legal Counsel - Employment</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4430864197/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -676,19 +685,19 @@
           <t>Sr Manager, Software Systems &amp; Solutions</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4218028502/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -696,19 +705,19 @@
           <t>Manager SW Test Development Engineering</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4281993770/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="13" t="n">
         <v>46263</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -716,19 +725,19 @@
           <t>Security and Privacy Compliance Analyst - Cybersecurity</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4257269392/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -736,19 +745,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461768038/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="n">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -756,19 +765,19 @@
           <t>Mechanical Engineer 2</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462032756/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n">
+      <c r="B14" s="13" t="n">
         <v>46263</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -776,19 +785,19 @@
           <t>Supervisor Customer Advocacy</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442102156/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="n">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
         <v>46267</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -796,19 +805,19 @@
           <t>Senior Staff Process Development Engineer</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443563067/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="n">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -816,19 +825,19 @@
           <t>Staff Process Engineer</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461543337/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -836,19 +845,19 @@
           <t>Sr QA Engineer</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460398658/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
         <v>46268</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -856,19 +865,19 @@
           <t>Senior Director, Lean</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462725850/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
+      <c r="B19" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -876,19 +885,19 @@
           <t>Benefits Analyst</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461581171/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n">
+      <c r="B20" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -896,19 +905,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458914791/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
+      <c r="B21" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -916,19 +925,19 @@
           <t>Financial Analyst</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441984900/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
+      <c r="B22" s="13" t="n">
         <v>46267</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -936,19 +945,19 @@
           <t>Intelligence Analyst</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082218/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
+      <c r="B23" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -956,19 +965,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765127/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B24" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -976,19 +985,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461754390/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
+      <c r="B25" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -996,19 +1005,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458902988/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="n">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n">
         <v>46263</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1016,19 +1025,19 @@
           <t>Benefits Manager (Americas)</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450760638/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n">
+      <c r="B27" s="13" t="n">
         <v>46265</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1036,19 +1045,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451545592/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n">
+      <c r="B28" s="13" t="n">
         <v>46267</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1056,19 +1065,19 @@
           <t>Sr Process Engineer</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435122348/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n">
+      <c r="B29" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1076,19 +1085,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461772012/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n">
+      <c r="B30" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1096,19 +1105,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765131/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n">
+      <c r="B31" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1116,19 +1125,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461762151/</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="n">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="n">
         <v>46265</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1136,19 +1145,19 @@
           <t>New Business Development Manager (Senior Analyst, Strategic Finance )</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434090087/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="n">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1156,19 +1165,19 @@
           <t>Sr Manager - Sensor Automation</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461540445/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="n">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="n">
         <v>46265</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1176,19 +1185,19 @@
           <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D34" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461264820/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n">
+      <c r="B35" s="13" t="n">
         <v>46267</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1196,19 +1205,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D35" s="11" t="inlineStr">
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453096131/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="n">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1216,19 +1225,19 @@
           <t>Sr SW Design Quality Engineer</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D36" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450008915/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B37" s="10" t="n">
+      <c r="B37" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1236,19 +1245,19 @@
           <t>Engineering Technician 4</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="D37" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461760270/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="n">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="n">
         <v>46265</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1256,19 +1265,19 @@
           <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D38" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461275610/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="n">
         <v>46265</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1276,19 +1285,19 @@
           <t>Associate Customer Insights Manager</t>
         </is>
       </c>
-      <c r="D39" s="11" t="inlineStr">
+      <c r="D39" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434083415/</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1296,19 +1305,19 @@
           <t>Staff SW QA Engineer</t>
         </is>
       </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="D40" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450025503/</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="n">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="n">
         <v>46267</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1316,19 +1325,19 @@
           <t>Lead Corporate Development Manager</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
+      <c r="D41" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462460922/</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B42" s="10" t="n">
+      <c r="B42" s="13" t="n">
         <v>46264</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1336,19 +1345,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="D42" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442446290/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="n">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="n">
         <v>46265</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1356,19 +1365,19 @@
           <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="D43" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461277558/</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B44" s="10" t="n">
+      <c r="B44" s="13" t="n">
         <v>46267</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1376,19 +1385,19 @@
           <t>Accountant - Healthcare - Edinburgh</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D44" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453144035/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B45" s="10" t="n">
+      <c r="B45" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1396,19 +1405,19 @@
           <t>Staff Systems Engineer</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461770016/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="n">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="n">
         <v>46268</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1416,19 +1425,19 @@
           <t>Staff Quality Compliance Specialist</t>
         </is>
       </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="D46" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462730823/</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="B47" s="10" t="n">
+      <c r="B47" s="13" t="n">
         <v>46267</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1436,19 +1445,19 @@
           <t>Territory Sales Manager (m/w/d) - Zentralschweiz : Luzern, Obwalden, Nidwalden, Uri, Chur</t>
         </is>
       </c>
-      <c r="D47" s="11" t="inlineStr">
+      <c r="D47" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453133160/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="n">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="n">
         <v>46262</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1456,19 +1465,19 @@
           <t>Staff Planner</t>
         </is>
       </c>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="D48" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450636243/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="n">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="n">
         <v>46267</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1476,19 +1485,19 @@
           <t>Territory Business Manager - Morristown, New Jersey</t>
         </is>
       </c>
-      <c r="D49" s="11" t="inlineStr">
+      <c r="D49" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4452316210/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="n">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1496,19 +1505,19 @@
           <t>Sr Manager Medical Affairs</t>
         </is>
       </c>
-      <c r="D50" s="11" t="inlineStr">
+      <c r="D50" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461536483/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B51" s="10" t="n">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="n">
         <v>46263</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1516,19 +1525,19 @@
           <t>Capital Planning &amp; Analytics Manager</t>
         </is>
       </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="D51" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450775200/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="n">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="n">
         <v>46263</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -1536,19 +1545,19 @@
           <t>Supervisor, Manufacturing</t>
         </is>
       </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="D52" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460573058/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="n">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1556,19 +1565,19 @@
           <t>Territory Business Manager - Anchorage, AK</t>
         </is>
       </c>
-      <c r="D53" s="11" t="inlineStr">
+      <c r="D53" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462041571/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="n">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="n">
         <v>46268</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1576,19 +1585,19 @@
           <t>QC Inspector 4 - 1B Thur-Sat, every other Wednesday from 5am-5pm</t>
         </is>
       </c>
-      <c r="D54" s="11" t="inlineStr">
+      <c r="D54" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462726839/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="A55" s="12" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B55" s="10" t="n">
+      <c r="B55" s="13" t="n">
         <v>46267</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1596,19 +1605,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D55" s="11" t="inlineStr">
+      <c r="D55" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097086/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+      <c r="A56" s="12" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B56" s="10" t="n">
+      <c r="B56" s="13" t="n">
         <v>46267</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1616,19 +1625,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="D56" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453076276/</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="A57" s="12" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B57" s="10" t="n">
+      <c r="B57" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1636,19 +1645,19 @@
           <t>Territory Business Manager - Ottawa</t>
         </is>
       </c>
-      <c r="D57" s="11" t="inlineStr">
+      <c r="D57" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462038604/</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+      <c r="A58" s="12" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B58" s="10" t="n">
+      <c r="B58" s="13" t="n">
         <v>46267</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1656,19 +1665,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="D58" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453087192/</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="n">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="n">
         <v>46267</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1676,19 +1685,19 @@
           <t>Manufacturing Technician 3-1B Thursday-Saturday every other Wednesday(5AM-5PM)</t>
         </is>
       </c>
-      <c r="D59" s="11" t="inlineStr">
+      <c r="D59" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460900071/</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="n">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1696,19 +1705,19 @@
           <t>Equipment Technician 2-1A Sunday-Tuesday every other Wednesday(5AM-5PM)</t>
         </is>
       </c>
-      <c r="D60" s="11" t="inlineStr">
+      <c r="D60" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461550206/</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="A61" s="12" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B61" s="10" t="n">
+      <c r="B61" s="13" t="n">
         <v>46267</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1716,19 +1725,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D61" s="11" t="inlineStr">
+      <c r="D61" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453078274/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B62" s="10" t="n">
+      <c r="B62" s="13" t="n">
         <v>46266</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1736,19 +1745,19 @@
           <t>Staff Veeva and Master Data Analyst</t>
         </is>
       </c>
-      <c r="D62" s="11" t="inlineStr">
+      <c r="D62" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461758265/</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B63" s="10" t="n">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="n">
         <v>46268</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1756,7 +1765,7 @@
           <t>Platform Security Engineer 2</t>
         </is>
       </c>
-      <c r="D63" s="11" t="inlineStr">
+      <c r="D63" s="14" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462736772/</t>
         </is>
@@ -1802,8 +1811,88 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B66" s="16" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Document Control and Training Specialist 1</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463157831/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B67" s="16" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Sr Supply Chain Analyst</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463169639/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B68" s="16" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>IT Procurement Analyst</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463313428/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="15" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B69" s="16" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>IT Procurement Analyst</t>
+        </is>
+      </c>
+      <c r="D69" s="17" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463314400/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D65"/>
+  <autoFilter ref="A1:D69"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -1869,6 +1958,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -500,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -532,12 +541,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B2" s="13" t="n">
+      <c r="B2" s="16" t="n">
         <v>46266</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -545,19 +554,19 @@
           <t>Sr Project Lead - APAC</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461543326/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n">
+      <c r="B3" s="16" t="n">
         <v>46262</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -565,19 +574,19 @@
           <t>SW Development Engineer 2</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460357219/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n">
+      <c r="B4" s="16" t="n">
         <v>46267</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -585,19 +594,19 @@
           <t>Intelligence Analyst</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453085191/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
+      <c r="B5" s="16" t="n">
         <v>46266</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -605,19 +614,19 @@
           <t>Senior Manager Corporate Compliance - EMEA (m/w/d)</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461752409/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="16" t="n">
         <v>46262</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -625,19 +634,19 @@
           <t>Customer Service Representative - French Speaker</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460500502/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="16" t="n">
         <v>46265</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -645,19 +654,19 @@
           <t>Staff Program Manager</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451501447/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="n">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
         <v>46266</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -665,19 +674,19 @@
           <t>Lead Legal Counsel - Employment</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4430864197/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="16" t="n">
         <v>46262</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -685,19 +694,19 @@
           <t>Sr Manager, Software Systems &amp; Solutions</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4218028502/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="16" t="n">
         <v>46262</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -705,19 +714,19 @@
           <t>Manager SW Test Development Engineering</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4281993770/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="16" t="n">
         <v>46263</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -725,19 +734,19 @@
           <t>Security and Privacy Compliance Analyst - Cybersecurity</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4257269392/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="16" t="n">
         <v>46266</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -745,19 +754,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461768038/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="n">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n">
         <v>46266</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -765,19 +774,19 @@
           <t>Mechanical Engineer 2</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462032756/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="16" t="n">
         <v>46263</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -785,19 +794,19 @@
           <t>Supervisor Customer Advocacy</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442102156/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="n">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="n">
         <v>46267</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -805,19 +814,19 @@
           <t>Senior Staff Process Development Engineer</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443563067/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="n">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="n">
         <v>46266</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -825,19 +834,19 @@
           <t>Staff Process Engineer</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461543337/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="n">
         <v>46262</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -845,19 +854,19 @@
           <t>Sr QA Engineer</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460398658/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="n">
         <v>46268</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -865,19 +874,19 @@
           <t>Senior Director, Lean</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462725850/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n">
+      <c r="B19" s="16" t="n">
         <v>46266</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -885,19 +894,19 @@
           <t>Benefits Analyst</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461581171/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n">
+      <c r="B20" s="16" t="n">
         <v>46262</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -905,19 +914,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458914791/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n">
+      <c r="B21" s="16" t="n">
         <v>46262</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -925,19 +934,19 @@
           <t>Financial Analyst</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441984900/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n">
+      <c r="B22" s="16" t="n">
         <v>46267</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -945,19 +954,19 @@
           <t>Intelligence Analyst</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082218/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n">
+      <c r="B23" s="16" t="n">
         <v>46266</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -965,19 +974,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765127/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n">
+      <c r="B24" s="16" t="n">
         <v>46266</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -985,19 +994,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461754390/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n">
+      <c r="B25" s="16" t="n">
         <v>46262</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1005,19 +1014,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458902988/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="n">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="n">
         <v>46263</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1025,19 +1034,19 @@
           <t>Benefits Manager (Americas)</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450760638/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n">
+      <c r="B27" s="16" t="n">
         <v>46265</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1045,19 +1054,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451545592/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n">
+      <c r="B28" s="16" t="n">
         <v>46267</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1065,19 +1074,19 @@
           <t>Sr Process Engineer</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435122348/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n">
+      <c r="B29" s="16" t="n">
         <v>46266</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1085,19 +1094,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461772012/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n">
+      <c r="B30" s="16" t="n">
         <v>46266</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1105,19 +1114,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765131/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n">
+      <c r="B31" s="16" t="n">
         <v>46266</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1125,19 +1134,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461762151/</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="n">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="n">
         <v>46265</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1145,19 +1154,19 @@
           <t>New Business Development Manager (Senior Analyst, Strategic Finance )</t>
         </is>
       </c>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434090087/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="n">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="n">
         <v>46266</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1165,19 +1174,19 @@
           <t>Sr Manager - Sensor Automation</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461540445/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="n">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="n">
         <v>46265</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1185,19 +1194,19 @@
           <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
-      <c r="D34" s="14" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461264820/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n">
+      <c r="B35" s="16" t="n">
         <v>46267</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1205,19 +1214,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453096131/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="n">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="n">
         <v>46262</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1225,19 +1234,19 @@
           <t>Sr SW Design Quality Engineer</t>
         </is>
       </c>
-      <c r="D36" s="14" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450008915/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B37" s="13" t="n">
+      <c r="B37" s="16" t="n">
         <v>46266</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1245,19 +1254,19 @@
           <t>Engineering Technician 4</t>
         </is>
       </c>
-      <c r="D37" s="14" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461760270/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="n">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="n">
         <v>46265</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1265,19 +1274,19 @@
           <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
-      <c r="D38" s="14" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461275610/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="n">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="n">
         <v>46265</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1285,19 +1294,19 @@
           <t>Associate Customer Insights Manager</t>
         </is>
       </c>
-      <c r="D39" s="14" t="inlineStr">
+      <c r="D39" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434083415/</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="n">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="n">
         <v>46262</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1305,19 +1314,19 @@
           <t>Staff SW QA Engineer</t>
         </is>
       </c>
-      <c r="D40" s="14" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450025503/</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="n">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="n">
         <v>46267</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1325,19 +1334,19 @@
           <t>Lead Corporate Development Manager</t>
         </is>
       </c>
-      <c r="D41" s="14" t="inlineStr">
+      <c r="D41" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462460922/</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B42" s="13" t="n">
+      <c r="B42" s="16" t="n">
         <v>46264</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1345,19 +1354,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D42" s="14" t="inlineStr">
+      <c r="D42" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442446290/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="n">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="n">
         <v>46265</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1365,19 +1374,19 @@
           <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
-      <c r="D43" s="14" t="inlineStr">
+      <c r="D43" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461277558/</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="12" t="inlineStr">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B44" s="13" t="n">
+      <c r="B44" s="16" t="n">
         <v>46267</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1385,19 +1394,19 @@
           <t>Accountant - Healthcare - Edinburgh</t>
         </is>
       </c>
-      <c r="D44" s="14" t="inlineStr">
+      <c r="D44" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453144035/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B45" s="13" t="n">
+      <c r="B45" s="16" t="n">
         <v>46266</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1405,19 +1414,19 @@
           <t>Staff Systems Engineer</t>
         </is>
       </c>
-      <c r="D45" s="14" t="inlineStr">
+      <c r="D45" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461770016/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B46" s="13" t="n">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="n">
         <v>46268</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1425,19 +1434,19 @@
           <t>Staff Quality Compliance Specialist</t>
         </is>
       </c>
-      <c r="D46" s="14" t="inlineStr">
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462730823/</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="inlineStr">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="B47" s="13" t="n">
+      <c r="B47" s="16" t="n">
         <v>46267</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1445,19 +1454,19 @@
           <t>Territory Sales Manager (m/w/d) - Zentralschweiz : Luzern, Obwalden, Nidwalden, Uri, Chur</t>
         </is>
       </c>
-      <c r="D47" s="14" t="inlineStr">
+      <c r="D47" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453133160/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="n">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="n">
         <v>46262</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1465,19 +1474,19 @@
           <t>Staff Planner</t>
         </is>
       </c>
-      <c r="D48" s="14" t="inlineStr">
+      <c r="D48" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450636243/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="n">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="n">
         <v>46267</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1485,19 +1494,19 @@
           <t>Territory Business Manager - Morristown, New Jersey</t>
         </is>
       </c>
-      <c r="D49" s="14" t="inlineStr">
+      <c r="D49" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4452316210/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B50" s="13" t="n">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="n">
         <v>46266</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1505,19 +1514,19 @@
           <t>Sr Manager Medical Affairs</t>
         </is>
       </c>
-      <c r="D50" s="14" t="inlineStr">
+      <c r="D50" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461536483/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B51" s="13" t="n">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B51" s="16" t="n">
         <v>46263</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1525,19 +1534,19 @@
           <t>Capital Planning &amp; Analytics Manager</t>
         </is>
       </c>
-      <c r="D51" s="14" t="inlineStr">
+      <c r="D51" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450775200/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B52" s="13" t="n">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="n">
         <v>46263</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -1545,19 +1554,19 @@
           <t>Supervisor, Manufacturing</t>
         </is>
       </c>
-      <c r="D52" s="14" t="inlineStr">
+      <c r="D52" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460573058/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B53" s="13" t="n">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="n">
         <v>46266</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1565,19 +1574,19 @@
           <t>Territory Business Manager - Anchorage, AK</t>
         </is>
       </c>
-      <c r="D53" s="14" t="inlineStr">
+      <c r="D53" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462041571/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B54" s="13" t="n">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B54" s="16" t="n">
         <v>46268</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1585,19 +1594,19 @@
           <t>QC Inspector 4 - 1B Thur-Sat, every other Wednesday from 5am-5pm</t>
         </is>
       </c>
-      <c r="D54" s="14" t="inlineStr">
+      <c r="D54" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462726839/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="inlineStr">
+      <c r="A55" s="15" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B55" s="13" t="n">
+      <c r="B55" s="16" t="n">
         <v>46267</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1605,19 +1614,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D55" s="14" t="inlineStr">
+      <c r="D55" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097086/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="12" t="inlineStr">
+      <c r="A56" s="15" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B56" s="13" t="n">
+      <c r="B56" s="16" t="n">
         <v>46267</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1625,19 +1634,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D56" s="14" t="inlineStr">
+      <c r="D56" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453076276/</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="12" t="inlineStr">
+      <c r="A57" s="15" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B57" s="13" t="n">
+      <c r="B57" s="16" t="n">
         <v>46266</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1645,19 +1654,19 @@
           <t>Territory Business Manager - Ottawa</t>
         </is>
       </c>
-      <c r="D57" s="14" t="inlineStr">
+      <c r="D57" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462038604/</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" s="15" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B58" s="13" t="n">
+      <c r="B58" s="16" t="n">
         <v>46267</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1665,19 +1674,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D58" s="14" t="inlineStr">
+      <c r="D58" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453087192/</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B59" s="13" t="n">
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B59" s="16" t="n">
         <v>46267</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1685,19 +1694,19 @@
           <t>Manufacturing Technician 3-1B Thursday-Saturday every other Wednesday(5AM-5PM)</t>
         </is>
       </c>
-      <c r="D59" s="14" t="inlineStr">
+      <c r="D59" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460900071/</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B60" s="13" t="n">
+      <c r="A60" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B60" s="16" t="n">
         <v>46266</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1705,19 +1714,19 @@
           <t>Equipment Technician 2-1A Sunday-Tuesday every other Wednesday(5AM-5PM)</t>
         </is>
       </c>
-      <c r="D60" s="14" t="inlineStr">
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461550206/</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="12" t="inlineStr">
+      <c r="A61" s="15" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B61" s="13" t="n">
+      <c r="B61" s="16" t="n">
         <v>46267</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1725,19 +1734,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D61" s="14" t="inlineStr">
+      <c r="D61" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453078274/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" s="15" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B62" s="13" t="n">
+      <c r="B62" s="16" t="n">
         <v>46266</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1745,19 +1754,19 @@
           <t>Staff Veeva and Master Data Analyst</t>
         </is>
       </c>
-      <c r="D62" s="14" t="inlineStr">
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461758265/</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="n">
+      <c r="A63" s="15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B63" s="16" t="n">
         <v>46268</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1765,19 +1774,19 @@
           <t>Platform Security Engineer 2</t>
         </is>
       </c>
-      <c r="D63" s="14" t="inlineStr">
+      <c r="D63" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462736772/</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="12" t="inlineStr">
+      <c r="A64" s="15" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B64" s="13" t="n">
+      <c r="B64" s="16" t="n">
         <v>46268</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1785,19 +1794,19 @@
           <t>APAC FP&amp;A Manager</t>
         </is>
       </c>
-      <c r="D64" s="14" t="inlineStr">
+      <c r="D64" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462770899/</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+      <c r="A65" s="15" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B65" s="13" t="n">
+      <c r="B65" s="16" t="n">
         <v>46268</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1805,7 +1814,7 @@
           <t>Commercial Analytics &amp; Operations Associate</t>
         </is>
       </c>
-      <c r="D65" s="14" t="inlineStr">
+      <c r="D65" s="17" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462778751/</t>
         </is>
@@ -1891,8 +1900,448 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B70" s="19" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Product Manager, Patient Onboarding &amp; First Value</t>
+        </is>
+      </c>
+      <c r="D70" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453357502/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B71" s="19" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Staff Technical Program Manager - Innovation Ventures &amp; Sensor Technology</t>
+        </is>
+      </c>
+      <c r="D71" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4454853005/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B72" s="19" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Project Manager 2</t>
+        </is>
+      </c>
+      <c r="D72" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463687671/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Senior Medical Affairs Manager – Value, Evidence, and Outcomes</t>
+        </is>
+      </c>
+      <c r="D73" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443448275/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B74" s="19" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Director of Sensor Research</t>
+        </is>
+      </c>
+      <c r="D74" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4427088373/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B75" s="19" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Staff QA Engineer</t>
+        </is>
+      </c>
+      <c r="D75" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436409441/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="18" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B76" s="19" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Distributor Manager - Channel Excellence (MedTech)</t>
+        </is>
+      </c>
+      <c r="D76" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463683762/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B77" s="19" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Territory Business Manager - Erie Pennsylvania</t>
+        </is>
+      </c>
+      <c r="D77" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4440304526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B78" s="19" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>QA Inspector 2 ( Dobson ) - 1A Sun- Tues, every other Wednesday, Can work anytime from 5am-5pm</t>
+        </is>
+      </c>
+      <c r="D78" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463691655/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="18" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B79" s="19" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Distributor Manager - Channel Excellence (MedTech)</t>
+        </is>
+      </c>
+      <c r="D79" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463684766/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B80" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Clinical Customer Advocate</t>
+        </is>
+      </c>
+      <c r="D80" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463625584/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B81" s="19" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Staff Data Scientist</t>
+        </is>
+      </c>
+      <c r="D81" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463110275/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="18" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B82" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Senior Forecasting Analyst – Healthcare - UK</t>
+        </is>
+      </c>
+      <c r="D82" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463622979/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="18" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B83" s="19" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Bracknell, UK</t>
+        </is>
+      </c>
+      <c r="D83" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4462849233/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B84" s="19" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Hardware Engineer 2</t>
+        </is>
+      </c>
+      <c r="D84" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4454834815/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B85" s="19" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Principal SW Development Engineer</t>
+        </is>
+      </c>
+      <c r="D85" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453345730/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="18" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B86" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Senior Forecasting Analyst – Healthcare - UK</t>
+        </is>
+      </c>
+      <c r="D86" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463634192/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B87" s="19" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Associate Customer Experience Manager</t>
+        </is>
+      </c>
+      <c r="D87" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4454599227/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B88" s="19" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Sr Software QA Engineer</t>
+        </is>
+      </c>
+      <c r="D88" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453636185/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="18" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B89" s="19" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
+        </is>
+      </c>
+      <c r="D89" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453092177/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="18" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B90" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Senior Forecasting Analyst</t>
+        </is>
+      </c>
+      <c r="D90" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463637144/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="18" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B91" s="19" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D91" s="20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461756319/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D69"/>
+  <autoFilter ref="A1:D91"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -1962,6 +2411,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -509,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -541,12 +550,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -554,19 +563,19 @@
           <t>Sr Project Lead - APAC</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461543326/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="19" t="n">
         <v>46262</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -574,19 +583,19 @@
           <t>SW Development Engineer 2</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460357219/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="19" t="n">
         <v>46267</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -594,19 +603,19 @@
           <t>Intelligence Analyst</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453085191/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -614,19 +623,19 @@
           <t>Senior Manager Corporate Compliance - EMEA (m/w/d)</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461752409/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="19" t="n">
         <v>46262</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -634,19 +643,19 @@
           <t>Customer Service Representative - French Speaker</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460500502/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="19" t="n">
         <v>46265</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -654,19 +663,19 @@
           <t>Staff Program Manager</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451501447/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="n">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -674,19 +683,19 @@
           <t>Lead Legal Counsel - Employment</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4430864197/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="19" t="n">
         <v>46262</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -694,19 +703,19 @@
           <t>Sr Manager, Software Systems &amp; Solutions</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4218028502/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="19" t="n">
         <v>46262</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -714,19 +723,19 @@
           <t>Manager SW Test Development Engineering</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4281993770/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="19" t="n">
         <v>46263</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -734,19 +743,19 @@
           <t>Security and Privacy Compliance Analyst - Cybersecurity</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4257269392/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -754,19 +763,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461768038/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -774,19 +783,19 @@
           <t>Mechanical Engineer 2</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462032756/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="19" t="n">
         <v>46263</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -794,19 +803,19 @@
           <t>Supervisor Customer Advocacy</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442102156/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="n">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
         <v>46267</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -814,19 +823,19 @@
           <t>Senior Staff Process Development Engineer</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443563067/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -834,19 +843,19 @@
           <t>Staff Process Engineer</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461543337/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="n">
         <v>46262</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -854,19 +863,19 @@
           <t>Sr QA Engineer</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460398658/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n">
         <v>46268</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -874,19 +883,19 @@
           <t>Senior Director, Lean</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462725850/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -894,19 +903,19 @@
           <t>Benefits Analyst</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461581171/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="19" t="n">
         <v>46262</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -914,19 +923,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458914791/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="19" t="n">
         <v>46262</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -934,19 +943,19 @@
           <t>Financial Analyst</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441984900/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" s="19" t="n">
         <v>46267</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -954,19 +963,19 @@
           <t>Intelligence Analyst</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082218/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -974,19 +983,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765127/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
+      <c r="B24" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -994,19 +1003,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461754390/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
+      <c r="B25" s="19" t="n">
         <v>46262</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1014,19 +1023,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458902988/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="n">
         <v>46263</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1034,19 +1043,19 @@
           <t>Benefits Manager (Americas)</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450760638/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
+      <c r="B27" s="19" t="n">
         <v>46265</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1054,19 +1063,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451545592/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
+      <c r="B28" s="19" t="n">
         <v>46267</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1074,19 +1083,19 @@
           <t>Sr Process Engineer</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435122348/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
+      <c r="B29" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1094,19 +1103,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461772012/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
+      <c r="B30" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1114,19 +1123,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765131/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n">
+      <c r="B31" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1134,19 +1143,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461762151/</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="n">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="n">
         <v>46265</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1154,19 +1163,19 @@
           <t>New Business Development Manager (Senior Analyst, Strategic Finance )</t>
         </is>
       </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434090087/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="n">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1174,19 +1183,19 @@
           <t>Sr Manager - Sensor Automation</t>
         </is>
       </c>
-      <c r="D33" s="17" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461540445/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="n">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="n">
         <v>46265</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1194,19 +1203,19 @@
           <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461264820/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n">
+      <c r="B35" s="19" t="n">
         <v>46267</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1214,19 +1223,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453096131/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="n">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="n">
         <v>46262</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1234,19 +1243,19 @@
           <t>Sr SW Design Quality Engineer</t>
         </is>
       </c>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="D36" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450008915/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
+      <c r="B37" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1254,19 +1263,19 @@
           <t>Engineering Technician 4</t>
         </is>
       </c>
-      <c r="D37" s="17" t="inlineStr">
+      <c r="D37" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461760270/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="n">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="n">
         <v>46265</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1274,19 +1283,19 @@
           <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="D38" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461275610/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="n">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="n">
         <v>46265</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1294,19 +1303,19 @@
           <t>Associate Customer Insights Manager</t>
         </is>
       </c>
-      <c r="D39" s="17" t="inlineStr">
+      <c r="D39" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434083415/</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="n">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="n">
         <v>46262</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1314,19 +1323,19 @@
           <t>Staff SW QA Engineer</t>
         </is>
       </c>
-      <c r="D40" s="17" t="inlineStr">
+      <c r="D40" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450025503/</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="n">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="n">
         <v>46267</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1334,19 +1343,19 @@
           <t>Lead Corporate Development Manager</t>
         </is>
       </c>
-      <c r="D41" s="17" t="inlineStr">
+      <c r="D41" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462460922/</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="18" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n">
+      <c r="B42" s="19" t="n">
         <v>46264</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1354,19 +1363,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D42" s="17" t="inlineStr">
+      <c r="D42" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442446290/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="n">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="n">
         <v>46265</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1374,19 +1383,19 @@
           <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
-      <c r="D43" s="17" t="inlineStr">
+      <c r="D43" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461277558/</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n">
+      <c r="B44" s="19" t="n">
         <v>46267</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1394,19 +1403,19 @@
           <t>Accountant - Healthcare - Edinburgh</t>
         </is>
       </c>
-      <c r="D44" s="17" t="inlineStr">
+      <c r="D44" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453144035/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n">
+      <c r="B45" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1414,19 +1423,19 @@
           <t>Staff Systems Engineer</t>
         </is>
       </c>
-      <c r="D45" s="17" t="inlineStr">
+      <c r="D45" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461770016/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="n">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B46" s="19" t="n">
         <v>46268</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1434,19 +1443,19 @@
           <t>Staff Quality Compliance Specialist</t>
         </is>
       </c>
-      <c r="D46" s="17" t="inlineStr">
+      <c r="D46" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462730823/</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n">
+      <c r="B47" s="19" t="n">
         <v>46267</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1454,19 +1463,19 @@
           <t>Territory Sales Manager (m/w/d) - Zentralschweiz : Luzern, Obwalden, Nidwalden, Uri, Chur</t>
         </is>
       </c>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="D47" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453133160/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n">
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="n">
         <v>46262</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1474,19 +1483,19 @@
           <t>Staff Planner</t>
         </is>
       </c>
-      <c r="D48" s="17" t="inlineStr">
+      <c r="D48" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450636243/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="n">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="n">
         <v>46267</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1494,19 +1503,19 @@
           <t>Territory Business Manager - Morristown, New Jersey</t>
         </is>
       </c>
-      <c r="D49" s="17" t="inlineStr">
+      <c r="D49" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4452316210/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="n">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1514,19 +1523,19 @@
           <t>Sr Manager Medical Affairs</t>
         </is>
       </c>
-      <c r="D50" s="17" t="inlineStr">
+      <c r="D50" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461536483/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="n">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="n">
         <v>46263</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1534,19 +1543,19 @@
           <t>Capital Planning &amp; Analytics Manager</t>
         </is>
       </c>
-      <c r="D51" s="17" t="inlineStr">
+      <c r="D51" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450775200/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="n">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B52" s="19" t="n">
         <v>46263</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -1554,19 +1563,19 @@
           <t>Supervisor, Manufacturing</t>
         </is>
       </c>
-      <c r="D52" s="17" t="inlineStr">
+      <c r="D52" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460573058/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="n">
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1574,19 +1583,19 @@
           <t>Territory Business Manager - Anchorage, AK</t>
         </is>
       </c>
-      <c r="D53" s="17" t="inlineStr">
+      <c r="D53" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462041571/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="n">
+      <c r="A54" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="n">
         <v>46268</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1594,19 +1603,19 @@
           <t>QC Inspector 4 - 1B Thur-Sat, every other Wednesday from 5am-5pm</t>
         </is>
       </c>
-      <c r="D54" s="17" t="inlineStr">
+      <c r="D54" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462726839/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="15" t="inlineStr">
+      <c r="A55" s="18" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B55" s="16" t="n">
+      <c r="B55" s="19" t="n">
         <v>46267</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1614,19 +1623,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D55" s="17" t="inlineStr">
+      <c r="D55" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097086/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="15" t="inlineStr">
+      <c r="A56" s="18" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B56" s="16" t="n">
+      <c r="B56" s="19" t="n">
         <v>46267</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1634,19 +1643,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D56" s="17" t="inlineStr">
+      <c r="D56" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453076276/</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="15" t="inlineStr">
+      <c r="A57" s="18" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B57" s="16" t="n">
+      <c r="B57" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1654,19 +1663,19 @@
           <t>Territory Business Manager - Ottawa</t>
         </is>
       </c>
-      <c r="D57" s="17" t="inlineStr">
+      <c r="D57" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462038604/</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="15" t="inlineStr">
+      <c r="A58" s="18" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B58" s="16" t="n">
+      <c r="B58" s="19" t="n">
         <v>46267</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1674,19 +1683,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D58" s="17" t="inlineStr">
+      <c r="D58" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453087192/</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B59" s="16" t="n">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B59" s="19" t="n">
         <v>46267</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1694,19 +1703,19 @@
           <t>Manufacturing Technician 3-1B Thursday-Saturday every other Wednesday(5AM-5PM)</t>
         </is>
       </c>
-      <c r="D59" s="17" t="inlineStr">
+      <c r="D59" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460900071/</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B60" s="16" t="n">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B60" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1714,19 +1723,19 @@
           <t>Equipment Technician 2-1A Sunday-Tuesday every other Wednesday(5AM-5PM)</t>
         </is>
       </c>
-      <c r="D60" s="17" t="inlineStr">
+      <c r="D60" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461550206/</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="15" t="inlineStr">
+      <c r="A61" s="18" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B61" s="16" t="n">
+      <c r="B61" s="19" t="n">
         <v>46267</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1734,19 +1743,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D61" s="17" t="inlineStr">
+      <c r="D61" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453078274/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="15" t="inlineStr">
+      <c r="A62" s="18" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B62" s="16" t="n">
+      <c r="B62" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1754,19 +1763,19 @@
           <t>Staff Veeva and Master Data Analyst</t>
         </is>
       </c>
-      <c r="D62" s="17" t="inlineStr">
+      <c r="D62" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461758265/</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B63" s="16" t="n">
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B63" s="19" t="n">
         <v>46268</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1774,19 +1783,19 @@
           <t>Platform Security Engineer 2</t>
         </is>
       </c>
-      <c r="D63" s="17" t="inlineStr">
+      <c r="D63" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462736772/</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="15" t="inlineStr">
+      <c r="A64" s="18" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B64" s="16" t="n">
+      <c r="B64" s="19" t="n">
         <v>46268</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1794,19 +1803,19 @@
           <t>APAC FP&amp;A Manager</t>
         </is>
       </c>
-      <c r="D64" s="17" t="inlineStr">
+      <c r="D64" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462770899/</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="15" t="inlineStr">
+      <c r="A65" s="18" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B65" s="16" t="n">
+      <c r="B65" s="19" t="n">
         <v>46268</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1814,19 +1823,19 @@
           <t>Commercial Analytics &amp; Operations Associate</t>
         </is>
       </c>
-      <c r="D65" s="17" t="inlineStr">
+      <c r="D65" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462778751/</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B66" s="16" t="n">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B66" s="19" t="n">
         <v>46269</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1834,19 +1843,19 @@
           <t>Document Control and Training Specialist 1</t>
         </is>
       </c>
-      <c r="D66" s="17" t="inlineStr">
+      <c r="D66" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463157831/</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="15" t="inlineStr">
+      <c r="A67" s="18" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B67" s="16" t="n">
+      <c r="B67" s="19" t="n">
         <v>46269</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1854,19 +1863,19 @@
           <t>Sr Supply Chain Analyst</t>
         </is>
       </c>
-      <c r="D67" s="17" t="inlineStr">
+      <c r="D67" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463169639/</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="15" t="inlineStr">
+      <c r="A68" s="18" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B68" s="16" t="n">
+      <c r="B68" s="19" t="n">
         <v>46269</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1874,19 +1883,19 @@
           <t>IT Procurement Analyst</t>
         </is>
       </c>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="D68" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463313428/</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="15" t="inlineStr">
+      <c r="A69" s="18" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B69" s="16" t="n">
+      <c r="B69" s="19" t="n">
         <v>46269</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1894,7 +1903,7 @@
           <t>IT Procurement Analyst</t>
         </is>
       </c>
-      <c r="D69" s="17" t="inlineStr">
+      <c r="D69" s="20" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463314400/</t>
         </is>
@@ -2340,8 +2349,28 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B92" s="22" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>Senior SW Development Engineer</t>
+        </is>
+      </c>
+      <c r="D92" s="23" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4454303425/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D91"/>
+  <autoFilter ref="A1:D92"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -2433,6 +2462,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId91"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -518,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -550,12 +559,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B2" s="19" t="n">
+      <c r="B2" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -563,19 +572,19 @@
           <t>Sr Project Lead - APAC</t>
         </is>
       </c>
-      <c r="D2" s="20" t="inlineStr">
+      <c r="D2" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461543326/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B3" s="19" t="n">
+      <c r="B3" s="22" t="n">
         <v>46262</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -583,19 +592,19 @@
           <t>SW Development Engineer 2</t>
         </is>
       </c>
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460357219/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B4" s="19" t="n">
+      <c r="B4" s="22" t="n">
         <v>46267</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -603,19 +612,19 @@
           <t>Intelligence Analyst</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453085191/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
+      <c r="B5" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -623,19 +632,19 @@
           <t>Senior Manager Corporate Compliance - EMEA (m/w/d)</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461752409/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
+      <c r="B6" s="22" t="n">
         <v>46262</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -643,19 +652,19 @@
           <t>Customer Service Representative - French Speaker</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460500502/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="22" t="n">
         <v>46265</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -663,19 +672,19 @@
           <t>Staff Program Manager</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451501447/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="n">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -683,19 +692,19 @@
           <t>Lead Legal Counsel - Employment</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4430864197/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="22" t="n">
         <v>46262</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -703,19 +712,19 @@
           <t>Sr Manager, Software Systems &amp; Solutions</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4218028502/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n">
+      <c r="B10" s="22" t="n">
         <v>46262</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -723,19 +732,19 @@
           <t>Manager SW Test Development Engineering</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4281993770/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n">
+      <c r="B11" s="22" t="n">
         <v>46263</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -743,19 +752,19 @@
           <t>Security and Privacy Compliance Analyst - Cybersecurity</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4257269392/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n">
+      <c r="B12" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -763,19 +772,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461768038/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="n">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -783,19 +792,19 @@
           <t>Mechanical Engineer 2</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462032756/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B14" s="19" t="n">
+      <c r="B14" s="22" t="n">
         <v>46263</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -803,19 +812,19 @@
           <t>Supervisor Customer Advocacy</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442102156/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="n">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="n">
         <v>46267</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -823,19 +832,19 @@
           <t>Senior Staff Process Development Engineer</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443563067/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="n">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -843,19 +852,19 @@
           <t>Staff Process Engineer</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461543337/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="n">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="n">
         <v>46262</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -863,19 +872,19 @@
           <t>Sr QA Engineer</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460398658/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="n">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="n">
         <v>46268</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -883,19 +892,19 @@
           <t>Senior Director, Lean</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462725850/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B19" s="19" t="n">
+      <c r="B19" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -903,19 +912,19 @@
           <t>Benefits Analyst</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461581171/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B20" s="19" t="n">
+      <c r="B20" s="22" t="n">
         <v>46262</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -923,19 +932,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458914791/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B21" s="19" t="n">
+      <c r="B21" s="22" t="n">
         <v>46262</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -943,19 +952,19 @@
           <t>Financial Analyst</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441984900/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B22" s="19" t="n">
+      <c r="B22" s="22" t="n">
         <v>46267</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -963,19 +972,19 @@
           <t>Intelligence Analyst</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082218/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B23" s="19" t="n">
+      <c r="B23" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -983,19 +992,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765127/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B24" s="19" t="n">
+      <c r="B24" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1003,19 +1012,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461754390/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B25" s="19" t="n">
+      <c r="B25" s="22" t="n">
         <v>46262</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1023,19 +1032,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458902988/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="n">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n">
         <v>46263</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1043,19 +1052,19 @@
           <t>Benefits Manager (Americas)</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450760638/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B27" s="19" t="n">
+      <c r="B27" s="22" t="n">
         <v>46265</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1063,19 +1072,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451545592/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B28" s="19" t="n">
+      <c r="B28" s="22" t="n">
         <v>46267</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1083,19 +1092,19 @@
           <t>Sr Process Engineer</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435122348/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B29" s="19" t="n">
+      <c r="B29" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1103,19 +1112,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D29" s="20" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461772012/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B30" s="19" t="n">
+      <c r="B30" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1123,19 +1132,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D30" s="20" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765131/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n">
+      <c r="B31" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1143,19 +1152,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D31" s="20" t="inlineStr">
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461762151/</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="n">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n">
         <v>46265</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1163,19 +1172,19 @@
           <t>New Business Development Manager (Senior Analyst, Strategic Finance )</t>
         </is>
       </c>
-      <c r="D32" s="20" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434090087/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="n">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1183,19 +1192,19 @@
           <t>Sr Manager - Sensor Automation</t>
         </is>
       </c>
-      <c r="D33" s="20" t="inlineStr">
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461540445/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B34" s="19" t="n">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="n">
         <v>46265</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1203,19 +1212,19 @@
           <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
-      <c r="D34" s="20" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461264820/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B35" s="19" t="n">
+      <c r="B35" s="22" t="n">
         <v>46267</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1223,19 +1232,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D35" s="20" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453096131/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B36" s="19" t="n">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="n">
         <v>46262</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1243,19 +1252,19 @@
           <t>Sr SW Design Quality Engineer</t>
         </is>
       </c>
-      <c r="D36" s="20" t="inlineStr">
+      <c r="D36" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450008915/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B37" s="19" t="n">
+      <c r="B37" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1263,19 +1272,19 @@
           <t>Engineering Technician 4</t>
         </is>
       </c>
-      <c r="D37" s="20" t="inlineStr">
+      <c r="D37" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461760270/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B38" s="19" t="n">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="n">
         <v>46265</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1283,19 +1292,19 @@
           <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
-      <c r="D38" s="20" t="inlineStr">
+      <c r="D38" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461275610/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B39" s="19" t="n">
+      <c r="A39" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="n">
         <v>46265</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1303,19 +1312,19 @@
           <t>Associate Customer Insights Manager</t>
         </is>
       </c>
-      <c r="D39" s="20" t="inlineStr">
+      <c r="D39" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434083415/</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B40" s="19" t="n">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="n">
         <v>46262</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1323,19 +1332,19 @@
           <t>Staff SW QA Engineer</t>
         </is>
       </c>
-      <c r="D40" s="20" t="inlineStr">
+      <c r="D40" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450025503/</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B41" s="19" t="n">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="n">
         <v>46267</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1343,19 +1352,19 @@
           <t>Lead Corporate Development Manager</t>
         </is>
       </c>
-      <c r="D41" s="20" t="inlineStr">
+      <c r="D41" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462460922/</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B42" s="19" t="n">
+      <c r="B42" s="22" t="n">
         <v>46264</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1363,19 +1372,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D42" s="20" t="inlineStr">
+      <c r="D42" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442446290/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B43" s="19" t="n">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="n">
         <v>46265</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1383,19 +1392,19 @@
           <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
-      <c r="D43" s="20" t="inlineStr">
+      <c r="D43" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461277558/</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B44" s="19" t="n">
+      <c r="B44" s="22" t="n">
         <v>46267</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1403,19 +1412,19 @@
           <t>Accountant - Healthcare - Edinburgh</t>
         </is>
       </c>
-      <c r="D44" s="20" t="inlineStr">
+      <c r="D44" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453144035/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B45" s="19" t="n">
+      <c r="B45" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1423,19 +1432,19 @@
           <t>Staff Systems Engineer</t>
         </is>
       </c>
-      <c r="D45" s="20" t="inlineStr">
+      <c r="D45" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461770016/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B46" s="19" t="n">
+      <c r="A46" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="n">
         <v>46268</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1443,19 +1452,19 @@
           <t>Staff Quality Compliance Specialist</t>
         </is>
       </c>
-      <c r="D46" s="20" t="inlineStr">
+      <c r="D46" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462730823/</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="inlineStr">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="B47" s="19" t="n">
+      <c r="B47" s="22" t="n">
         <v>46267</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1463,19 +1472,19 @@
           <t>Territory Sales Manager (m/w/d) - Zentralschweiz : Luzern, Obwalden, Nidwalden, Uri, Chur</t>
         </is>
       </c>
-      <c r="D47" s="20" t="inlineStr">
+      <c r="D47" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453133160/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B48" s="19" t="n">
+      <c r="A48" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="n">
         <v>46262</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1483,19 +1492,19 @@
           <t>Staff Planner</t>
         </is>
       </c>
-      <c r="D48" s="20" t="inlineStr">
+      <c r="D48" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450636243/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B49" s="19" t="n">
+      <c r="A49" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="n">
         <v>46267</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1503,19 +1512,19 @@
           <t>Territory Business Manager - Morristown, New Jersey</t>
         </is>
       </c>
-      <c r="D49" s="20" t="inlineStr">
+      <c r="D49" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4452316210/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B50" s="19" t="n">
+      <c r="A50" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1523,19 +1532,19 @@
           <t>Sr Manager Medical Affairs</t>
         </is>
       </c>
-      <c r="D50" s="20" t="inlineStr">
+      <c r="D50" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461536483/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B51" s="19" t="n">
+      <c r="A51" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="n">
         <v>46263</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1543,19 +1552,19 @@
           <t>Capital Planning &amp; Analytics Manager</t>
         </is>
       </c>
-      <c r="D51" s="20" t="inlineStr">
+      <c r="D51" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450775200/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B52" s="19" t="n">
+      <c r="A52" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="n">
         <v>46263</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -1563,19 +1572,19 @@
           <t>Supervisor, Manufacturing</t>
         </is>
       </c>
-      <c r="D52" s="20" t="inlineStr">
+      <c r="D52" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460573058/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B53" s="19" t="n">
+      <c r="A53" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1583,19 +1592,19 @@
           <t>Territory Business Manager - Anchorage, AK</t>
         </is>
       </c>
-      <c r="D53" s="20" t="inlineStr">
+      <c r="D53" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462041571/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B54" s="19" t="n">
+      <c r="A54" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="n">
         <v>46268</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1603,19 +1612,19 @@
           <t>QC Inspector 4 - 1B Thur-Sat, every other Wednesday from 5am-5pm</t>
         </is>
       </c>
-      <c r="D54" s="20" t="inlineStr">
+      <c r="D54" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462726839/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="inlineStr">
+      <c r="A55" s="21" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B55" s="19" t="n">
+      <c r="B55" s="22" t="n">
         <v>46267</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1623,19 +1632,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D55" s="20" t="inlineStr">
+      <c r="D55" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097086/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="inlineStr">
+      <c r="A56" s="21" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B56" s="19" t="n">
+      <c r="B56" s="22" t="n">
         <v>46267</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1643,19 +1652,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D56" s="20" t="inlineStr">
+      <c r="D56" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453076276/</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="inlineStr">
+      <c r="A57" s="21" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B57" s="19" t="n">
+      <c r="B57" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1663,19 +1672,19 @@
           <t>Territory Business Manager - Ottawa</t>
         </is>
       </c>
-      <c r="D57" s="20" t="inlineStr">
+      <c r="D57" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462038604/</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="inlineStr">
+      <c r="A58" s="21" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B58" s="19" t="n">
+      <c r="B58" s="22" t="n">
         <v>46267</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1683,19 +1692,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D58" s="20" t="inlineStr">
+      <c r="D58" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453087192/</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B59" s="19" t="n">
+      <c r="A59" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B59" s="22" t="n">
         <v>46267</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1703,19 +1712,19 @@
           <t>Manufacturing Technician 3-1B Thursday-Saturday every other Wednesday(5AM-5PM)</t>
         </is>
       </c>
-      <c r="D59" s="20" t="inlineStr">
+      <c r="D59" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460900071/</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B60" s="19" t="n">
+      <c r="A60" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1723,19 +1732,19 @@
           <t>Equipment Technician 2-1A Sunday-Tuesday every other Wednesday(5AM-5PM)</t>
         </is>
       </c>
-      <c r="D60" s="20" t="inlineStr">
+      <c r="D60" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461550206/</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="inlineStr">
+      <c r="A61" s="21" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B61" s="19" t="n">
+      <c r="B61" s="22" t="n">
         <v>46267</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1743,19 +1752,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D61" s="20" t="inlineStr">
+      <c r="D61" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453078274/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="inlineStr">
+      <c r="A62" s="21" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B62" s="19" t="n">
+      <c r="B62" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1763,19 +1772,19 @@
           <t>Staff Veeva and Master Data Analyst</t>
         </is>
       </c>
-      <c r="D62" s="20" t="inlineStr">
+      <c r="D62" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461758265/</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B63" s="19" t="n">
+      <c r="A63" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B63" s="22" t="n">
         <v>46268</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1783,19 +1792,19 @@
           <t>Platform Security Engineer 2</t>
         </is>
       </c>
-      <c r="D63" s="20" t="inlineStr">
+      <c r="D63" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462736772/</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="inlineStr">
+      <c r="A64" s="21" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B64" s="19" t="n">
+      <c r="B64" s="22" t="n">
         <v>46268</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1803,19 +1812,19 @@
           <t>APAC FP&amp;A Manager</t>
         </is>
       </c>
-      <c r="D64" s="20" t="inlineStr">
+      <c r="D64" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462770899/</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="inlineStr">
+      <c r="A65" s="21" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B65" s="19" t="n">
+      <c r="B65" s="22" t="n">
         <v>46268</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1823,19 +1832,19 @@
           <t>Commercial Analytics &amp; Operations Associate</t>
         </is>
       </c>
-      <c r="D65" s="20" t="inlineStr">
+      <c r="D65" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462778751/</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B66" s="19" t="n">
+      <c r="A66" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B66" s="22" t="n">
         <v>46269</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1843,19 +1852,19 @@
           <t>Document Control and Training Specialist 1</t>
         </is>
       </c>
-      <c r="D66" s="20" t="inlineStr">
+      <c r="D66" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463157831/</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="18" t="inlineStr">
+      <c r="A67" s="21" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B67" s="19" t="n">
+      <c r="B67" s="22" t="n">
         <v>46269</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1863,19 +1872,19 @@
           <t>Sr Supply Chain Analyst</t>
         </is>
       </c>
-      <c r="D67" s="20" t="inlineStr">
+      <c r="D67" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463169639/</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="18" t="inlineStr">
+      <c r="A68" s="21" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B68" s="19" t="n">
+      <c r="B68" s="22" t="n">
         <v>46269</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1883,19 +1892,19 @@
           <t>IT Procurement Analyst</t>
         </is>
       </c>
-      <c r="D68" s="20" t="inlineStr">
+      <c r="D68" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463313428/</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="18" t="inlineStr">
+      <c r="A69" s="21" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B69" s="19" t="n">
+      <c r="B69" s="22" t="n">
         <v>46269</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1903,19 +1912,19 @@
           <t>IT Procurement Analyst</t>
         </is>
       </c>
-      <c r="D69" s="20" t="inlineStr">
+      <c r="D69" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463314400/</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B70" s="19" t="n">
+      <c r="A70" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B70" s="22" t="n">
         <v>46268</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1923,19 +1932,19 @@
           <t>Product Manager, Patient Onboarding &amp; First Value</t>
         </is>
       </c>
-      <c r="D70" s="20" t="inlineStr">
+      <c r="D70" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453357502/</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B71" s="19" t="n">
+      <c r="A71" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="n">
         <v>46270</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1943,19 +1952,19 @@
           <t>Staff Technical Program Manager - Innovation Ventures &amp; Sensor Technology</t>
         </is>
       </c>
-      <c r="D71" s="20" t="inlineStr">
+      <c r="D71" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454853005/</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B72" s="19" t="n">
+      <c r="A72" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B72" s="22" t="n">
         <v>46270</v>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -1963,19 +1972,19 @@
           <t>Project Manager 2</t>
         </is>
       </c>
-      <c r="D72" s="20" t="inlineStr">
+      <c r="D72" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463687671/</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B73" s="19" t="n">
+      <c r="A73" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B73" s="22" t="n">
         <v>46269</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -1983,19 +1992,19 @@
           <t>Senior Medical Affairs Manager – Value, Evidence, and Outcomes</t>
         </is>
       </c>
-      <c r="D73" s="20" t="inlineStr">
+      <c r="D73" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443448275/</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B74" s="19" t="n">
+      <c r="A74" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B74" s="22" t="n">
         <v>46268</v>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -2003,19 +2012,19 @@
           <t>Director of Sensor Research</t>
         </is>
       </c>
-      <c r="D74" s="20" t="inlineStr">
+      <c r="D74" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427088373/</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B75" s="19" t="n">
+      <c r="A75" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B75" s="22" t="n">
         <v>46271</v>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -2023,19 +2032,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D75" s="20" t="inlineStr">
+      <c r="D75" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436409441/</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="18" t="inlineStr">
+      <c r="A76" s="21" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B76" s="19" t="n">
+      <c r="B76" s="22" t="n">
         <v>46270</v>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -2043,19 +2052,19 @@
           <t>Distributor Manager - Channel Excellence (MedTech)</t>
         </is>
       </c>
-      <c r="D76" s="20" t="inlineStr">
+      <c r="D76" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463683762/</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B77" s="19" t="n">
+      <c r="A77" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B77" s="22" t="n">
         <v>46268</v>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -2063,19 +2072,19 @@
           <t>Territory Business Manager - Erie Pennsylvania</t>
         </is>
       </c>
-      <c r="D77" s="20" t="inlineStr">
+      <c r="D77" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440304526/</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B78" s="19" t="n">
+      <c r="A78" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B78" s="22" t="n">
         <v>46270</v>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -2083,19 +2092,19 @@
           <t>QA Inspector 2 ( Dobson ) - 1A Sun- Tues, every other Wednesday, Can work anytime from 5am-5pm</t>
         </is>
       </c>
-      <c r="D78" s="20" t="inlineStr">
+      <c r="D78" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463691655/</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="18" t="inlineStr">
+      <c r="A79" s="21" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B79" s="19" t="n">
+      <c r="B79" s="22" t="n">
         <v>46270</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -2103,19 +2112,19 @@
           <t>Distributor Manager - Channel Excellence (MedTech)</t>
         </is>
       </c>
-      <c r="D79" s="20" t="inlineStr">
+      <c r="D79" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463684766/</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B80" s="19" t="n">
+      <c r="A80" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B80" s="22" t="n">
         <v>46269</v>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -2123,19 +2132,19 @@
           <t>Sr. Clinical Customer Advocate</t>
         </is>
       </c>
-      <c r="D80" s="20" t="inlineStr">
+      <c r="D80" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463625584/</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B81" s="19" t="n">
+      <c r="A81" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B81" s="22" t="n">
         <v>46268</v>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2143,19 +2152,19 @@
           <t>Staff Data Scientist</t>
         </is>
       </c>
-      <c r="D81" s="20" t="inlineStr">
+      <c r="D81" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463110275/</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="18" t="inlineStr">
+      <c r="A82" s="21" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B82" s="19" t="n">
+      <c r="B82" s="22" t="n">
         <v>46269</v>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -2163,19 +2172,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D82" s="20" t="inlineStr">
+      <c r="D82" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463622979/</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="18" t="inlineStr">
+      <c r="A83" s="21" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B83" s="19" t="n">
+      <c r="B83" s="22" t="n">
         <v>46268</v>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2183,19 +2192,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Bracknell, UK</t>
         </is>
       </c>
-      <c r="D83" s="20" t="inlineStr">
+      <c r="D83" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462849233/</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B84" s="19" t="n">
+      <c r="A84" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B84" s="22" t="n">
         <v>46270</v>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -2203,19 +2212,19 @@
           <t>Hardware Engineer 2</t>
         </is>
       </c>
-      <c r="D84" s="20" t="inlineStr">
+      <c r="D84" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454834815/</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B85" s="19" t="n">
+      <c r="A85" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B85" s="22" t="n">
         <v>46268</v>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2223,19 +2232,19 @@
           <t>Principal SW Development Engineer</t>
         </is>
       </c>
-      <c r="D85" s="20" t="inlineStr">
+      <c r="D85" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453345730/</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="18" t="inlineStr">
+      <c r="A86" s="21" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B86" s="19" t="n">
+      <c r="B86" s="22" t="n">
         <v>46269</v>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -2243,19 +2252,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D86" s="20" t="inlineStr">
+      <c r="D86" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463634192/</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B87" s="19" t="n">
+      <c r="A87" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B87" s="22" t="n">
         <v>46270</v>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -2263,19 +2272,19 @@
           <t>Associate Customer Experience Manager</t>
         </is>
       </c>
-      <c r="D87" s="20" t="inlineStr">
+      <c r="D87" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454599227/</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B88" s="19" t="n">
+      <c r="A88" s="21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B88" s="22" t="n">
         <v>46268</v>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -2283,19 +2292,19 @@
           <t>Sr Software QA Engineer</t>
         </is>
       </c>
-      <c r="D88" s="20" t="inlineStr">
+      <c r="D88" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453636185/</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="18" t="inlineStr">
+      <c r="A89" s="21" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B89" s="19" t="n">
+      <c r="B89" s="22" t="n">
         <v>46267</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -2303,19 +2312,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D89" s="20" t="inlineStr">
+      <c r="D89" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453092177/</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="18" t="inlineStr">
+      <c r="A90" s="21" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B90" s="19" t="n">
+      <c r="B90" s="22" t="n">
         <v>46269</v>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -2323,19 +2332,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D90" s="20" t="inlineStr">
+      <c r="D90" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463637144/</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="18" t="inlineStr">
+      <c r="A91" s="21" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B91" s="19" t="n">
+      <c r="B91" s="22" t="n">
         <v>46266</v>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -2343,7 +2352,7 @@
           <t>Sr. Systems Engineer</t>
         </is>
       </c>
-      <c r="D91" s="20" t="inlineStr">
+      <c r="D91" s="23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461756319/</t>
         </is>
@@ -2369,8 +2378,368 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B93" s="25" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Senior Staff Mechanical Engineer - Characterization Lead</t>
+        </is>
+      </c>
+      <c r="D93" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4427645063/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="24" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B94" s="25" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>QA Engineer 2</t>
+        </is>
+      </c>
+      <c r="D94" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464097498/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="24" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B95" s="25" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Software Development Engineer 2</t>
+        </is>
+      </c>
+      <c r="D95" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453360435/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="24" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B96" s="25" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="D96" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453371096/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B97" s="25" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>Sr SW Development Engineer</t>
+        </is>
+      </c>
+      <c r="D97" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463626373/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="24" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B98" s="25" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>Senior Forecasting Analyst</t>
+        </is>
+      </c>
+      <c r="D98" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463633190/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="24" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B99" s="25" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Senior Forecasting Analyst</t>
+        </is>
+      </c>
+      <c r="D99" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463628391/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="24" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B100" s="25" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Sr IT Project Manager</t>
+        </is>
+      </c>
+      <c r="D100" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436188818/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="24" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B101" s="25" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
+        </is>
+      </c>
+      <c r="D101" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453075275/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B102" s="25" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>Sr Software QA Engineer</t>
+        </is>
+      </c>
+      <c r="D102" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463370785/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B103" s="25" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Material Handler 1 ( RDC ) - Days 1A and 1B</t>
+        </is>
+      </c>
+      <c r="D103" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455128356/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="24" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="B104" s="25" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>Territory Sales Manager - Brussels (Bilingual Flemish &amp; French)</t>
+        </is>
+      </c>
+      <c r="D104" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453090144/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="24" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B105" s="25" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>Systems Engineer 2</t>
+        </is>
+      </c>
+      <c r="D105" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461767088/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="24" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="B106" s="25" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>Territory Sales Manager - Brussels (Bilingual Flemish &amp; French)</t>
+        </is>
+      </c>
+      <c r="D106" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453073289/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="24" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B107" s="25" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
+        </is>
+      </c>
+      <c r="D107" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453083196/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B108" s="25" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>Principal Firmware Architect</t>
+        </is>
+      </c>
+      <c r="D108" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463626391/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B109" s="25" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>Software Development Engineer 1</t>
+        </is>
+      </c>
+      <c r="D109" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4454097524/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B110" s="25" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>Sr Staff Endpoint Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D110" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453090143/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D92"/>
+  <autoFilter ref="A1:D110"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -2463,6 +2832,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId109"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -559,12 +559,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B2" s="22" t="n">
+      <c r="B2" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -572,19 +572,19 @@
           <t>Sr Project Lead - APAC</t>
         </is>
       </c>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="D2" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461543326/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B3" s="22" t="n">
+      <c r="B3" s="25" t="n">
         <v>46262</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -592,19 +592,19 @@
           <t>SW Development Engineer 2</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460357219/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B4" s="22" t="n">
+      <c r="B4" s="25" t="n">
         <v>46267</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -612,19 +612,19 @@
           <t>Intelligence Analyst</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453085191/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -632,19 +632,19 @@
           <t>Senior Manager Corporate Compliance - EMEA (m/w/d)</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461752409/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="25" t="n">
         <v>46262</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -652,19 +652,19 @@
           <t>Customer Service Representative - French Speaker</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460500502/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="25" t="n">
         <v>46265</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -672,19 +672,19 @@
           <t>Staff Program Manager</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451501447/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="n">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -692,19 +692,19 @@
           <t>Lead Legal Counsel - Employment</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4430864197/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="25" t="n">
         <v>46262</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -712,19 +712,19 @@
           <t>Sr Manager, Software Systems &amp; Solutions</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4218028502/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B10" s="22" t="n">
+      <c r="B10" s="25" t="n">
         <v>46262</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -732,19 +732,19 @@
           <t>Manager SW Test Development Engineering</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4281993770/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="25" t="n">
         <v>46263</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -752,19 +752,19 @@
           <t>Security and Privacy Compliance Analyst - Cybersecurity</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4257269392/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -772,19 +772,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461768038/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="n">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -792,19 +792,19 @@
           <t>Mechanical Engineer 2</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462032756/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n">
+      <c r="B14" s="25" t="n">
         <v>46263</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -812,19 +812,19 @@
           <t>Supervisor Customer Advocacy</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442102156/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="n">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="n">
         <v>46267</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -832,19 +832,19 @@
           <t>Senior Staff Process Development Engineer</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443563067/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="n">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -852,19 +852,19 @@
           <t>Staff Process Engineer</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461543337/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="n">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B17" s="25" t="n">
         <v>46262</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -872,19 +872,19 @@
           <t>Sr QA Engineer</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460398658/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="n">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B18" s="25" t="n">
         <v>46268</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -892,19 +892,19 @@
           <t>Senior Director, Lean</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462725850/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B19" s="22" t="n">
+      <c r="B19" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -912,19 +912,19 @@
           <t>Benefits Analyst</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461581171/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="25" t="n">
         <v>46262</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -932,19 +932,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458914791/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B21" s="22" t="n">
+      <c r="B21" s="25" t="n">
         <v>46262</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -952,19 +952,19 @@
           <t>Financial Analyst</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441984900/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B22" s="22" t="n">
+      <c r="B22" s="25" t="n">
         <v>46267</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -972,19 +972,19 @@
           <t>Intelligence Analyst</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082218/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n">
+      <c r="B23" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -992,19 +992,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765127/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B24" s="22" t="n">
+      <c r="B24" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1012,19 +1012,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461754390/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B25" s="22" t="n">
+      <c r="B25" s="25" t="n">
         <v>46262</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1032,19 +1032,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458902988/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B26" s="22" t="n">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="n">
         <v>46263</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1052,19 +1052,19 @@
           <t>Benefits Manager (Americas)</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450760638/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="A27" s="24" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B27" s="22" t="n">
+      <c r="B27" s="25" t="n">
         <v>46265</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1072,19 +1072,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451545592/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B28" s="22" t="n">
+      <c r="B28" s="25" t="n">
         <v>46267</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1092,19 +1092,19 @@
           <t>Sr Process Engineer</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D28" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435122348/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="21" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B29" s="22" t="n">
+      <c r="B29" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1112,19 +1112,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="D29" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461772012/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B30" s="22" t="n">
+      <c r="B30" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1132,19 +1132,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D30" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765131/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n">
+      <c r="B31" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1152,19 +1152,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="D31" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461762151/</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B32" s="22" t="n">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="n">
         <v>46265</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1172,19 +1172,19 @@
           <t>New Business Development Manager (Senior Analyst, Strategic Finance )</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D32" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434090087/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B33" s="22" t="n">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1192,19 +1192,19 @@
           <t>Sr Manager - Sensor Automation</t>
         </is>
       </c>
-      <c r="D33" s="23" t="inlineStr">
+      <c r="D33" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461540445/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B34" s="22" t="n">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="n">
         <v>46265</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1212,19 +1212,19 @@
           <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="D34" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461264820/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="21" t="inlineStr">
+      <c r="A35" s="24" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B35" s="22" t="n">
+      <c r="B35" s="25" t="n">
         <v>46267</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1232,19 +1232,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D35" s="23" t="inlineStr">
+      <c r="D35" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453096131/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B36" s="22" t="n">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="n">
         <v>46262</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1252,19 +1252,19 @@
           <t>Sr SW Design Quality Engineer</t>
         </is>
       </c>
-      <c r="D36" s="23" t="inlineStr">
+      <c r="D36" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450008915/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="21" t="inlineStr">
+      <c r="A37" s="24" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B37" s="22" t="n">
+      <c r="B37" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1272,19 +1272,19 @@
           <t>Engineering Technician 4</t>
         </is>
       </c>
-      <c r="D37" s="23" t="inlineStr">
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461760270/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B38" s="22" t="n">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B38" s="25" t="n">
         <v>46265</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1292,19 +1292,19 @@
           <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
-      <c r="D38" s="23" t="inlineStr">
+      <c r="D38" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461275610/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B39" s="22" t="n">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B39" s="25" t="n">
         <v>46265</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1312,19 +1312,19 @@
           <t>Associate Customer Insights Manager</t>
         </is>
       </c>
-      <c r="D39" s="23" t="inlineStr">
+      <c r="D39" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434083415/</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B40" s="22" t="n">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B40" s="25" t="n">
         <v>46262</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1332,19 +1332,19 @@
           <t>Staff SW QA Engineer</t>
         </is>
       </c>
-      <c r="D40" s="23" t="inlineStr">
+      <c r="D40" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450025503/</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B41" s="22" t="n">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="n">
         <v>46267</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1352,19 +1352,19 @@
           <t>Lead Corporate Development Manager</t>
         </is>
       </c>
-      <c r="D41" s="23" t="inlineStr">
+      <c r="D41" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462460922/</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="21" t="inlineStr">
+      <c r="A42" s="24" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B42" s="22" t="n">
+      <c r="B42" s="25" t="n">
         <v>46264</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1372,19 +1372,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D42" s="23" t="inlineStr">
+      <c r="D42" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442446290/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B43" s="22" t="n">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="n">
         <v>46265</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1392,19 +1392,19 @@
           <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
-      <c r="D43" s="23" t="inlineStr">
+      <c r="D43" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461277558/</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="21" t="inlineStr">
+      <c r="A44" s="24" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B44" s="22" t="n">
+      <c r="B44" s="25" t="n">
         <v>46267</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1412,19 +1412,19 @@
           <t>Accountant - Healthcare - Edinburgh</t>
         </is>
       </c>
-      <c r="D44" s="23" t="inlineStr">
+      <c r="D44" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453144035/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="21" t="inlineStr">
+      <c r="A45" s="24" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B45" s="22" t="n">
+      <c r="B45" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1432,19 +1432,19 @@
           <t>Staff Systems Engineer</t>
         </is>
       </c>
-      <c r="D45" s="23" t="inlineStr">
+      <c r="D45" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461770016/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B46" s="22" t="n">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B46" s="25" t="n">
         <v>46268</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1452,19 +1452,19 @@
           <t>Staff Quality Compliance Specialist</t>
         </is>
       </c>
-      <c r="D46" s="23" t="inlineStr">
+      <c r="D46" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462730823/</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="21" t="inlineStr">
+      <c r="A47" s="24" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="B47" s="22" t="n">
+      <c r="B47" s="25" t="n">
         <v>46267</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1472,19 +1472,19 @@
           <t>Territory Sales Manager (m/w/d) - Zentralschweiz : Luzern, Obwalden, Nidwalden, Uri, Chur</t>
         </is>
       </c>
-      <c r="D47" s="23" t="inlineStr">
+      <c r="D47" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453133160/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B48" s="22" t="n">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B48" s="25" t="n">
         <v>46262</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1492,19 +1492,19 @@
           <t>Staff Planner</t>
         </is>
       </c>
-      <c r="D48" s="23" t="inlineStr">
+      <c r="D48" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450636243/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B49" s="22" t="n">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B49" s="25" t="n">
         <v>46267</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1512,19 +1512,19 @@
           <t>Territory Business Manager - Morristown, New Jersey</t>
         </is>
       </c>
-      <c r="D49" s="23" t="inlineStr">
+      <c r="D49" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4452316210/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B50" s="22" t="n">
+      <c r="A50" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B50" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1532,19 +1532,19 @@
           <t>Sr Manager Medical Affairs</t>
         </is>
       </c>
-      <c r="D50" s="23" t="inlineStr">
+      <c r="D50" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461536483/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B51" s="22" t="n">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B51" s="25" t="n">
         <v>46263</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1552,19 +1552,19 @@
           <t>Capital Planning &amp; Analytics Manager</t>
         </is>
       </c>
-      <c r="D51" s="23" t="inlineStr">
+      <c r="D51" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450775200/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B52" s="22" t="n">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B52" s="25" t="n">
         <v>46263</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -1572,19 +1572,19 @@
           <t>Supervisor, Manufacturing</t>
         </is>
       </c>
-      <c r="D52" s="23" t="inlineStr">
+      <c r="D52" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460573058/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B53" s="22" t="n">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B53" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1592,19 +1592,19 @@
           <t>Territory Business Manager - Anchorage, AK</t>
         </is>
       </c>
-      <c r="D53" s="23" t="inlineStr">
+      <c r="D53" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462041571/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B54" s="22" t="n">
+      <c r="A54" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B54" s="25" t="n">
         <v>46268</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1612,19 +1612,19 @@
           <t>QC Inspector 4 - 1B Thur-Sat, every other Wednesday from 5am-5pm</t>
         </is>
       </c>
-      <c r="D54" s="23" t="inlineStr">
+      <c r="D54" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462726839/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="21" t="inlineStr">
+      <c r="A55" s="24" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B55" s="22" t="n">
+      <c r="B55" s="25" t="n">
         <v>46267</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1632,19 +1632,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D55" s="23" t="inlineStr">
+      <c r="D55" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097086/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="21" t="inlineStr">
+      <c r="A56" s="24" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B56" s="22" t="n">
+      <c r="B56" s="25" t="n">
         <v>46267</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1652,19 +1652,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D56" s="23" t="inlineStr">
+      <c r="D56" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453076276/</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="21" t="inlineStr">
+      <c r="A57" s="24" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B57" s="22" t="n">
+      <c r="B57" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1672,19 +1672,19 @@
           <t>Territory Business Manager - Ottawa</t>
         </is>
       </c>
-      <c r="D57" s="23" t="inlineStr">
+      <c r="D57" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462038604/</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="21" t="inlineStr">
+      <c r="A58" s="24" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B58" s="22" t="n">
+      <c r="B58" s="25" t="n">
         <v>46267</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1692,19 +1692,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D58" s="23" t="inlineStr">
+      <c r="D58" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453087192/</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B59" s="22" t="n">
+      <c r="A59" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B59" s="25" t="n">
         <v>46267</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1712,19 +1712,19 @@
           <t>Manufacturing Technician 3-1B Thursday-Saturday every other Wednesday(5AM-5PM)</t>
         </is>
       </c>
-      <c r="D59" s="23" t="inlineStr">
+      <c r="D59" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460900071/</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B60" s="22" t="n">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B60" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1732,19 +1732,19 @@
           <t>Equipment Technician 2-1A Sunday-Tuesday every other Wednesday(5AM-5PM)</t>
         </is>
       </c>
-      <c r="D60" s="23" t="inlineStr">
+      <c r="D60" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461550206/</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="21" t="inlineStr">
+      <c r="A61" s="24" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B61" s="22" t="n">
+      <c r="B61" s="25" t="n">
         <v>46267</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1752,19 +1752,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D61" s="23" t="inlineStr">
+      <c r="D61" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453078274/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="21" t="inlineStr">
+      <c r="A62" s="24" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B62" s="22" t="n">
+      <c r="B62" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1772,19 +1772,19 @@
           <t>Staff Veeva and Master Data Analyst</t>
         </is>
       </c>
-      <c r="D62" s="23" t="inlineStr">
+      <c r="D62" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461758265/</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B63" s="22" t="n">
+      <c r="A63" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B63" s="25" t="n">
         <v>46268</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1792,19 +1792,19 @@
           <t>Platform Security Engineer 2</t>
         </is>
       </c>
-      <c r="D63" s="23" t="inlineStr">
+      <c r="D63" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462736772/</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="21" t="inlineStr">
+      <c r="A64" s="24" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B64" s="22" t="n">
+      <c r="B64" s="25" t="n">
         <v>46268</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1812,19 +1812,19 @@
           <t>APAC FP&amp;A Manager</t>
         </is>
       </c>
-      <c r="D64" s="23" t="inlineStr">
+      <c r="D64" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462770899/</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="21" t="inlineStr">
+      <c r="A65" s="24" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B65" s="22" t="n">
+      <c r="B65" s="25" t="n">
         <v>46268</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1832,19 +1832,19 @@
           <t>Commercial Analytics &amp; Operations Associate</t>
         </is>
       </c>
-      <c r="D65" s="23" t="inlineStr">
+      <c r="D65" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462778751/</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B66" s="22" t="n">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B66" s="25" t="n">
         <v>46269</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1852,19 +1852,19 @@
           <t>Document Control and Training Specialist 1</t>
         </is>
       </c>
-      <c r="D66" s="23" t="inlineStr">
+      <c r="D66" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463157831/</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="21" t="inlineStr">
+      <c r="A67" s="24" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B67" s="22" t="n">
+      <c r="B67" s="25" t="n">
         <v>46269</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1872,19 +1872,19 @@
           <t>Sr Supply Chain Analyst</t>
         </is>
       </c>
-      <c r="D67" s="23" t="inlineStr">
+      <c r="D67" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463169639/</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="21" t="inlineStr">
+      <c r="A68" s="24" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B68" s="22" t="n">
+      <c r="B68" s="25" t="n">
         <v>46269</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1892,19 +1892,19 @@
           <t>IT Procurement Analyst</t>
         </is>
       </c>
-      <c r="D68" s="23" t="inlineStr">
+      <c r="D68" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463313428/</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="21" t="inlineStr">
+      <c r="A69" s="24" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B69" s="22" t="n">
+      <c r="B69" s="25" t="n">
         <v>46269</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1912,19 +1912,19 @@
           <t>IT Procurement Analyst</t>
         </is>
       </c>
-      <c r="D69" s="23" t="inlineStr">
+      <c r="D69" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463314400/</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B70" s="22" t="n">
+      <c r="A70" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B70" s="25" t="n">
         <v>46268</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1932,19 +1932,19 @@
           <t>Product Manager, Patient Onboarding &amp; First Value</t>
         </is>
       </c>
-      <c r="D70" s="23" t="inlineStr">
+      <c r="D70" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453357502/</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B71" s="22" t="n">
+      <c r="A71" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B71" s="25" t="n">
         <v>46270</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1952,19 +1952,19 @@
           <t>Staff Technical Program Manager - Innovation Ventures &amp; Sensor Technology</t>
         </is>
       </c>
-      <c r="D71" s="23" t="inlineStr">
+      <c r="D71" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454853005/</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B72" s="22" t="n">
+      <c r="A72" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B72" s="25" t="n">
         <v>46270</v>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -1972,19 +1972,19 @@
           <t>Project Manager 2</t>
         </is>
       </c>
-      <c r="D72" s="23" t="inlineStr">
+      <c r="D72" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463687671/</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B73" s="22" t="n">
+      <c r="A73" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B73" s="25" t="n">
         <v>46269</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -1992,19 +1992,19 @@
           <t>Senior Medical Affairs Manager – Value, Evidence, and Outcomes</t>
         </is>
       </c>
-      <c r="D73" s="23" t="inlineStr">
+      <c r="D73" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443448275/</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B74" s="22" t="n">
+      <c r="A74" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B74" s="25" t="n">
         <v>46268</v>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -2012,19 +2012,19 @@
           <t>Director of Sensor Research</t>
         </is>
       </c>
-      <c r="D74" s="23" t="inlineStr">
+      <c r="D74" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427088373/</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B75" s="22" t="n">
+      <c r="A75" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B75" s="25" t="n">
         <v>46271</v>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -2032,19 +2032,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D75" s="23" t="inlineStr">
+      <c r="D75" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436409441/</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="21" t="inlineStr">
+      <c r="A76" s="24" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B76" s="22" t="n">
+      <c r="B76" s="25" t="n">
         <v>46270</v>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -2052,19 +2052,19 @@
           <t>Distributor Manager - Channel Excellence (MedTech)</t>
         </is>
       </c>
-      <c r="D76" s="23" t="inlineStr">
+      <c r="D76" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463683762/</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B77" s="22" t="n">
+      <c r="A77" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B77" s="25" t="n">
         <v>46268</v>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -2072,19 +2072,19 @@
           <t>Territory Business Manager - Erie Pennsylvania</t>
         </is>
       </c>
-      <c r="D77" s="23" t="inlineStr">
+      <c r="D77" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440304526/</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B78" s="22" t="n">
+      <c r="A78" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B78" s="25" t="n">
         <v>46270</v>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -2092,19 +2092,19 @@
           <t>QA Inspector 2 ( Dobson ) - 1A Sun- Tues, every other Wednesday, Can work anytime from 5am-5pm</t>
         </is>
       </c>
-      <c r="D78" s="23" t="inlineStr">
+      <c r="D78" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463691655/</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="21" t="inlineStr">
+      <c r="A79" s="24" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B79" s="22" t="n">
+      <c r="B79" s="25" t="n">
         <v>46270</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -2112,19 +2112,19 @@
           <t>Distributor Manager - Channel Excellence (MedTech)</t>
         </is>
       </c>
-      <c r="D79" s="23" t="inlineStr">
+      <c r="D79" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463684766/</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B80" s="22" t="n">
+      <c r="A80" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B80" s="25" t="n">
         <v>46269</v>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -2132,19 +2132,19 @@
           <t>Sr. Clinical Customer Advocate</t>
         </is>
       </c>
-      <c r="D80" s="23" t="inlineStr">
+      <c r="D80" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463625584/</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B81" s="22" t="n">
+      <c r="A81" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B81" s="25" t="n">
         <v>46268</v>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2152,19 +2152,19 @@
           <t>Staff Data Scientist</t>
         </is>
       </c>
-      <c r="D81" s="23" t="inlineStr">
+      <c r="D81" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463110275/</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="21" t="inlineStr">
+      <c r="A82" s="24" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B82" s="22" t="n">
+      <c r="B82" s="25" t="n">
         <v>46269</v>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -2172,19 +2172,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D82" s="23" t="inlineStr">
+      <c r="D82" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463622979/</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="21" t="inlineStr">
+      <c r="A83" s="24" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B83" s="22" t="n">
+      <c r="B83" s="25" t="n">
         <v>46268</v>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2192,19 +2192,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Bracknell, UK</t>
         </is>
       </c>
-      <c r="D83" s="23" t="inlineStr">
+      <c r="D83" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462849233/</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B84" s="22" t="n">
+      <c r="A84" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B84" s="25" t="n">
         <v>46270</v>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -2212,19 +2212,19 @@
           <t>Hardware Engineer 2</t>
         </is>
       </c>
-      <c r="D84" s="23" t="inlineStr">
+      <c r="D84" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454834815/</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B85" s="22" t="n">
+      <c r="A85" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B85" s="25" t="n">
         <v>46268</v>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2232,19 +2232,19 @@
           <t>Principal SW Development Engineer</t>
         </is>
       </c>
-      <c r="D85" s="23" t="inlineStr">
+      <c r="D85" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453345730/</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="21" t="inlineStr">
+      <c r="A86" s="24" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B86" s="22" t="n">
+      <c r="B86" s="25" t="n">
         <v>46269</v>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -2252,19 +2252,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D86" s="23" t="inlineStr">
+      <c r="D86" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463634192/</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B87" s="22" t="n">
+      <c r="A87" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B87" s="25" t="n">
         <v>46270</v>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -2272,19 +2272,19 @@
           <t>Associate Customer Experience Manager</t>
         </is>
       </c>
-      <c r="D87" s="23" t="inlineStr">
+      <c r="D87" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454599227/</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B88" s="22" t="n">
+      <c r="A88" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B88" s="25" t="n">
         <v>46268</v>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -2292,19 +2292,19 @@
           <t>Sr Software QA Engineer</t>
         </is>
       </c>
-      <c r="D88" s="23" t="inlineStr">
+      <c r="D88" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453636185/</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="21" t="inlineStr">
+      <c r="A89" s="24" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B89" s="22" t="n">
+      <c r="B89" s="25" t="n">
         <v>46267</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -2312,19 +2312,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D89" s="23" t="inlineStr">
+      <c r="D89" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453092177/</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="21" t="inlineStr">
+      <c r="A90" s="24" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B90" s="22" t="n">
+      <c r="B90" s="25" t="n">
         <v>46269</v>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -2332,19 +2332,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D90" s="23" t="inlineStr">
+      <c r="D90" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463637144/</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="21" t="inlineStr">
+      <c r="A91" s="24" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B91" s="22" t="n">
+      <c r="B91" s="25" t="n">
         <v>46266</v>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -2352,19 +2352,19 @@
           <t>Sr. Systems Engineer</t>
         </is>
       </c>
-      <c r="D91" s="23" t="inlineStr">
+      <c r="D91" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461756319/</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="21" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B92" s="22" t="n">
+      <c r="A92" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B92" s="25" t="n">
         <v>46269</v>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -2372,7 +2372,7 @@
           <t>Senior SW Development Engineer</t>
         </is>
       </c>
-      <c r="D92" s="23" t="inlineStr">
+      <c r="D92" s="26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454303425/</t>
         </is>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$120</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -527,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D110"/>
+  <dimension ref="A1:D120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2738,8 +2747,208 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="27" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B111" s="28" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Supervisor Customer Advocacy</t>
+        </is>
+      </c>
+      <c r="D111" s="29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4454022788/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="27" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B112" s="28" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Customer Service Representative (German-speaking)</t>
+        </is>
+      </c>
+      <c r="D112" s="29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463120173/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="27" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B113" s="28" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>Sr Cybersecurity Analyst - GRC</t>
+        </is>
+      </c>
+      <c r="D113" s="29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4454019825/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="27" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B114" s="28" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>Customer Service Representative, French Speaker</t>
+        </is>
+      </c>
+      <c r="D114" s="29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4462772822/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="27" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B115" s="28" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>Intelligence Analyst - Geopolitical</t>
+        </is>
+      </c>
+      <c r="D115" s="29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444046742/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="27" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B116" s="28" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>GBS Engagement &amp; Service Management Lead</t>
+        </is>
+      </c>
+      <c r="D116" s="29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4427554137/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="27" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B117" s="28" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>Contact Center Platform Analyst</t>
+        </is>
+      </c>
+      <c r="D117" s="29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4462857053/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="27" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B118" s="28" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>Program Manager - AI Initiatives</t>
+        </is>
+      </c>
+      <c r="D118" s="29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4435119512/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="27" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B119" s="28" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>Staff Cybersecurity Engineer (SecOps)</t>
+        </is>
+      </c>
+      <c r="D119" s="29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4452459722/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="27" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B120" s="28" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>Senior Telecom Engineer (Genesys Cloud)</t>
+        </is>
+      </c>
+      <c r="D120" s="29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463370784/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D110"/>
+  <autoFilter ref="A1:D120"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -2850,6 +3059,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId119"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$135</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -536,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -568,12 +577,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n">
+      <c r="B2" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -581,19 +590,19 @@
           <t>Sr Project Lead - APAC</t>
         </is>
       </c>
-      <c r="D2" s="26" t="inlineStr">
+      <c r="D2" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461543326/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B3" s="25" t="n">
+      <c r="B3" s="28" t="n">
         <v>46262</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -601,19 +610,19 @@
           <t>SW Development Engineer 2</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460357219/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B4" s="25" t="n">
+      <c r="B4" s="28" t="n">
         <v>46267</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -621,19 +630,19 @@
           <t>Intelligence Analyst</t>
         </is>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453085191/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -641,19 +650,19 @@
           <t>Senior Manager Corporate Compliance - EMEA (m/w/d)</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461752409/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="28" t="n">
         <v>46262</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -661,19 +670,19 @@
           <t>Customer Service Representative - French Speaker</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460500502/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="28" t="n">
         <v>46265</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -681,19 +690,19 @@
           <t>Staff Program Manager</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451501447/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B8" s="25" t="n">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -701,19 +710,19 @@
           <t>Lead Legal Counsel - Employment</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4430864197/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="28" t="n">
         <v>46262</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -721,19 +730,19 @@
           <t>Sr Manager, Software Systems &amp; Solutions</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4218028502/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B10" s="25" t="n">
+      <c r="B10" s="28" t="n">
         <v>46262</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -741,19 +750,19 @@
           <t>Manager SW Test Development Engineering</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4281993770/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B11" s="25" t="n">
+      <c r="B11" s="28" t="n">
         <v>46263</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -761,19 +770,19 @@
           <t>Security and Privacy Compliance Analyst - Cybersecurity</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4257269392/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n">
+      <c r="B12" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -781,19 +790,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461768038/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B13" s="25" t="n">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -801,19 +810,19 @@
           <t>Mechanical Engineer 2</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462032756/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="28" t="n">
         <v>46263</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -821,19 +830,19 @@
           <t>Supervisor Customer Advocacy</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442102156/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B15" s="25" t="n">
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="n">
         <v>46267</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -841,19 +850,19 @@
           <t>Senior Staff Process Development Engineer</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443563067/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B16" s="25" t="n">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -861,19 +870,19 @@
           <t>Staff Process Engineer</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461543337/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B17" s="25" t="n">
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B17" s="28" t="n">
         <v>46262</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -881,19 +890,19 @@
           <t>Sr QA Engineer</t>
         </is>
       </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460398658/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B18" s="25" t="n">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="n">
         <v>46268</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -901,19 +910,19 @@
           <t>Senior Director, Lean</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462725850/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B19" s="25" t="n">
+      <c r="B19" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -921,19 +930,19 @@
           <t>Benefits Analyst</t>
         </is>
       </c>
-      <c r="D19" s="26" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461581171/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B20" s="25" t="n">
+      <c r="B20" s="28" t="n">
         <v>46262</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -941,19 +950,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458914791/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B21" s="25" t="n">
+      <c r="B21" s="28" t="n">
         <v>46262</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -961,19 +970,19 @@
           <t>Financial Analyst</t>
         </is>
       </c>
-      <c r="D21" s="26" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441984900/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B22" s="25" t="n">
+      <c r="B22" s="28" t="n">
         <v>46267</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -981,19 +990,19 @@
           <t>Intelligence Analyst</t>
         </is>
       </c>
-      <c r="D22" s="26" t="inlineStr">
+      <c r="D22" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082218/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B23" s="25" t="n">
+      <c r="B23" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1001,19 +1010,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D23" s="26" t="inlineStr">
+      <c r="D23" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765127/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B24" s="25" t="n">
+      <c r="B24" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1021,19 +1030,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D24" s="26" t="inlineStr">
+      <c r="D24" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461754390/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B25" s="25" t="n">
+      <c r="B25" s="28" t="n">
         <v>46262</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1041,19 +1050,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D25" s="26" t="inlineStr">
+      <c r="D25" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458902988/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B26" s="25" t="n">
+      <c r="A26" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B26" s="28" t="n">
         <v>46263</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1061,19 +1070,19 @@
           <t>Benefits Manager (Americas)</t>
         </is>
       </c>
-      <c r="D26" s="26" t="inlineStr">
+      <c r="D26" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450760638/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B27" s="25" t="n">
+      <c r="B27" s="28" t="n">
         <v>46265</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1081,19 +1090,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D27" s="26" t="inlineStr">
+      <c r="D27" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451545592/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B28" s="25" t="n">
+      <c r="B28" s="28" t="n">
         <v>46267</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1101,19 +1110,19 @@
           <t>Sr Process Engineer</t>
         </is>
       </c>
-      <c r="D28" s="26" t="inlineStr">
+      <c r="D28" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435122348/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B29" s="25" t="n">
+      <c r="B29" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1121,19 +1130,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D29" s="26" t="inlineStr">
+      <c r="D29" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461772012/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B30" s="25" t="n">
+      <c r="B30" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1141,19 +1150,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D30" s="26" t="inlineStr">
+      <c r="D30" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765131/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B31" s="25" t="n">
+      <c r="B31" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1161,19 +1170,19 @@
           <t>Territory Sales Manager - Castilla y León</t>
         </is>
       </c>
-      <c r="D31" s="26" t="inlineStr">
+      <c r="D31" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461762151/</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B32" s="25" t="n">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B32" s="28" t="n">
         <v>46265</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1181,19 +1190,19 @@
           <t>New Business Development Manager (Senior Analyst, Strategic Finance )</t>
         </is>
       </c>
-      <c r="D32" s="26" t="inlineStr">
+      <c r="D32" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434090087/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B33" s="25" t="n">
+      <c r="A33" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1201,19 +1210,19 @@
           <t>Sr Manager - Sensor Automation</t>
         </is>
       </c>
-      <c r="D33" s="26" t="inlineStr">
+      <c r="D33" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461540445/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B34" s="25" t="n">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B34" s="28" t="n">
         <v>46265</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1221,19 +1230,19 @@
           <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
-      <c r="D34" s="26" t="inlineStr">
+      <c r="D34" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461264820/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24" t="inlineStr">
+      <c r="A35" s="27" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B35" s="25" t="n">
+      <c r="B35" s="28" t="n">
         <v>46267</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1241,19 +1250,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D35" s="26" t="inlineStr">
+      <c r="D35" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453096131/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B36" s="25" t="n">
+      <c r="A36" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B36" s="28" t="n">
         <v>46262</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1261,19 +1270,19 @@
           <t>Sr SW Design Quality Engineer</t>
         </is>
       </c>
-      <c r="D36" s="26" t="inlineStr">
+      <c r="D36" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450008915/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="24" t="inlineStr">
+      <c r="A37" s="27" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B37" s="25" t="n">
+      <c r="B37" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1281,19 +1290,19 @@
           <t>Engineering Technician 4</t>
         </is>
       </c>
-      <c r="D37" s="26" t="inlineStr">
+      <c r="D37" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461760270/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B38" s="25" t="n">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B38" s="28" t="n">
         <v>46265</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1301,19 +1310,19 @@
           <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
-      <c r="D38" s="26" t="inlineStr">
+      <c r="D38" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461275610/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B39" s="25" t="n">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B39" s="28" t="n">
         <v>46265</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1321,19 +1330,19 @@
           <t>Associate Customer Insights Manager</t>
         </is>
       </c>
-      <c r="D39" s="26" t="inlineStr">
+      <c r="D39" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434083415/</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B40" s="25" t="n">
+      <c r="A40" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B40" s="28" t="n">
         <v>46262</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1341,19 +1350,19 @@
           <t>Staff SW QA Engineer</t>
         </is>
       </c>
-      <c r="D40" s="26" t="inlineStr">
+      <c r="D40" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450025503/</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B41" s="25" t="n">
+      <c r="A41" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B41" s="28" t="n">
         <v>46267</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1361,19 +1370,19 @@
           <t>Lead Corporate Development Manager</t>
         </is>
       </c>
-      <c r="D41" s="26" t="inlineStr">
+      <c r="D41" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462460922/</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="A42" s="27" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B42" s="25" t="n">
+      <c r="B42" s="28" t="n">
         <v>46264</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1381,19 +1390,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D42" s="26" t="inlineStr">
+      <c r="D42" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442446290/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B43" s="25" t="n">
+      <c r="A43" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B43" s="28" t="n">
         <v>46265</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1401,19 +1410,19 @@
           <t>Staff Business Financial Analyst - IT Infrastructure</t>
         </is>
       </c>
-      <c r="D43" s="26" t="inlineStr">
+      <c r="D43" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461277558/</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="24" t="inlineStr">
+      <c r="A44" s="27" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B44" s="25" t="n">
+      <c r="B44" s="28" t="n">
         <v>46267</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1421,19 +1430,19 @@
           <t>Accountant - Healthcare - Edinburgh</t>
         </is>
       </c>
-      <c r="D44" s="26" t="inlineStr">
+      <c r="D44" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453144035/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="24" t="inlineStr">
+      <c r="A45" s="27" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B45" s="25" t="n">
+      <c r="B45" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1441,19 +1450,19 @@
           <t>Staff Systems Engineer</t>
         </is>
       </c>
-      <c r="D45" s="26" t="inlineStr">
+      <c r="D45" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461770016/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B46" s="25" t="n">
+      <c r="A46" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B46" s="28" t="n">
         <v>46268</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1461,19 +1470,19 @@
           <t>Staff Quality Compliance Specialist</t>
         </is>
       </c>
-      <c r="D46" s="26" t="inlineStr">
+      <c r="D46" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462730823/</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="24" t="inlineStr">
+      <c r="A47" s="27" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="B47" s="25" t="n">
+      <c r="B47" s="28" t="n">
         <v>46267</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1481,19 +1490,19 @@
           <t>Territory Sales Manager (m/w/d) - Zentralschweiz : Luzern, Obwalden, Nidwalden, Uri, Chur</t>
         </is>
       </c>
-      <c r="D47" s="26" t="inlineStr">
+      <c r="D47" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453133160/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B48" s="25" t="n">
+      <c r="A48" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B48" s="28" t="n">
         <v>46262</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1501,19 +1510,19 @@
           <t>Staff Planner</t>
         </is>
       </c>
-      <c r="D48" s="26" t="inlineStr">
+      <c r="D48" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450636243/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B49" s="25" t="n">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B49" s="28" t="n">
         <v>46267</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1521,19 +1530,19 @@
           <t>Territory Business Manager - Morristown, New Jersey</t>
         </is>
       </c>
-      <c r="D49" s="26" t="inlineStr">
+      <c r="D49" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4452316210/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B50" s="25" t="n">
+      <c r="A50" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B50" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1541,19 +1550,19 @@
           <t>Sr Manager Medical Affairs</t>
         </is>
       </c>
-      <c r="D50" s="26" t="inlineStr">
+      <c r="D50" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461536483/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B51" s="25" t="n">
+      <c r="A51" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B51" s="28" t="n">
         <v>46263</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1561,19 +1570,19 @@
           <t>Capital Planning &amp; Analytics Manager</t>
         </is>
       </c>
-      <c r="D51" s="26" t="inlineStr">
+      <c r="D51" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450775200/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B52" s="25" t="n">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B52" s="28" t="n">
         <v>46263</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -1581,19 +1590,19 @@
           <t>Supervisor, Manufacturing</t>
         </is>
       </c>
-      <c r="D52" s="26" t="inlineStr">
+      <c r="D52" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460573058/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B53" s="25" t="n">
+      <c r="A53" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B53" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1601,19 +1610,19 @@
           <t>Territory Business Manager - Anchorage, AK</t>
         </is>
       </c>
-      <c r="D53" s="26" t="inlineStr">
+      <c r="D53" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462041571/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B54" s="25" t="n">
+      <c r="A54" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B54" s="28" t="n">
         <v>46268</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1621,19 +1630,19 @@
           <t>QC Inspector 4 - 1B Thur-Sat, every other Wednesday from 5am-5pm</t>
         </is>
       </c>
-      <c r="D54" s="26" t="inlineStr">
+      <c r="D54" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462726839/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="24" t="inlineStr">
+      <c r="A55" s="27" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B55" s="25" t="n">
+      <c r="B55" s="28" t="n">
         <v>46267</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1641,19 +1650,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D55" s="26" t="inlineStr">
+      <c r="D55" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097086/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="24" t="inlineStr">
+      <c r="A56" s="27" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B56" s="25" t="n">
+      <c r="B56" s="28" t="n">
         <v>46267</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1661,19 +1670,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D56" s="26" t="inlineStr">
+      <c r="D56" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453076276/</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="24" t="inlineStr">
+      <c r="A57" s="27" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B57" s="25" t="n">
+      <c r="B57" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1681,19 +1690,19 @@
           <t>Territory Business Manager - Ottawa</t>
         </is>
       </c>
-      <c r="D57" s="26" t="inlineStr">
+      <c r="D57" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462038604/</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="24" t="inlineStr">
+      <c r="A58" s="27" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B58" s="25" t="n">
+      <c r="B58" s="28" t="n">
         <v>46267</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1701,19 +1710,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D58" s="26" t="inlineStr">
+      <c r="D58" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453087192/</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B59" s="25" t="n">
+      <c r="A59" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B59" s="28" t="n">
         <v>46267</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1721,19 +1730,19 @@
           <t>Manufacturing Technician 3-1B Thursday-Saturday every other Wednesday(5AM-5PM)</t>
         </is>
       </c>
-      <c r="D59" s="26" t="inlineStr">
+      <c r="D59" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460900071/</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B60" s="25" t="n">
+      <c r="A60" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B60" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1741,19 +1750,19 @@
           <t>Equipment Technician 2-1A Sunday-Tuesday every other Wednesday(5AM-5PM)</t>
         </is>
       </c>
-      <c r="D60" s="26" t="inlineStr">
+      <c r="D60" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461550206/</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="24" t="inlineStr">
+      <c r="A61" s="27" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B61" s="25" t="n">
+      <c r="B61" s="28" t="n">
         <v>46267</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1761,19 +1770,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D61" s="26" t="inlineStr">
+      <c r="D61" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453078274/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="24" t="inlineStr">
+      <c r="A62" s="27" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B62" s="25" t="n">
+      <c r="B62" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1781,19 +1790,19 @@
           <t>Staff Veeva and Master Data Analyst</t>
         </is>
       </c>
-      <c r="D62" s="26" t="inlineStr">
+      <c r="D62" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461758265/</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B63" s="25" t="n">
+      <c r="A63" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B63" s="28" t="n">
         <v>46268</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1801,19 +1810,19 @@
           <t>Platform Security Engineer 2</t>
         </is>
       </c>
-      <c r="D63" s="26" t="inlineStr">
+      <c r="D63" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462736772/</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="24" t="inlineStr">
+      <c r="A64" s="27" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B64" s="25" t="n">
+      <c r="B64" s="28" t="n">
         <v>46268</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1821,19 +1830,19 @@
           <t>APAC FP&amp;A Manager</t>
         </is>
       </c>
-      <c r="D64" s="26" t="inlineStr">
+      <c r="D64" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462770899/</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="24" t="inlineStr">
+      <c r="A65" s="27" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B65" s="25" t="n">
+      <c r="B65" s="28" t="n">
         <v>46268</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1841,19 +1850,19 @@
           <t>Commercial Analytics &amp; Operations Associate</t>
         </is>
       </c>
-      <c r="D65" s="26" t="inlineStr">
+      <c r="D65" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462778751/</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B66" s="25" t="n">
+      <c r="A66" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B66" s="28" t="n">
         <v>46269</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1861,19 +1870,19 @@
           <t>Document Control and Training Specialist 1</t>
         </is>
       </c>
-      <c r="D66" s="26" t="inlineStr">
+      <c r="D66" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463157831/</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="24" t="inlineStr">
+      <c r="A67" s="27" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B67" s="25" t="n">
+      <c r="B67" s="28" t="n">
         <v>46269</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1881,19 +1890,19 @@
           <t>Sr Supply Chain Analyst</t>
         </is>
       </c>
-      <c r="D67" s="26" t="inlineStr">
+      <c r="D67" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463169639/</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="24" t="inlineStr">
+      <c r="A68" s="27" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B68" s="25" t="n">
+      <c r="B68" s="28" t="n">
         <v>46269</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1901,19 +1910,19 @@
           <t>IT Procurement Analyst</t>
         </is>
       </c>
-      <c r="D68" s="26" t="inlineStr">
+      <c r="D68" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463313428/</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="24" t="inlineStr">
+      <c r="A69" s="27" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B69" s="25" t="n">
+      <c r="B69" s="28" t="n">
         <v>46269</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1921,19 +1930,19 @@
           <t>IT Procurement Analyst</t>
         </is>
       </c>
-      <c r="D69" s="26" t="inlineStr">
+      <c r="D69" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463314400/</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B70" s="25" t="n">
+      <c r="A70" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B70" s="28" t="n">
         <v>46268</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1941,19 +1950,19 @@
           <t>Product Manager, Patient Onboarding &amp; First Value</t>
         </is>
       </c>
-      <c r="D70" s="26" t="inlineStr">
+      <c r="D70" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453357502/</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B71" s="25" t="n">
+      <c r="A71" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B71" s="28" t="n">
         <v>46270</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1961,19 +1970,19 @@
           <t>Staff Technical Program Manager - Innovation Ventures &amp; Sensor Technology</t>
         </is>
       </c>
-      <c r="D71" s="26" t="inlineStr">
+      <c r="D71" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454853005/</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B72" s="25" t="n">
+      <c r="A72" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B72" s="28" t="n">
         <v>46270</v>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -1981,19 +1990,19 @@
           <t>Project Manager 2</t>
         </is>
       </c>
-      <c r="D72" s="26" t="inlineStr">
+      <c r="D72" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463687671/</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B73" s="25" t="n">
+      <c r="A73" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B73" s="28" t="n">
         <v>46269</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2001,19 +2010,19 @@
           <t>Senior Medical Affairs Manager – Value, Evidence, and Outcomes</t>
         </is>
       </c>
-      <c r="D73" s="26" t="inlineStr">
+      <c r="D73" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443448275/</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B74" s="25" t="n">
+      <c r="A74" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B74" s="28" t="n">
         <v>46268</v>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -2021,19 +2030,19 @@
           <t>Director of Sensor Research</t>
         </is>
       </c>
-      <c r="D74" s="26" t="inlineStr">
+      <c r="D74" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427088373/</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B75" s="25" t="n">
+      <c r="A75" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B75" s="28" t="n">
         <v>46271</v>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -2041,19 +2050,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D75" s="26" t="inlineStr">
+      <c r="D75" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436409441/</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="24" t="inlineStr">
+      <c r="A76" s="27" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B76" s="25" t="n">
+      <c r="B76" s="28" t="n">
         <v>46270</v>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -2061,19 +2070,19 @@
           <t>Distributor Manager - Channel Excellence (MedTech)</t>
         </is>
       </c>
-      <c r="D76" s="26" t="inlineStr">
+      <c r="D76" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463683762/</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B77" s="25" t="n">
+      <c r="A77" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B77" s="28" t="n">
         <v>46268</v>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -2081,19 +2090,19 @@
           <t>Territory Business Manager - Erie Pennsylvania</t>
         </is>
       </c>
-      <c r="D77" s="26" t="inlineStr">
+      <c r="D77" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440304526/</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B78" s="25" t="n">
+      <c r="A78" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B78" s="28" t="n">
         <v>46270</v>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -2101,19 +2110,19 @@
           <t>QA Inspector 2 ( Dobson ) - 1A Sun- Tues, every other Wednesday, Can work anytime from 5am-5pm</t>
         </is>
       </c>
-      <c r="D78" s="26" t="inlineStr">
+      <c r="D78" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463691655/</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="24" t="inlineStr">
+      <c r="A79" s="27" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B79" s="25" t="n">
+      <c r="B79" s="28" t="n">
         <v>46270</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -2121,19 +2130,19 @@
           <t>Distributor Manager - Channel Excellence (MedTech)</t>
         </is>
       </c>
-      <c r="D79" s="26" t="inlineStr">
+      <c r="D79" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463684766/</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B80" s="25" t="n">
+      <c r="A80" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B80" s="28" t="n">
         <v>46269</v>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -2141,19 +2150,19 @@
           <t>Sr. Clinical Customer Advocate</t>
         </is>
       </c>
-      <c r="D80" s="26" t="inlineStr">
+      <c r="D80" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463625584/</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B81" s="25" t="n">
+      <c r="A81" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B81" s="28" t="n">
         <v>46268</v>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2161,19 +2170,19 @@
           <t>Staff Data Scientist</t>
         </is>
       </c>
-      <c r="D81" s="26" t="inlineStr">
+      <c r="D81" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463110275/</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="24" t="inlineStr">
+      <c r="A82" s="27" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B82" s="25" t="n">
+      <c r="B82" s="28" t="n">
         <v>46269</v>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -2181,19 +2190,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D82" s="26" t="inlineStr">
+      <c r="D82" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463622979/</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="24" t="inlineStr">
+      <c r="A83" s="27" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B83" s="25" t="n">
+      <c r="B83" s="28" t="n">
         <v>46268</v>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2201,19 +2210,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Bracknell, UK</t>
         </is>
       </c>
-      <c r="D83" s="26" t="inlineStr">
+      <c r="D83" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462849233/</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B84" s="25" t="n">
+      <c r="A84" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B84" s="28" t="n">
         <v>46270</v>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -2221,19 +2230,19 @@
           <t>Hardware Engineer 2</t>
         </is>
       </c>
-      <c r="D84" s="26" t="inlineStr">
+      <c r="D84" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454834815/</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B85" s="25" t="n">
+      <c r="A85" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B85" s="28" t="n">
         <v>46268</v>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2241,19 +2250,19 @@
           <t>Principal SW Development Engineer</t>
         </is>
       </c>
-      <c r="D85" s="26" t="inlineStr">
+      <c r="D85" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453345730/</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="24" t="inlineStr">
+      <c r="A86" s="27" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B86" s="25" t="n">
+      <c r="B86" s="28" t="n">
         <v>46269</v>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -2261,19 +2270,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D86" s="26" t="inlineStr">
+      <c r="D86" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463634192/</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B87" s="25" t="n">
+      <c r="A87" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B87" s="28" t="n">
         <v>46270</v>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -2281,19 +2290,19 @@
           <t>Associate Customer Experience Manager</t>
         </is>
       </c>
-      <c r="D87" s="26" t="inlineStr">
+      <c r="D87" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454599227/</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B88" s="25" t="n">
+      <c r="A88" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B88" s="28" t="n">
         <v>46268</v>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -2301,19 +2310,19 @@
           <t>Sr Software QA Engineer</t>
         </is>
       </c>
-      <c r="D88" s="26" t="inlineStr">
+      <c r="D88" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453636185/</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="24" t="inlineStr">
+      <c r="A89" s="27" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B89" s="25" t="n">
+      <c r="B89" s="28" t="n">
         <v>46267</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -2321,19 +2330,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D89" s="26" t="inlineStr">
+      <c r="D89" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453092177/</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="24" t="inlineStr">
+      <c r="A90" s="27" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B90" s="25" t="n">
+      <c r="B90" s="28" t="n">
         <v>46269</v>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -2341,19 +2350,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D90" s="26" t="inlineStr">
+      <c r="D90" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463637144/</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="24" t="inlineStr">
+      <c r="A91" s="27" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B91" s="25" t="n">
+      <c r="B91" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -2361,19 +2370,19 @@
           <t>Sr. Systems Engineer</t>
         </is>
       </c>
-      <c r="D91" s="26" t="inlineStr">
+      <c r="D91" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461756319/</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B92" s="25" t="n">
+      <c r="A92" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B92" s="28" t="n">
         <v>46269</v>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -2381,19 +2390,19 @@
           <t>Senior SW Development Engineer</t>
         </is>
       </c>
-      <c r="D92" s="26" t="inlineStr">
+      <c r="D92" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454303425/</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B93" s="25" t="n">
+      <c r="A93" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B93" s="28" t="n">
         <v>46270</v>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -2401,19 +2410,19 @@
           <t>Senior Staff Mechanical Engineer - Characterization Lead</t>
         </is>
       </c>
-      <c r="D93" s="26" t="inlineStr">
+      <c r="D93" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427645063/</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="24" t="inlineStr">
+      <c r="A94" s="27" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B94" s="25" t="n">
+      <c r="B94" s="28" t="n">
         <v>46272</v>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -2421,19 +2430,19 @@
           <t>QA Engineer 2</t>
         </is>
       </c>
-      <c r="D94" s="26" t="inlineStr">
+      <c r="D94" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464097498/</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="24" t="inlineStr">
+      <c r="A95" s="27" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B95" s="25" t="n">
+      <c r="B95" s="28" t="n">
         <v>46268</v>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -2441,19 +2450,19 @@
           <t>Software Development Engineer 2</t>
         </is>
       </c>
-      <c r="D95" s="26" t="inlineStr">
+      <c r="D95" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453360435/</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="24" t="inlineStr">
+      <c r="A96" s="27" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B96" s="25" t="n">
+      <c r="B96" s="28" t="n">
         <v>46268</v>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -2461,19 +2470,19 @@
           <t>Senior Software Development Engineer</t>
         </is>
       </c>
-      <c r="D96" s="26" t="inlineStr">
+      <c r="D96" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453371096/</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B97" s="25" t="n">
+      <c r="A97" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B97" s="28" t="n">
         <v>46269</v>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -2481,19 +2490,19 @@
           <t>Sr SW Development Engineer</t>
         </is>
       </c>
-      <c r="D97" s="26" t="inlineStr">
+      <c r="D97" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463626373/</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="24" t="inlineStr">
+      <c r="A98" s="27" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B98" s="25" t="n">
+      <c r="B98" s="28" t="n">
         <v>46269</v>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -2501,19 +2510,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D98" s="26" t="inlineStr">
+      <c r="D98" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463633190/</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="24" t="inlineStr">
+      <c r="A99" s="27" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B99" s="25" t="n">
+      <c r="B99" s="28" t="n">
         <v>46269</v>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -2521,19 +2530,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D99" s="26" t="inlineStr">
+      <c r="D99" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463628391/</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="24" t="inlineStr">
+      <c r="A100" s="27" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B100" s="25" t="n">
+      <c r="B100" s="28" t="n">
         <v>46270</v>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -2541,19 +2550,19 @@
           <t>Sr IT Project Manager</t>
         </is>
       </c>
-      <c r="D100" s="26" t="inlineStr">
+      <c r="D100" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436188818/</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="24" t="inlineStr">
+      <c r="A101" s="27" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B101" s="25" t="n">
+      <c r="B101" s="28" t="n">
         <v>46267</v>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -2561,19 +2570,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D101" s="26" t="inlineStr">
+      <c r="D101" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453075275/</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B102" s="25" t="n">
+      <c r="A102" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B102" s="28" t="n">
         <v>46269</v>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -2581,19 +2590,19 @@
           <t>Sr Software QA Engineer</t>
         </is>
       </c>
-      <c r="D102" s="26" t="inlineStr">
+      <c r="D102" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463370785/</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B103" s="25" t="n">
+      <c r="A103" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B103" s="28" t="n">
         <v>46270</v>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -2601,19 +2610,19 @@
           <t>Material Handler 1 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D103" s="26" t="inlineStr">
+      <c r="D103" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455128356/</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="24" t="inlineStr">
+      <c r="A104" s="27" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="B104" s="25" t="n">
+      <c r="B104" s="28" t="n">
         <v>46267</v>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -2621,19 +2630,19 @@
           <t>Territory Sales Manager - Brussels (Bilingual Flemish &amp; French)</t>
         </is>
       </c>
-      <c r="D104" s="26" t="inlineStr">
+      <c r="D104" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453090144/</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="24" t="inlineStr">
+      <c r="A105" s="27" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B105" s="25" t="n">
+      <c r="B105" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -2641,19 +2650,19 @@
           <t>Systems Engineer 2</t>
         </is>
       </c>
-      <c r="D105" s="26" t="inlineStr">
+      <c r="D105" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461767088/</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="24" t="inlineStr">
+      <c r="A106" s="27" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="B106" s="25" t="n">
+      <c r="B106" s="28" t="n">
         <v>46267</v>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -2661,19 +2670,19 @@
           <t>Territory Sales Manager - Brussels (Bilingual Flemish &amp; French)</t>
         </is>
       </c>
-      <c r="D106" s="26" t="inlineStr">
+      <c r="D106" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453073289/</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="24" t="inlineStr">
+      <c r="A107" s="27" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B107" s="25" t="n">
+      <c r="B107" s="28" t="n">
         <v>46267</v>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -2681,19 +2690,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D107" s="26" t="inlineStr">
+      <c r="D107" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453083196/</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B108" s="25" t="n">
+      <c r="A108" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B108" s="28" t="n">
         <v>46269</v>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -2701,19 +2710,19 @@
           <t>Principal Firmware Architect</t>
         </is>
       </c>
-      <c r="D108" s="26" t="inlineStr">
+      <c r="D108" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463626391/</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B109" s="25" t="n">
+      <c r="A109" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B109" s="28" t="n">
         <v>46269</v>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -2721,19 +2730,19 @@
           <t>Software Development Engineer 1</t>
         </is>
       </c>
-      <c r="D109" s="26" t="inlineStr">
+      <c r="D109" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454097524/</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B110" s="25" t="n">
+      <c r="A110" s="27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B110" s="28" t="n">
         <v>46267</v>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -2741,7 +2750,7 @@
           <t>Sr Staff Endpoint Systems Engineer</t>
         </is>
       </c>
-      <c r="D110" s="26" t="inlineStr">
+      <c r="D110" s="29" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453090143/</t>
         </is>
@@ -2947,8 +2956,308 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="30" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B121" s="31" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>SW Development Engineer 1 - Android</t>
+        </is>
+      </c>
+      <c r="D121" s="32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464353380/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="30" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B122" s="31" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>Customer Advocacy Generalist</t>
+        </is>
+      </c>
+      <c r="D122" s="32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464354416/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="30" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B123" s="31" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>Staff Equipment Engineer</t>
+        </is>
+      </c>
+      <c r="D123" s="32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455253909/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="30" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B124" s="31" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>Customer Advocacy Generalist</t>
+        </is>
+      </c>
+      <c r="D124" s="32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464339507/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="30" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B125" s="31" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
+        </is>
+      </c>
+      <c r="D125" s="32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453077256/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="30" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B126" s="31" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
+        </is>
+      </c>
+      <c r="D126" s="32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453079245/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="30" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B127" s="31" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
+        </is>
+      </c>
+      <c r="D127" s="32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453091134/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="30" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B128" s="31" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
+        </is>
+      </c>
+      <c r="D128" s="32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453082209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="30" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B129" s="31" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>Material Handler 2 ( RDC ) - Days 1A and 1B</t>
+        </is>
+      </c>
+      <c r="D129" s="32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455289757/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="30" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B130" s="31" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>Procurement Ops Manager (IC)</t>
+        </is>
+      </c>
+      <c r="D130" s="32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453097103/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="30" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B131" s="31" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>Manager, APAC Business Development and Partnership</t>
+        </is>
+      </c>
+      <c r="D131" s="32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453093132/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="30" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B132" s="31" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>Territory Sales Manager - Galicia</t>
+        </is>
+      </c>
+      <c r="D132" s="32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4462835756/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="30" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B133" s="31" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>Desktop Support Specialist 3</t>
+        </is>
+      </c>
+      <c r="D133" s="32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4445930979/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="30" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B134" s="31" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>Sr Staff Endpoint Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D134" s="32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453076275/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="30" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B135" s="31" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>Material Handler 4 ( 2B Thur-Sat, every other Wednesday, Can work anytime from 5pm-5am )</t>
+        </is>
+      </c>
+      <c r="D135" s="32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464432288/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D120"/>
+  <autoFilter ref="A1:D135"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -3069,6 +3378,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -586,12 +586,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="33" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B2" s="31" t="n">
+      <c r="B2" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -599,19 +599,19 @@
           <t>Intelligence Analyst</t>
         </is>
       </c>
-      <c r="D2" s="32" t="inlineStr">
+      <c r="D2" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453085191/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B3" s="31" t="n">
+      <c r="A3" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B3" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -619,19 +619,19 @@
           <t>Senior Staff Process Development Engineer</t>
         </is>
       </c>
-      <c r="D3" s="32" t="inlineStr">
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443563067/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B4" s="31" t="n">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B4" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -639,19 +639,19 @@
           <t>Senior Director, Lean</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462725850/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B5" s="31" t="n">
+      <c r="B5" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -659,19 +659,19 @@
           <t>Intelligence Analyst</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082218/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B6" s="31" t="n">
+      <c r="B6" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -679,19 +679,19 @@
           <t>Sr Process Engineer</t>
         </is>
       </c>
-      <c r="D6" s="32" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435122348/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B7" s="31" t="n">
+      <c r="B7" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -699,19 +699,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D7" s="32" t="inlineStr">
+      <c r="D7" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453096131/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B8" s="31" t="n">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -719,19 +719,19 @@
           <t>Lead Corporate Development Manager</t>
         </is>
       </c>
-      <c r="D8" s="32" t="inlineStr">
+      <c r="D8" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462460922/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B9" s="31" t="n">
+      <c r="B9" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -739,19 +739,19 @@
           <t>Accountant - Healthcare - Edinburgh</t>
         </is>
       </c>
-      <c r="D9" s="32" t="inlineStr">
+      <c r="D9" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453144035/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="n">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -759,19 +759,19 @@
           <t>Staff Quality Compliance Specialist</t>
         </is>
       </c>
-      <c r="D10" s="32" t="inlineStr">
+      <c r="D10" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462730823/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="B11" s="31" t="n">
+      <c r="B11" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -779,19 +779,19 @@
           <t>Territory Sales Manager (m/w/d) - Zentralschweiz : Luzern, Obwalden, Nidwalden, Uri, Chur</t>
         </is>
       </c>
-      <c r="D11" s="32" t="inlineStr">
+      <c r="D11" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453133160/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B12" s="31" t="n">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -799,19 +799,19 @@
           <t>Territory Business Manager - Morristown, New Jersey</t>
         </is>
       </c>
-      <c r="D12" s="32" t="inlineStr">
+      <c r="D12" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4452316210/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B13" s="31" t="n">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -819,19 +819,19 @@
           <t>QC Inspector 4 - 1B Thur-Sat, every other Wednesday from 5am-5pm</t>
         </is>
       </c>
-      <c r="D13" s="32" t="inlineStr">
+      <c r="D13" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462726839/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B14" s="31" t="n">
+      <c r="B14" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -839,19 +839,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D14" s="32" t="inlineStr">
+      <c r="D14" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097086/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B15" s="31" t="n">
+      <c r="B15" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -859,19 +859,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D15" s="32" t="inlineStr">
+      <c r="D15" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453076276/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B16" s="31" t="n">
+      <c r="B16" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -879,19 +879,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D16" s="32" t="inlineStr">
+      <c r="D16" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453087192/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B17" s="31" t="n">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -899,19 +899,19 @@
           <t>Manufacturing Technician 3-1B Thursday-Saturday every other Wednesday(5AM-5PM)</t>
         </is>
       </c>
-      <c r="D17" s="32" t="inlineStr">
+      <c r="D17" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460900071/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B18" s="31" t="n">
+      <c r="B18" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -919,19 +919,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D18" s="32" t="inlineStr">
+      <c r="D18" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453078274/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B19" s="31" t="n">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -939,19 +939,19 @@
           <t>Platform Security Engineer 2</t>
         </is>
       </c>
-      <c r="D19" s="32" t="inlineStr">
+      <c r="D19" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462736772/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="inlineStr">
+      <c r="A20" s="33" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B20" s="31" t="n">
+      <c r="B20" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -959,19 +959,19 @@
           <t>APAC FP&amp;A Manager</t>
         </is>
       </c>
-      <c r="D20" s="32" t="inlineStr">
+      <c r="D20" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462770899/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="A21" s="33" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B21" s="31" t="n">
+      <c r="B21" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -979,19 +979,19 @@
           <t>Commercial Analytics &amp; Operations Associate</t>
         </is>
       </c>
-      <c r="D21" s="32" t="inlineStr">
+      <c r="D21" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462778751/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B22" s="31" t="n">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B22" s="34" t="n">
         <v>46269</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -999,19 +999,19 @@
           <t>Document Control and Training Specialist 1</t>
         </is>
       </c>
-      <c r="D22" s="32" t="inlineStr">
+      <c r="D22" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463157831/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="A23" s="33" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B23" s="31" t="n">
+      <c r="B23" s="34" t="n">
         <v>46269</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1019,19 +1019,19 @@
           <t>Sr Supply Chain Analyst</t>
         </is>
       </c>
-      <c r="D23" s="32" t="inlineStr">
+      <c r="D23" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463169639/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="A24" s="33" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B24" s="31" t="n">
+      <c r="B24" s="34" t="n">
         <v>46269</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1039,19 +1039,19 @@
           <t>IT Procurement Analyst</t>
         </is>
       </c>
-      <c r="D24" s="32" t="inlineStr">
+      <c r="D24" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463313428/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="30" t="inlineStr">
+      <c r="A25" s="33" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B25" s="31" t="n">
+      <c r="B25" s="34" t="n">
         <v>46269</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1059,19 +1059,19 @@
           <t>IT Procurement Analyst</t>
         </is>
       </c>
-      <c r="D25" s="32" t="inlineStr">
+      <c r="D25" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463314400/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B26" s="31" t="n">
+      <c r="A26" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B26" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1079,19 +1079,19 @@
           <t>Product Manager, Patient Onboarding &amp; First Value</t>
         </is>
       </c>
-      <c r="D26" s="32" t="inlineStr">
+      <c r="D26" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453357502/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B27" s="31" t="n">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B27" s="34" t="n">
         <v>46270</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1099,19 +1099,19 @@
           <t>Staff Technical Program Manager - Innovation Ventures &amp; Sensor Technology</t>
         </is>
       </c>
-      <c r="D27" s="32" t="inlineStr">
+      <c r="D27" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454853005/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B28" s="31" t="n">
+      <c r="A28" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B28" s="34" t="n">
         <v>46270</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1119,19 +1119,19 @@
           <t>Project Manager 2</t>
         </is>
       </c>
-      <c r="D28" s="32" t="inlineStr">
+      <c r="D28" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463687671/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B29" s="31" t="n">
+      <c r="A29" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B29" s="34" t="n">
         <v>46269</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1139,19 +1139,19 @@
           <t>Senior Medical Affairs Manager – Value, Evidence, and Outcomes</t>
         </is>
       </c>
-      <c r="D29" s="32" t="inlineStr">
+      <c r="D29" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443448275/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B30" s="31" t="n">
+      <c r="A30" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B30" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1159,19 +1159,19 @@
           <t>Director of Sensor Research</t>
         </is>
       </c>
-      <c r="D30" s="32" t="inlineStr">
+      <c r="D30" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427088373/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B31" s="31" t="n">
+      <c r="A31" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B31" s="34" t="n">
         <v>46271</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1179,19 +1179,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D31" s="32" t="inlineStr">
+      <c r="D31" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436409441/</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="30" t="inlineStr">
+      <c r="A32" s="33" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B32" s="31" t="n">
+      <c r="B32" s="34" t="n">
         <v>46270</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1199,19 +1199,19 @@
           <t>Distributor Manager - Channel Excellence (MedTech)</t>
         </is>
       </c>
-      <c r="D32" s="32" t="inlineStr">
+      <c r="D32" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463683762/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B33" s="31" t="n">
+      <c r="A33" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B33" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1219,19 +1219,19 @@
           <t>Territory Business Manager - Erie Pennsylvania</t>
         </is>
       </c>
-      <c r="D33" s="32" t="inlineStr">
+      <c r="D33" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440304526/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B34" s="31" t="n">
+      <c r="A34" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B34" s="34" t="n">
         <v>46270</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1239,19 +1239,19 @@
           <t>QA Inspector 2 ( Dobson ) - 1A Sun- Tues, every other Wednesday, Can work anytime from 5am-5pm</t>
         </is>
       </c>
-      <c r="D34" s="32" t="inlineStr">
+      <c r="D34" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463691655/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="30" t="inlineStr">
+      <c r="A35" s="33" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B35" s="31" t="n">
+      <c r="B35" s="34" t="n">
         <v>46270</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1259,19 +1259,19 @@
           <t>Distributor Manager - Channel Excellence (MedTech)</t>
         </is>
       </c>
-      <c r="D35" s="32" t="inlineStr">
+      <c r="D35" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463684766/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B36" s="31" t="n">
+      <c r="A36" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B36" s="34" t="n">
         <v>46269</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1279,19 +1279,19 @@
           <t>Sr. Clinical Customer Advocate</t>
         </is>
       </c>
-      <c r="D36" s="32" t="inlineStr">
+      <c r="D36" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463625584/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B37" s="31" t="n">
+      <c r="A37" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B37" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1299,19 +1299,19 @@
           <t>Staff Data Scientist</t>
         </is>
       </c>
-      <c r="D37" s="32" t="inlineStr">
+      <c r="D37" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463110275/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="30" t="inlineStr">
+      <c r="A38" s="33" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B38" s="31" t="n">
+      <c r="B38" s="34" t="n">
         <v>46269</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1319,19 +1319,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D38" s="32" t="inlineStr">
+      <c r="D38" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463622979/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="30" t="inlineStr">
+      <c r="A39" s="33" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B39" s="31" t="n">
+      <c r="B39" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1339,19 +1339,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Bracknell, UK</t>
         </is>
       </c>
-      <c r="D39" s="32" t="inlineStr">
+      <c r="D39" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462849233/</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B40" s="31" t="n">
+      <c r="A40" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B40" s="34" t="n">
         <v>46270</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1359,19 +1359,19 @@
           <t>Hardware Engineer 2</t>
         </is>
       </c>
-      <c r="D40" s="32" t="inlineStr">
+      <c r="D40" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454834815/</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B41" s="31" t="n">
+      <c r="A41" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B41" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1379,19 +1379,19 @@
           <t>Principal SW Development Engineer</t>
         </is>
       </c>
-      <c r="D41" s="32" t="inlineStr">
+      <c r="D41" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453345730/</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="30" t="inlineStr">
+      <c r="A42" s="33" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B42" s="31" t="n">
+      <c r="B42" s="34" t="n">
         <v>46269</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1399,19 +1399,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D42" s="32" t="inlineStr">
+      <c r="D42" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463634192/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B43" s="31" t="n">
+      <c r="A43" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B43" s="34" t="n">
         <v>46270</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1419,19 +1419,19 @@
           <t>Associate Customer Experience Manager</t>
         </is>
       </c>
-      <c r="D43" s="32" t="inlineStr">
+      <c r="D43" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454599227/</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B44" s="31" t="n">
+      <c r="A44" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B44" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1439,19 +1439,19 @@
           <t>Sr Software QA Engineer</t>
         </is>
       </c>
-      <c r="D44" s="32" t="inlineStr">
+      <c r="D44" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453636185/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="30" t="inlineStr">
+      <c r="A45" s="33" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B45" s="31" t="n">
+      <c r="B45" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1459,19 +1459,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D45" s="32" t="inlineStr">
+      <c r="D45" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453092177/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="30" t="inlineStr">
+      <c r="A46" s="33" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B46" s="31" t="n">
+      <c r="B46" s="34" t="n">
         <v>46269</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1479,19 +1479,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D46" s="32" t="inlineStr">
+      <c r="D46" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463637144/</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B47" s="31" t="n">
+      <c r="A47" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B47" s="34" t="n">
         <v>46269</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1499,19 +1499,19 @@
           <t>Senior SW Development Engineer</t>
         </is>
       </c>
-      <c r="D47" s="32" t="inlineStr">
+      <c r="D47" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454303425/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B48" s="31" t="n">
+      <c r="A48" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B48" s="34" t="n">
         <v>46270</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1519,19 +1519,19 @@
           <t>Senior Staff Mechanical Engineer - Characterization Lead</t>
         </is>
       </c>
-      <c r="D48" s="32" t="inlineStr">
+      <c r="D48" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427645063/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="30" t="inlineStr">
+      <c r="A49" s="33" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B49" s="31" t="n">
+      <c r="B49" s="34" t="n">
         <v>46272</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1539,19 +1539,19 @@
           <t>QA Engineer 2</t>
         </is>
       </c>
-      <c r="D49" s="32" t="inlineStr">
+      <c r="D49" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464097498/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="30" t="inlineStr">
+      <c r="A50" s="33" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B50" s="31" t="n">
+      <c r="B50" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1559,19 +1559,19 @@
           <t>Software Development Engineer 2</t>
         </is>
       </c>
-      <c r="D50" s="32" t="inlineStr">
+      <c r="D50" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453360435/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="30" t="inlineStr">
+      <c r="A51" s="33" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B51" s="31" t="n">
+      <c r="B51" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1579,19 +1579,19 @@
           <t>Senior Software Development Engineer</t>
         </is>
       </c>
-      <c r="D51" s="32" t="inlineStr">
+      <c r="D51" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453371096/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B52" s="31" t="n">
+      <c r="A52" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B52" s="34" t="n">
         <v>46269</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -1599,19 +1599,19 @@
           <t>Sr SW Development Engineer</t>
         </is>
       </c>
-      <c r="D52" s="32" t="inlineStr">
+      <c r="D52" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463626373/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="30" t="inlineStr">
+      <c r="A53" s="33" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B53" s="31" t="n">
+      <c r="B53" s="34" t="n">
         <v>46269</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1619,19 +1619,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D53" s="32" t="inlineStr">
+      <c r="D53" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463633190/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="30" t="inlineStr">
+      <c r="A54" s="33" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B54" s="31" t="n">
+      <c r="B54" s="34" t="n">
         <v>46269</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1639,19 +1639,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D54" s="32" t="inlineStr">
+      <c r="D54" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463628391/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="30" t="inlineStr">
+      <c r="A55" s="33" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B55" s="31" t="n">
+      <c r="B55" s="34" t="n">
         <v>46270</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1659,19 +1659,19 @@
           <t>Sr IT Project Manager</t>
         </is>
       </c>
-      <c r="D55" s="32" t="inlineStr">
+      <c r="D55" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436188818/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="30" t="inlineStr">
+      <c r="A56" s="33" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B56" s="31" t="n">
+      <c r="B56" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1679,19 +1679,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D56" s="32" t="inlineStr">
+      <c r="D56" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453075275/</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B57" s="31" t="n">
+      <c r="A57" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B57" s="34" t="n">
         <v>46269</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1699,19 +1699,19 @@
           <t>Sr Software QA Engineer</t>
         </is>
       </c>
-      <c r="D57" s="32" t="inlineStr">
+      <c r="D57" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463370785/</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B58" s="31" t="n">
+      <c r="A58" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B58" s="34" t="n">
         <v>46270</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1719,19 +1719,19 @@
           <t>Material Handler 1 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D58" s="32" t="inlineStr">
+      <c r="D58" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455128356/</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="30" t="inlineStr">
+      <c r="A59" s="33" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="B59" s="31" t="n">
+      <c r="B59" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1739,19 +1739,19 @@
           <t>Territory Sales Manager - Brussels (Bilingual Flemish &amp; French)</t>
         </is>
       </c>
-      <c r="D59" s="32" t="inlineStr">
+      <c r="D59" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453090144/</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="30" t="inlineStr">
+      <c r="A60" s="33" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="B60" s="31" t="n">
+      <c r="B60" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1759,19 +1759,19 @@
           <t>Territory Sales Manager - Brussels (Bilingual Flemish &amp; French)</t>
         </is>
       </c>
-      <c r="D60" s="32" t="inlineStr">
+      <c r="D60" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453073289/</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="30" t="inlineStr">
+      <c r="A61" s="33" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B61" s="31" t="n">
+      <c r="B61" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1779,19 +1779,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D61" s="32" t="inlineStr">
+      <c r="D61" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453083196/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B62" s="31" t="n">
+      <c r="A62" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B62" s="34" t="n">
         <v>46269</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1799,19 +1799,19 @@
           <t>Principal Firmware Architect</t>
         </is>
       </c>
-      <c r="D62" s="32" t="inlineStr">
+      <c r="D62" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463626391/</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B63" s="31" t="n">
+      <c r="A63" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B63" s="34" t="n">
         <v>46269</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1819,19 +1819,19 @@
           <t>Software Development Engineer 1</t>
         </is>
       </c>
-      <c r="D63" s="32" t="inlineStr">
+      <c r="D63" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454097524/</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B64" s="31" t="n">
+      <c r="A64" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B64" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1839,19 +1839,19 @@
           <t>Sr Staff Endpoint Systems Engineer</t>
         </is>
       </c>
-      <c r="D64" s="32" t="inlineStr">
+      <c r="D64" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453090143/</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="30" t="inlineStr">
+      <c r="A65" s="33" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B65" s="31" t="n">
+      <c r="B65" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1859,19 +1859,19 @@
           <t>Supervisor Customer Advocacy</t>
         </is>
       </c>
-      <c r="D65" s="32" t="inlineStr">
+      <c r="D65" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454022788/</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="30" t="inlineStr">
+      <c r="A66" s="33" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B66" s="31" t="n">
+      <c r="B66" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1879,19 +1879,19 @@
           <t>Customer Service Representative (German-speaking)</t>
         </is>
       </c>
-      <c r="D66" s="32" t="inlineStr">
+      <c r="D66" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463120173/</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="30" t="inlineStr">
+      <c r="A67" s="33" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B67" s="31" t="n">
+      <c r="B67" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1899,19 +1899,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D67" s="32" t="inlineStr">
+      <c r="D67" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454019825/</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+      <c r="A68" s="33" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B68" s="31" t="n">
+      <c r="B68" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1919,19 +1919,19 @@
           <t>Customer Service Representative, French Speaker</t>
         </is>
       </c>
-      <c r="D68" s="32" t="inlineStr">
+      <c r="D68" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462772822/</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
+      <c r="A69" s="33" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B69" s="31" t="n">
+      <c r="B69" s="34" t="n">
         <v>46269</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1939,19 +1939,19 @@
           <t>Intelligence Analyst - Geopolitical</t>
         </is>
       </c>
-      <c r="D69" s="32" t="inlineStr">
+      <c r="D69" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444046742/</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
+      <c r="A70" s="33" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B70" s="31" t="n">
+      <c r="B70" s="34" t="n">
         <v>46270</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1959,19 +1959,19 @@
           <t>GBS Engagement &amp; Service Management Lead</t>
         </is>
       </c>
-      <c r="D70" s="32" t="inlineStr">
+      <c r="D70" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427554137/</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="30" t="inlineStr">
+      <c r="A71" s="33" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B71" s="31" t="n">
+      <c r="B71" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1979,19 +1979,19 @@
           <t>Contact Center Platform Analyst</t>
         </is>
       </c>
-      <c r="D71" s="32" t="inlineStr">
+      <c r="D71" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462857053/</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="30" t="inlineStr">
+      <c r="A72" s="33" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B72" s="31" t="n">
+      <c r="B72" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -1999,19 +1999,19 @@
           <t>Program Manager - AI Initiatives</t>
         </is>
       </c>
-      <c r="D72" s="32" t="inlineStr">
+      <c r="D72" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435119512/</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="30" t="inlineStr">
+      <c r="A73" s="33" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B73" s="31" t="n">
+      <c r="B73" s="34" t="n">
         <v>46269</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2019,19 +2019,19 @@
           <t>Senior Telecom Engineer (Genesys Cloud)</t>
         </is>
       </c>
-      <c r="D73" s="32" t="inlineStr">
+      <c r="D73" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463370784/</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="30" t="inlineStr">
+      <c r="A74" s="33" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B74" s="31" t="n">
+      <c r="B74" s="34" t="n">
         <v>46272</v>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -2039,19 +2039,19 @@
           <t>SW Development Engineer 1 - Android</t>
         </is>
       </c>
-      <c r="D74" s="32" t="inlineStr">
+      <c r="D74" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464353380/</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="30" t="inlineStr">
+      <c r="A75" s="33" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B75" s="31" t="n">
+      <c r="B75" s="34" t="n">
         <v>46272</v>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -2059,19 +2059,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D75" s="32" t="inlineStr">
+      <c r="D75" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464354416/</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="30" t="inlineStr">
+      <c r="A76" s="33" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B76" s="31" t="n">
+      <c r="B76" s="34" t="n">
         <v>46272</v>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -2079,19 +2079,19 @@
           <t>Staff Equipment Engineer</t>
         </is>
       </c>
-      <c r="D76" s="32" t="inlineStr">
+      <c r="D76" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455253909/</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="inlineStr">
+      <c r="A77" s="33" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B77" s="31" t="n">
+      <c r="B77" s="34" t="n">
         <v>46272</v>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -2099,19 +2099,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D77" s="32" t="inlineStr">
+      <c r="D77" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464339507/</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="inlineStr">
+      <c r="A78" s="33" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B78" s="31" t="n">
+      <c r="B78" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -2119,19 +2119,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D78" s="32" t="inlineStr">
+      <c r="D78" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453077256/</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="30" t="inlineStr">
+      <c r="A79" s="33" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B79" s="31" t="n">
+      <c r="B79" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -2139,19 +2139,19 @@
           <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
         </is>
       </c>
-      <c r="D79" s="32" t="inlineStr">
+      <c r="D79" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453079245/</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="30" t="inlineStr">
+      <c r="A80" s="33" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B80" s="31" t="n">
+      <c r="B80" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -2159,19 +2159,19 @@
           <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
         </is>
       </c>
-      <c r="D80" s="32" t="inlineStr">
+      <c r="D80" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453091134/</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="30" t="inlineStr">
+      <c r="A81" s="33" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B81" s="31" t="n">
+      <c r="B81" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2179,19 +2179,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D81" s="32" t="inlineStr">
+      <c r="D81" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082209/</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B82" s="31" t="n">
+      <c r="A82" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B82" s="34" t="n">
         <v>46272</v>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -2199,19 +2199,19 @@
           <t>Material Handler 2 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D82" s="32" t="inlineStr">
+      <c r="D82" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455289757/</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="30" t="inlineStr">
+      <c r="A83" s="33" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B83" s="31" t="n">
+      <c r="B83" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2219,19 +2219,19 @@
           <t>Procurement Ops Manager (IC)</t>
         </is>
       </c>
-      <c r="D83" s="32" t="inlineStr">
+      <c r="D83" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097103/</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="30" t="inlineStr">
+      <c r="A84" s="33" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B84" s="31" t="n">
+      <c r="B84" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -2239,19 +2239,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D84" s="32" t="inlineStr">
+      <c r="D84" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453093132/</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="30" t="inlineStr">
+      <c r="A85" s="33" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B85" s="31" t="n">
+      <c r="B85" s="34" t="n">
         <v>46268</v>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2259,19 +2259,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D85" s="32" t="inlineStr">
+      <c r="D85" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462835756/</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="30" t="inlineStr">
+      <c r="A86" s="33" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B86" s="31" t="n">
+      <c r="B86" s="34" t="n">
         <v>46272</v>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -2279,19 +2279,19 @@
           <t>Desktop Support Specialist 3</t>
         </is>
       </c>
-      <c r="D86" s="32" t="inlineStr">
+      <c r="D86" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4445930979/</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B87" s="31" t="n">
+      <c r="A87" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B87" s="34" t="n">
         <v>46267</v>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -2299,19 +2299,19 @@
           <t>Sr Staff Endpoint Systems Engineer</t>
         </is>
       </c>
-      <c r="D87" s="32" t="inlineStr">
+      <c r="D87" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453076275/</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B88" s="31" t="n">
+      <c r="A88" s="33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B88" s="34" t="n">
         <v>46273</v>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -2319,7 +2319,7 @@
           <t>Material Handler 4 ( 2B Thur-Sat, every other Wednesday, Can work anytime from 5pm-5am )</t>
         </is>
       </c>
-      <c r="D88" s="32" t="inlineStr">
+      <c r="D88" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464432288/</t>
         </is>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$123</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -554,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2545,8 +2554,488 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="36" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B100" s="37" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Sr Buyer</t>
+        </is>
+      </c>
+      <c r="D100" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4454535222/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="36" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B101" s="37" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>Planning Manager</t>
+        </is>
+      </c>
+      <c r="D101" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4454556094/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="36" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B102" s="37" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>Production Planner</t>
+        </is>
+      </c>
+      <c r="D102" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4454538160/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="36" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B103" s="37" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Quality Technician 2 Back End Days</t>
+        </is>
+      </c>
+      <c r="D103" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464613132/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="36" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B104" s="37" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>Process Technician 2 (Front End Night Shift)</t>
+        </is>
+      </c>
+      <c r="D104" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455755200/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="36" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B105" s="37" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>Supervisor Process Engineering</t>
+        </is>
+      </c>
+      <c r="D105" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464338496/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="36" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B106" s="37" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>Sr Production Supervisor (Front End Night Shift)</t>
+        </is>
+      </c>
+      <c r="D106" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455302580/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="36" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B107" s="37" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>Engineering Technician 4 (Monday to Friday days)</t>
+        </is>
+      </c>
+      <c r="D107" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463368770/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="36" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B108" s="37" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>Engineering Technician 3 (Front End Day Shift)</t>
+        </is>
+      </c>
+      <c r="D108" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463698028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="36" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B109" s="37" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>QA Engineer Digital Systems</t>
+        </is>
+      </c>
+      <c r="D109" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444460213/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="36" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B110" s="37" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>Lab Supervisor (Manufacturing) - Back End Day Shift</t>
+        </is>
+      </c>
+      <c r="D110" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463359959/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="36" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B111" s="37" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
+        </is>
+      </c>
+      <c r="D111" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463699027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="36" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B112" s="37" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Lab Technician 3 (Chemistry)</t>
+        </is>
+      </c>
+      <c r="D112" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464341469/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="36" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B113" s="37" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>Medical Representative MR 医療機器 糖尿病領域 営業職</t>
+        </is>
+      </c>
+      <c r="D113" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455248893/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="36" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B114" s="37" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>UI Designer (Design System)</t>
+        </is>
+      </c>
+      <c r="D114" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4427632128/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="36" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B115" s="37" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
+        </is>
+      </c>
+      <c r="D115" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443109225/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="36" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B116" s="37" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>Senior Warehouse Operative - Day Shift</t>
+        </is>
+      </c>
+      <c r="D116" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463635156/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="36" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B117" s="37" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>Senior Accountant/Bilanzbuchhalter (m/w/d) - Healthcare</t>
+        </is>
+      </c>
+      <c r="D117" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455750299/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="36" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B118" s="37" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>Territory Business Manager</t>
+        </is>
+      </c>
+      <c r="D118" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464350389/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="36" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B119" s="37" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>Sr Technical Writer</t>
+        </is>
+      </c>
+      <c r="D119" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465024024/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="36" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B120" s="37" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>Sr SW Development Engineer - IOS</t>
+        </is>
+      </c>
+      <c r="D120" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465020025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B121" s="37" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>Material Handler 2 ( RDC ) - Nights 2A and 2B</t>
+        </is>
+      </c>
+      <c r="D121" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455289751/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="36" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B122" s="37" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>SW Development Engineer 2 - Android</t>
+        </is>
+      </c>
+      <c r="D122" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464610755/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="36" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B123" s="37" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>Sr Enterprise Developer (Power Platform Developer)</t>
+        </is>
+      </c>
+      <c r="D123" s="38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455767052/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D99"/>
+  <autoFilter ref="A1:D123"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -2646,6 +3135,30 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId122"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$126</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -563,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -595,12 +604,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="36" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B2" s="34" t="n">
+      <c r="B2" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -608,19 +617,19 @@
           <t>Intelligence Analyst</t>
         </is>
       </c>
-      <c r="D2" s="35" t="inlineStr">
+      <c r="D2" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453085191/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B3" s="34" t="n">
+      <c r="A3" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B3" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -628,19 +637,19 @@
           <t>Senior Staff Process Development Engineer</t>
         </is>
       </c>
-      <c r="D3" s="35" t="inlineStr">
+      <c r="D3" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443563067/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B4" s="34" t="n">
+      <c r="A4" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B4" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -648,19 +657,19 @@
           <t>Senior Director, Lean</t>
         </is>
       </c>
-      <c r="D4" s="35" t="inlineStr">
+      <c r="D4" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462725850/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B5" s="34" t="n">
+      <c r="B5" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -668,19 +677,19 @@
           <t>Intelligence Analyst</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082218/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -688,19 +697,19 @@
           <t>Sr Process Engineer</t>
         </is>
       </c>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="D6" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435122348/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B7" s="34" t="n">
+      <c r="B7" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -708,19 +717,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D7" s="35" t="inlineStr">
+      <c r="D7" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453096131/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B8" s="34" t="n">
+      <c r="A8" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B8" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -728,19 +737,19 @@
           <t>Lead Corporate Development Manager</t>
         </is>
       </c>
-      <c r="D8" s="35" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462460922/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B9" s="34" t="n">
+      <c r="B9" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -748,19 +757,19 @@
           <t>Accountant - Healthcare - Edinburgh</t>
         </is>
       </c>
-      <c r="D9" s="35" t="inlineStr">
+      <c r="D9" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453144035/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B10" s="34" t="n">
+      <c r="A10" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B10" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -768,19 +777,19 @@
           <t>Staff Quality Compliance Specialist</t>
         </is>
       </c>
-      <c r="D10" s="35" t="inlineStr">
+      <c r="D10" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462730823/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="B11" s="34" t="n">
+      <c r="B11" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -788,19 +797,19 @@
           <t>Territory Sales Manager (m/w/d) - Zentralschweiz : Luzern, Obwalden, Nidwalden, Uri, Chur</t>
         </is>
       </c>
-      <c r="D11" s="35" t="inlineStr">
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453133160/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B12" s="34" t="n">
+      <c r="A12" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -808,19 +817,19 @@
           <t>Territory Business Manager - Morristown, New Jersey</t>
         </is>
       </c>
-      <c r="D12" s="35" t="inlineStr">
+      <c r="D12" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4452316210/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B13" s="34" t="n">
+      <c r="A13" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B13" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -828,19 +837,19 @@
           <t>QC Inspector 4 - 1B Thur-Sat, every other Wednesday from 5am-5pm</t>
         </is>
       </c>
-      <c r="D13" s="35" t="inlineStr">
+      <c r="D13" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462726839/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B14" s="34" t="n">
+      <c r="B14" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -848,19 +857,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D14" s="35" t="inlineStr">
+      <c r="D14" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097086/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B15" s="34" t="n">
+      <c r="B15" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -868,19 +877,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D15" s="35" t="inlineStr">
+      <c r="D15" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453076276/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B16" s="34" t="n">
+      <c r="B16" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -888,19 +897,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D16" s="35" t="inlineStr">
+      <c r="D16" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453087192/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B17" s="34" t="n">
+      <c r="A17" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B17" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -908,19 +917,19 @@
           <t>Manufacturing Technician 3-1B Thursday-Saturday every other Wednesday(5AM-5PM)</t>
         </is>
       </c>
-      <c r="D17" s="35" t="inlineStr">
+      <c r="D17" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460900071/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B18" s="34" t="n">
+      <c r="B18" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -928,19 +937,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D18" s="35" t="inlineStr">
+      <c r="D18" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453078274/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B19" s="34" t="n">
+      <c r="A19" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B19" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -948,19 +957,19 @@
           <t>Platform Security Engineer 2</t>
         </is>
       </c>
-      <c r="D19" s="35" t="inlineStr">
+      <c r="D19" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462736772/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="33" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B20" s="34" t="n">
+      <c r="B20" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -968,19 +977,19 @@
           <t>APAC FP&amp;A Manager</t>
         </is>
       </c>
-      <c r="D20" s="35" t="inlineStr">
+      <c r="D20" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462770899/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="33" t="inlineStr">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B21" s="34" t="n">
+      <c r="B21" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -988,19 +997,19 @@
           <t>Commercial Analytics &amp; Operations Associate</t>
         </is>
       </c>
-      <c r="D21" s="35" t="inlineStr">
+      <c r="D21" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462778751/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B22" s="34" t="n">
+      <c r="A22" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B22" s="37" t="n">
         <v>46269</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1008,19 +1017,19 @@
           <t>Document Control and Training Specialist 1</t>
         </is>
       </c>
-      <c r="D22" s="35" t="inlineStr">
+      <c r="D22" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463157831/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="33" t="inlineStr">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B23" s="34" t="n">
+      <c r="B23" s="37" t="n">
         <v>46269</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1028,19 +1037,19 @@
           <t>Sr Supply Chain Analyst</t>
         </is>
       </c>
-      <c r="D23" s="35" t="inlineStr">
+      <c r="D23" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463169639/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="33" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B24" s="34" t="n">
+      <c r="B24" s="37" t="n">
         <v>46269</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1048,19 +1057,19 @@
           <t>IT Procurement Analyst</t>
         </is>
       </c>
-      <c r="D24" s="35" t="inlineStr">
+      <c r="D24" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463313428/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="33" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B25" s="34" t="n">
+      <c r="B25" s="37" t="n">
         <v>46269</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1068,19 +1077,19 @@
           <t>IT Procurement Analyst</t>
         </is>
       </c>
-      <c r="D25" s="35" t="inlineStr">
+      <c r="D25" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463314400/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B26" s="34" t="n">
+      <c r="A26" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B26" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1088,19 +1097,19 @@
           <t>Product Manager, Patient Onboarding &amp; First Value</t>
         </is>
       </c>
-      <c r="D26" s="35" t="inlineStr">
+      <c r="D26" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453357502/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B27" s="34" t="n">
+      <c r="A27" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B27" s="37" t="n">
         <v>46270</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1108,19 +1117,19 @@
           <t>Staff Technical Program Manager - Innovation Ventures &amp; Sensor Technology</t>
         </is>
       </c>
-      <c r="D27" s="35" t="inlineStr">
+      <c r="D27" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454853005/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B28" s="34" t="n">
+      <c r="A28" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B28" s="37" t="n">
         <v>46270</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1128,19 +1137,19 @@
           <t>Project Manager 2</t>
         </is>
       </c>
-      <c r="D28" s="35" t="inlineStr">
+      <c r="D28" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463687671/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B29" s="34" t="n">
+      <c r="A29" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B29" s="37" t="n">
         <v>46269</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1148,19 +1157,19 @@
           <t>Senior Medical Affairs Manager – Value, Evidence, and Outcomes</t>
         </is>
       </c>
-      <c r="D29" s="35" t="inlineStr">
+      <c r="D29" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443448275/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B30" s="34" t="n">
+      <c r="A30" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B30" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1168,19 +1177,19 @@
           <t>Director of Sensor Research</t>
         </is>
       </c>
-      <c r="D30" s="35" t="inlineStr">
+      <c r="D30" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427088373/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B31" s="34" t="n">
+      <c r="A31" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B31" s="37" t="n">
         <v>46271</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1188,19 +1197,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D31" s="35" t="inlineStr">
+      <c r="D31" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436409441/</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="33" t="inlineStr">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B32" s="34" t="n">
+      <c r="B32" s="37" t="n">
         <v>46270</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1208,19 +1217,19 @@
           <t>Distributor Manager - Channel Excellence (MedTech)</t>
         </is>
       </c>
-      <c r="D32" s="35" t="inlineStr">
+      <c r="D32" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463683762/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B33" s="34" t="n">
+      <c r="A33" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B33" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1228,19 +1237,19 @@
           <t>Territory Business Manager - Erie Pennsylvania</t>
         </is>
       </c>
-      <c r="D33" s="35" t="inlineStr">
+      <c r="D33" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440304526/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B34" s="34" t="n">
+      <c r="A34" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B34" s="37" t="n">
         <v>46270</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1248,19 +1257,19 @@
           <t>QA Inspector 2 ( Dobson ) - 1A Sun- Tues, every other Wednesday, Can work anytime from 5am-5pm</t>
         </is>
       </c>
-      <c r="D34" s="35" t="inlineStr">
+      <c r="D34" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463691655/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="33" t="inlineStr">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B35" s="34" t="n">
+      <c r="B35" s="37" t="n">
         <v>46270</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1268,19 +1277,19 @@
           <t>Distributor Manager - Channel Excellence (MedTech)</t>
         </is>
       </c>
-      <c r="D35" s="35" t="inlineStr">
+      <c r="D35" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463684766/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B36" s="34" t="n">
+      <c r="A36" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B36" s="37" t="n">
         <v>46269</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1288,19 +1297,19 @@
           <t>Sr. Clinical Customer Advocate</t>
         </is>
       </c>
-      <c r="D36" s="35" t="inlineStr">
+      <c r="D36" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463625584/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B37" s="34" t="n">
+      <c r="A37" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B37" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1308,19 +1317,19 @@
           <t>Staff Data Scientist</t>
         </is>
       </c>
-      <c r="D37" s="35" t="inlineStr">
+      <c r="D37" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463110275/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="33" t="inlineStr">
+      <c r="A38" s="36" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B38" s="34" t="n">
+      <c r="B38" s="37" t="n">
         <v>46269</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1328,19 +1337,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D38" s="35" t="inlineStr">
+      <c r="D38" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463622979/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="33" t="inlineStr">
+      <c r="A39" s="36" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B39" s="34" t="n">
+      <c r="B39" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1348,19 +1357,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Bracknell, UK</t>
         </is>
       </c>
-      <c r="D39" s="35" t="inlineStr">
+      <c r="D39" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462849233/</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B40" s="34" t="n">
+      <c r="A40" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B40" s="37" t="n">
         <v>46270</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1368,19 +1377,19 @@
           <t>Hardware Engineer 2</t>
         </is>
       </c>
-      <c r="D40" s="35" t="inlineStr">
+      <c r="D40" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454834815/</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B41" s="34" t="n">
+      <c r="A41" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B41" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1388,19 +1397,19 @@
           <t>Principal SW Development Engineer</t>
         </is>
       </c>
-      <c r="D41" s="35" t="inlineStr">
+      <c r="D41" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453345730/</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="33" t="inlineStr">
+      <c r="A42" s="36" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B42" s="34" t="n">
+      <c r="B42" s="37" t="n">
         <v>46269</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1408,19 +1417,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D42" s="35" t="inlineStr">
+      <c r="D42" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463634192/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B43" s="34" t="n">
+      <c r="A43" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B43" s="37" t="n">
         <v>46270</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1428,19 +1437,19 @@
           <t>Associate Customer Experience Manager</t>
         </is>
       </c>
-      <c r="D43" s="35" t="inlineStr">
+      <c r="D43" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454599227/</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B44" s="34" t="n">
+      <c r="A44" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B44" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1448,19 +1457,19 @@
           <t>Sr Software QA Engineer</t>
         </is>
       </c>
-      <c r="D44" s="35" t="inlineStr">
+      <c r="D44" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453636185/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="33" t="inlineStr">
+      <c r="A45" s="36" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B45" s="34" t="n">
+      <c r="B45" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1468,19 +1477,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D45" s="35" t="inlineStr">
+      <c r="D45" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453092177/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="33" t="inlineStr">
+      <c r="A46" s="36" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B46" s="34" t="n">
+      <c r="B46" s="37" t="n">
         <v>46269</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1488,19 +1497,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D46" s="35" t="inlineStr">
+      <c r="D46" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463637144/</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B47" s="34" t="n">
+      <c r="A47" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B47" s="37" t="n">
         <v>46269</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1508,19 +1517,19 @@
           <t>Senior SW Development Engineer</t>
         </is>
       </c>
-      <c r="D47" s="35" t="inlineStr">
+      <c r="D47" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454303425/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B48" s="34" t="n">
+      <c r="A48" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B48" s="37" t="n">
         <v>46270</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1528,19 +1537,19 @@
           <t>Senior Staff Mechanical Engineer - Characterization Lead</t>
         </is>
       </c>
-      <c r="D48" s="35" t="inlineStr">
+      <c r="D48" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427645063/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="33" t="inlineStr">
+      <c r="A49" s="36" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B49" s="34" t="n">
+      <c r="B49" s="37" t="n">
         <v>46272</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1548,19 +1557,19 @@
           <t>QA Engineer 2</t>
         </is>
       </c>
-      <c r="D49" s="35" t="inlineStr">
+      <c r="D49" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464097498/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="33" t="inlineStr">
+      <c r="A50" s="36" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B50" s="34" t="n">
+      <c r="B50" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1568,19 +1577,19 @@
           <t>Software Development Engineer 2</t>
         </is>
       </c>
-      <c r="D50" s="35" t="inlineStr">
+      <c r="D50" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453360435/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="33" t="inlineStr">
+      <c r="A51" s="36" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B51" s="34" t="n">
+      <c r="B51" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1588,19 +1597,19 @@
           <t>Senior Software Development Engineer</t>
         </is>
       </c>
-      <c r="D51" s="35" t="inlineStr">
+      <c r="D51" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453371096/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B52" s="34" t="n">
+      <c r="A52" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B52" s="37" t="n">
         <v>46269</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -1608,19 +1617,19 @@
           <t>Sr SW Development Engineer</t>
         </is>
       </c>
-      <c r="D52" s="35" t="inlineStr">
+      <c r="D52" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463626373/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="33" t="inlineStr">
+      <c r="A53" s="36" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B53" s="34" t="n">
+      <c r="B53" s="37" t="n">
         <v>46269</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1628,19 +1637,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D53" s="35" t="inlineStr">
+      <c r="D53" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463633190/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="33" t="inlineStr">
+      <c r="A54" s="36" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B54" s="34" t="n">
+      <c r="B54" s="37" t="n">
         <v>46269</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1648,19 +1657,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D54" s="35" t="inlineStr">
+      <c r="D54" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463628391/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="33" t="inlineStr">
+      <c r="A55" s="36" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B55" s="34" t="n">
+      <c r="B55" s="37" t="n">
         <v>46270</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1668,19 +1677,19 @@
           <t>Sr IT Project Manager</t>
         </is>
       </c>
-      <c r="D55" s="35" t="inlineStr">
+      <c r="D55" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436188818/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="33" t="inlineStr">
+      <c r="A56" s="36" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B56" s="34" t="n">
+      <c r="B56" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1688,19 +1697,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D56" s="35" t="inlineStr">
+      <c r="D56" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453075275/</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B57" s="34" t="n">
+      <c r="A57" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B57" s="37" t="n">
         <v>46269</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1708,19 +1717,19 @@
           <t>Sr Software QA Engineer</t>
         </is>
       </c>
-      <c r="D57" s="35" t="inlineStr">
+      <c r="D57" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463370785/</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B58" s="34" t="n">
+      <c r="A58" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B58" s="37" t="n">
         <v>46270</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1728,19 +1737,19 @@
           <t>Material Handler 1 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D58" s="35" t="inlineStr">
+      <c r="D58" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455128356/</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="33" t="inlineStr">
+      <c r="A59" s="36" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="B59" s="34" t="n">
+      <c r="B59" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1748,19 +1757,19 @@
           <t>Territory Sales Manager - Brussels (Bilingual Flemish &amp; French)</t>
         </is>
       </c>
-      <c r="D59" s="35" t="inlineStr">
+      <c r="D59" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453090144/</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="33" t="inlineStr">
+      <c r="A60" s="36" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="B60" s="34" t="n">
+      <c r="B60" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1768,19 +1777,19 @@
           <t>Territory Sales Manager - Brussels (Bilingual Flemish &amp; French)</t>
         </is>
       </c>
-      <c r="D60" s="35" t="inlineStr">
+      <c r="D60" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453073289/</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="33" t="inlineStr">
+      <c r="A61" s="36" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B61" s="34" t="n">
+      <c r="B61" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1788,19 +1797,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D61" s="35" t="inlineStr">
+      <c r="D61" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453083196/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B62" s="34" t="n">
+      <c r="A62" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B62" s="37" t="n">
         <v>46269</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1808,19 +1817,19 @@
           <t>Principal Firmware Architect</t>
         </is>
       </c>
-      <c r="D62" s="35" t="inlineStr">
+      <c r="D62" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463626391/</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B63" s="34" t="n">
+      <c r="A63" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B63" s="37" t="n">
         <v>46269</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1828,19 +1837,19 @@
           <t>Software Development Engineer 1</t>
         </is>
       </c>
-      <c r="D63" s="35" t="inlineStr">
+      <c r="D63" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454097524/</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B64" s="34" t="n">
+      <c r="A64" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B64" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1848,19 +1857,19 @@
           <t>Sr Staff Endpoint Systems Engineer</t>
         </is>
       </c>
-      <c r="D64" s="35" t="inlineStr">
+      <c r="D64" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453090143/</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="33" t="inlineStr">
+      <c r="A65" s="36" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B65" s="34" t="n">
+      <c r="B65" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1868,19 +1877,19 @@
           <t>Supervisor Customer Advocacy</t>
         </is>
       </c>
-      <c r="D65" s="35" t="inlineStr">
+      <c r="D65" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454022788/</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="33" t="inlineStr">
+      <c r="A66" s="36" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B66" s="34" t="n">
+      <c r="B66" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1888,19 +1897,19 @@
           <t>Customer Service Representative (German-speaking)</t>
         </is>
       </c>
-      <c r="D66" s="35" t="inlineStr">
+      <c r="D66" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463120173/</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="33" t="inlineStr">
+      <c r="A67" s="36" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B67" s="34" t="n">
+      <c r="B67" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1908,19 +1917,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D67" s="35" t="inlineStr">
+      <c r="D67" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454019825/</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="33" t="inlineStr">
+      <c r="A68" s="36" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B68" s="34" t="n">
+      <c r="B68" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1928,19 +1937,19 @@
           <t>Customer Service Representative, French Speaker</t>
         </is>
       </c>
-      <c r="D68" s="35" t="inlineStr">
+      <c r="D68" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462772822/</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="33" t="inlineStr">
+      <c r="A69" s="36" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B69" s="34" t="n">
+      <c r="B69" s="37" t="n">
         <v>46269</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1948,19 +1957,19 @@
           <t>Intelligence Analyst - Geopolitical</t>
         </is>
       </c>
-      <c r="D69" s="35" t="inlineStr">
+      <c r="D69" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444046742/</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="33" t="inlineStr">
+      <c r="A70" s="36" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B70" s="34" t="n">
+      <c r="B70" s="37" t="n">
         <v>46270</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1968,19 +1977,19 @@
           <t>GBS Engagement &amp; Service Management Lead</t>
         </is>
       </c>
-      <c r="D70" s="35" t="inlineStr">
+      <c r="D70" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427554137/</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="33" t="inlineStr">
+      <c r="A71" s="36" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B71" s="34" t="n">
+      <c r="B71" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1988,19 +1997,19 @@
           <t>Contact Center Platform Analyst</t>
         </is>
       </c>
-      <c r="D71" s="35" t="inlineStr">
+      <c r="D71" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462857053/</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="33" t="inlineStr">
+      <c r="A72" s="36" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B72" s="34" t="n">
+      <c r="B72" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -2008,19 +2017,19 @@
           <t>Program Manager - AI Initiatives</t>
         </is>
       </c>
-      <c r="D72" s="35" t="inlineStr">
+      <c r="D72" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435119512/</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="33" t="inlineStr">
+      <c r="A73" s="36" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B73" s="34" t="n">
+      <c r="B73" s="37" t="n">
         <v>46269</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2028,19 +2037,19 @@
           <t>Senior Telecom Engineer (Genesys Cloud)</t>
         </is>
       </c>
-      <c r="D73" s="35" t="inlineStr">
+      <c r="D73" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463370784/</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="33" t="inlineStr">
+      <c r="A74" s="36" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B74" s="34" t="n">
+      <c r="B74" s="37" t="n">
         <v>46272</v>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -2048,19 +2057,19 @@
           <t>SW Development Engineer 1 - Android</t>
         </is>
       </c>
-      <c r="D74" s="35" t="inlineStr">
+      <c r="D74" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464353380/</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="33" t="inlineStr">
+      <c r="A75" s="36" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B75" s="34" t="n">
+      <c r="B75" s="37" t="n">
         <v>46272</v>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -2068,19 +2077,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D75" s="35" t="inlineStr">
+      <c r="D75" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464354416/</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="33" t="inlineStr">
+      <c r="A76" s="36" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B76" s="34" t="n">
+      <c r="B76" s="37" t="n">
         <v>46272</v>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -2088,19 +2097,19 @@
           <t>Staff Equipment Engineer</t>
         </is>
       </c>
-      <c r="D76" s="35" t="inlineStr">
+      <c r="D76" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455253909/</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="33" t="inlineStr">
+      <c r="A77" s="36" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B77" s="34" t="n">
+      <c r="B77" s="37" t="n">
         <v>46272</v>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -2108,19 +2117,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D77" s="35" t="inlineStr">
+      <c r="D77" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464339507/</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="33" t="inlineStr">
+      <c r="A78" s="36" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B78" s="34" t="n">
+      <c r="B78" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -2128,19 +2137,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D78" s="35" t="inlineStr">
+      <c r="D78" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453077256/</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="33" t="inlineStr">
+      <c r="A79" s="36" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B79" s="34" t="n">
+      <c r="B79" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -2148,19 +2157,19 @@
           <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
         </is>
       </c>
-      <c r="D79" s="35" t="inlineStr">
+      <c r="D79" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453079245/</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="33" t="inlineStr">
+      <c r="A80" s="36" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B80" s="34" t="n">
+      <c r="B80" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -2168,19 +2177,19 @@
           <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
         </is>
       </c>
-      <c r="D80" s="35" t="inlineStr">
+      <c r="D80" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453091134/</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="33" t="inlineStr">
+      <c r="A81" s="36" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B81" s="34" t="n">
+      <c r="B81" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2188,19 +2197,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D81" s="35" t="inlineStr">
+      <c r="D81" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082209/</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B82" s="34" t="n">
+      <c r="A82" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B82" s="37" t="n">
         <v>46272</v>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -2208,19 +2217,19 @@
           <t>Material Handler 2 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D82" s="35" t="inlineStr">
+      <c r="D82" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455289757/</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="33" t="inlineStr">
+      <c r="A83" s="36" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B83" s="34" t="n">
+      <c r="B83" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2228,19 +2237,19 @@
           <t>Procurement Ops Manager (IC)</t>
         </is>
       </c>
-      <c r="D83" s="35" t="inlineStr">
+      <c r="D83" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097103/</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="33" t="inlineStr">
+      <c r="A84" s="36" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B84" s="34" t="n">
+      <c r="B84" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -2248,19 +2257,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D84" s="35" t="inlineStr">
+      <c r="D84" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453093132/</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="33" t="inlineStr">
+      <c r="A85" s="36" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B85" s="34" t="n">
+      <c r="B85" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2268,19 +2277,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D85" s="35" t="inlineStr">
+      <c r="D85" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462835756/</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="33" t="inlineStr">
+      <c r="A86" s="36" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B86" s="34" t="n">
+      <c r="B86" s="37" t="n">
         <v>46272</v>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -2288,19 +2297,19 @@
           <t>Desktop Support Specialist 3</t>
         </is>
       </c>
-      <c r="D86" s="35" t="inlineStr">
+      <c r="D86" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4445930979/</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B87" s="34" t="n">
+      <c r="A87" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B87" s="37" t="n">
         <v>46267</v>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -2308,19 +2317,19 @@
           <t>Sr Staff Endpoint Systems Engineer</t>
         </is>
       </c>
-      <c r="D87" s="35" t="inlineStr">
+      <c r="D87" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453076275/</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B88" s="34" t="n">
+      <c r="A88" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B88" s="37" t="n">
         <v>46273</v>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -2328,19 +2337,19 @@
           <t>Material Handler 4 ( 2B Thur-Sat, every other Wednesday, Can work anytime from 5pm-5am )</t>
         </is>
       </c>
-      <c r="D88" s="35" t="inlineStr">
+      <c r="D88" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464432288/</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B89" s="34" t="n">
+      <c r="A89" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B89" s="37" t="n">
         <v>46273</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -2348,19 +2357,19 @@
           <t>Sr. Staff Technical Program Manager - Stelo</t>
         </is>
       </c>
-      <c r="D89" s="35" t="inlineStr">
+      <c r="D89" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455370480/</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B90" s="34" t="n">
+      <c r="A90" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B90" s="37" t="n">
         <v>46273</v>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -2368,19 +2377,19 @@
           <t>Sr Manager, Partnership Operations and Contracting</t>
         </is>
       </c>
-      <c r="D90" s="35" t="inlineStr">
+      <c r="D90" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464670623/</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B91" s="34" t="n">
+      <c r="A91" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B91" s="37" t="n">
         <v>46273</v>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -2388,19 +2397,19 @@
           <t>Manager Quality Compliance</t>
         </is>
       </c>
-      <c r="D91" s="35" t="inlineStr">
+      <c r="D91" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464662874/</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B92" s="34" t="n">
+      <c r="A92" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B92" s="37" t="n">
         <v>46273</v>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -2408,19 +2417,19 @@
           <t>Manager Systems Design Engineering</t>
         </is>
       </c>
-      <c r="D92" s="35" t="inlineStr">
+      <c r="D92" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464683405/</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B93" s="34" t="n">
+      <c r="A93" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B93" s="37" t="n">
         <v>46273</v>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -2428,19 +2437,19 @@
           <t>Sr. Federal Clinical Educator - East</t>
         </is>
       </c>
-      <c r="D93" s="35" t="inlineStr">
+      <c r="D93" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455357586/</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B94" s="34" t="n">
+      <c r="A94" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B94" s="37" t="n">
         <v>46274</v>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -2448,19 +2457,19 @@
           <t>Senior Staff Process Development Engineer</t>
         </is>
       </c>
-      <c r="D94" s="35" t="inlineStr">
+      <c r="D94" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464945232/</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B95" s="34" t="n">
+      <c r="A95" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B95" s="37" t="n">
         <v>46274</v>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -2468,19 +2477,19 @@
           <t>Production Chemist 3</t>
         </is>
       </c>
-      <c r="D95" s="35" t="inlineStr">
+      <c r="D95" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464932915/</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B96" s="34" t="n">
+      <c r="A96" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B96" s="37" t="n">
         <v>46269</v>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -2488,19 +2497,19 @@
           <t>SW Test Development Engineer 2</t>
         </is>
       </c>
-      <c r="D96" s="35" t="inlineStr">
+      <c r="D96" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436151688/</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B97" s="34" t="n">
+      <c r="A97" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B97" s="37" t="n">
         <v>46268</v>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -2508,19 +2517,19 @@
           <t>Global Brand Marketing Manager (Stelo)</t>
         </is>
       </c>
-      <c r="D97" s="35" t="inlineStr">
+      <c r="D97" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435306708/</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="33" t="inlineStr">
+      <c r="A98" s="36" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B98" s="34" t="n">
+      <c r="B98" s="37" t="n">
         <v>46273</v>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -2528,19 +2537,19 @@
           <t>Manager, SW System &amp; Solution Dev Engineer</t>
         </is>
       </c>
-      <c r="D98" s="35" t="inlineStr">
+      <c r="D98" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464452799/</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="33" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B99" s="34" t="n">
+      <c r="A99" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B99" s="37" t="n">
         <v>46273</v>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -2548,7 +2557,7 @@
           <t>Software QA Engineer 2</t>
         </is>
       </c>
-      <c r="D99" s="35" t="inlineStr">
+      <c r="D99" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464606837/</t>
         </is>
@@ -3034,8 +3043,68 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="39" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B124" s="40" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>SW Test Development Engineer 1</t>
+        </is>
+      </c>
+      <c r="D124" s="41" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465029007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="39" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B125" s="40" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>Sr. SW Test Development Engineer V&amp;V</t>
+        </is>
+      </c>
+      <c r="D125" s="41" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4387839555/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="39" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B126" s="40" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>Staff Software Test Development Engineer</t>
+        </is>
+      </c>
+      <c r="D126" s="41" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4388377406/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D123"/>
+  <autoFilter ref="A1:D126"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -3159,6 +3228,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId125"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -613,12 +613,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B2" s="40" t="n">
+      <c r="A2" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B2" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -626,19 +626,19 @@
           <t>Senior Director, Lean</t>
         </is>
       </c>
-      <c r="D2" s="41" t="inlineStr">
+      <c r="D2" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462725850/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B3" s="40" t="n">
+      <c r="A3" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B3" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -646,19 +646,19 @@
           <t>Staff Quality Compliance Specialist</t>
         </is>
       </c>
-      <c r="D3" s="41" t="inlineStr">
+      <c r="D3" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462730823/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B4" s="40" t="n">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B4" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -666,19 +666,19 @@
           <t>QC Inspector 4 - 1B Thur-Sat, every other Wednesday from 5am-5pm</t>
         </is>
       </c>
-      <c r="D4" s="41" t="inlineStr">
+      <c r="D4" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462726839/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B5" s="40" t="n">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -686,19 +686,19 @@
           <t>Platform Security Engineer 2</t>
         </is>
       </c>
-      <c r="D5" s="41" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462736772/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B6" s="40" t="n">
+      <c r="B6" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -706,19 +706,19 @@
           <t>APAC FP&amp;A Manager</t>
         </is>
       </c>
-      <c r="D6" s="41" t="inlineStr">
+      <c r="D6" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462770899/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B7" s="40" t="n">
+      <c r="B7" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -726,19 +726,19 @@
           <t>Commercial Analytics &amp; Operations Associate</t>
         </is>
       </c>
-      <c r="D7" s="41" t="inlineStr">
+      <c r="D7" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462778751/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B8" s="40" t="n">
+      <c r="A8" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -746,19 +746,19 @@
           <t>Document Control and Training Specialist 1</t>
         </is>
       </c>
-      <c r="D8" s="41" t="inlineStr">
+      <c r="D8" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463157831/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B9" s="40" t="n">
+      <c r="B9" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -766,19 +766,19 @@
           <t>Sr Supply Chain Analyst</t>
         </is>
       </c>
-      <c r="D9" s="41" t="inlineStr">
+      <c r="D9" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463169639/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="A10" s="42" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B10" s="40" t="n">
+      <c r="B10" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -786,19 +786,19 @@
           <t>IT Procurement Analyst</t>
         </is>
       </c>
-      <c r="D10" s="41" t="inlineStr">
+      <c r="D10" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463313428/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B11" s="40" t="n">
+      <c r="B11" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -806,19 +806,19 @@
           <t>IT Procurement Analyst</t>
         </is>
       </c>
-      <c r="D11" s="41" t="inlineStr">
+      <c r="D11" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463314400/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B12" s="40" t="n">
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B12" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -826,19 +826,19 @@
           <t>Product Manager, Patient Onboarding &amp; First Value</t>
         </is>
       </c>
-      <c r="D12" s="41" t="inlineStr">
+      <c r="D12" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453357502/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B13" s="40" t="n">
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="n">
         <v>46270</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -846,19 +846,19 @@
           <t>Staff Technical Program Manager - Innovation Ventures &amp; Sensor Technology</t>
         </is>
       </c>
-      <c r="D13" s="41" t="inlineStr">
+      <c r="D13" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454853005/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B14" s="40" t="n">
+      <c r="A14" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="n">
         <v>46270</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -866,19 +866,19 @@
           <t>Project Manager 2</t>
         </is>
       </c>
-      <c r="D14" s="41" t="inlineStr">
+      <c r="D14" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463687671/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B15" s="40" t="n">
+      <c r="A15" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -886,19 +886,19 @@
           <t>Senior Medical Affairs Manager – Value, Evidence, and Outcomes</t>
         </is>
       </c>
-      <c r="D15" s="41" t="inlineStr">
+      <c r="D15" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443448275/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B16" s="40" t="n">
+      <c r="A16" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -906,19 +906,19 @@
           <t>Director of Sensor Research</t>
         </is>
       </c>
-      <c r="D16" s="41" t="inlineStr">
+      <c r="D16" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427088373/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B17" s="40" t="n">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="n">
         <v>46271</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -926,19 +926,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D17" s="41" t="inlineStr">
+      <c r="D17" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436409441/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="39" t="inlineStr">
+      <c r="A18" s="42" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B18" s="40" t="n">
+      <c r="B18" s="43" t="n">
         <v>46270</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -946,19 +946,19 @@
           <t>Distributor Manager - Channel Excellence (MedTech)</t>
         </is>
       </c>
-      <c r="D18" s="41" t="inlineStr">
+      <c r="D18" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463683762/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B19" s="40" t="n">
+      <c r="A19" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B19" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -966,19 +966,19 @@
           <t>Territory Business Manager - Erie Pennsylvania</t>
         </is>
       </c>
-      <c r="D19" s="41" t="inlineStr">
+      <c r="D19" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440304526/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B20" s="40" t="n">
+      <c r="A20" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B20" s="43" t="n">
         <v>46270</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -986,19 +986,19 @@
           <t>QA Inspector 2 ( Dobson ) - 1A Sun- Tues, every other Wednesday, Can work anytime from 5am-5pm</t>
         </is>
       </c>
-      <c r="D20" s="41" t="inlineStr">
+      <c r="D20" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463691655/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="39" t="inlineStr">
+      <c r="A21" s="42" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B21" s="40" t="n">
+      <c r="B21" s="43" t="n">
         <v>46270</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1006,19 +1006,19 @@
           <t>Distributor Manager - Channel Excellence (MedTech)</t>
         </is>
       </c>
-      <c r="D21" s="41" t="inlineStr">
+      <c r="D21" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463684766/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B22" s="40" t="n">
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B22" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1026,19 +1026,19 @@
           <t>Sr. Clinical Customer Advocate</t>
         </is>
       </c>
-      <c r="D22" s="41" t="inlineStr">
+      <c r="D22" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463625584/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B23" s="40" t="n">
+      <c r="A23" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B23" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1046,19 +1046,19 @@
           <t>Staff Data Scientist</t>
         </is>
       </c>
-      <c r="D23" s="41" t="inlineStr">
+      <c r="D23" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463110275/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="39" t="inlineStr">
+      <c r="A24" s="42" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B24" s="40" t="n">
+      <c r="B24" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1066,19 +1066,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D24" s="41" t="inlineStr">
+      <c r="D24" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463622979/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="39" t="inlineStr">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B25" s="40" t="n">
+      <c r="B25" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1086,19 +1086,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Bracknell, UK</t>
         </is>
       </c>
-      <c r="D25" s="41" t="inlineStr">
+      <c r="D25" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462849233/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B26" s="40" t="n">
+      <c r="A26" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B26" s="43" t="n">
         <v>46270</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1106,19 +1106,19 @@
           <t>Hardware Engineer 2</t>
         </is>
       </c>
-      <c r="D26" s="41" t="inlineStr">
+      <c r="D26" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454834815/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B27" s="40" t="n">
+      <c r="A27" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B27" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1126,19 +1126,19 @@
           <t>Principal SW Development Engineer</t>
         </is>
       </c>
-      <c r="D27" s="41" t="inlineStr">
+      <c r="D27" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453345730/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="39" t="inlineStr">
+      <c r="A28" s="42" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B28" s="40" t="n">
+      <c r="B28" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1146,19 +1146,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D28" s="41" t="inlineStr">
+      <c r="D28" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463634192/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B29" s="40" t="n">
+      <c r="A29" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B29" s="43" t="n">
         <v>46270</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1166,19 +1166,19 @@
           <t>Associate Customer Experience Manager</t>
         </is>
       </c>
-      <c r="D29" s="41" t="inlineStr">
+      <c r="D29" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454599227/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B30" s="40" t="n">
+      <c r="A30" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B30" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1186,19 +1186,19 @@
           <t>Sr Software QA Engineer</t>
         </is>
       </c>
-      <c r="D30" s="41" t="inlineStr">
+      <c r="D30" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453636185/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="39" t="inlineStr">
+      <c r="A31" s="42" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B31" s="40" t="n">
+      <c r="B31" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1206,19 +1206,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D31" s="41" t="inlineStr">
+      <c r="D31" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463637144/</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B32" s="40" t="n">
+      <c r="A32" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B32" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1226,19 +1226,19 @@
           <t>Senior SW Development Engineer</t>
         </is>
       </c>
-      <c r="D32" s="41" t="inlineStr">
+      <c r="D32" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454303425/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B33" s="40" t="n">
+      <c r="A33" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B33" s="43" t="n">
         <v>46270</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1246,19 +1246,19 @@
           <t>Senior Staff Mechanical Engineer - Characterization Lead</t>
         </is>
       </c>
-      <c r="D33" s="41" t="inlineStr">
+      <c r="D33" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427645063/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="39" t="inlineStr">
+      <c r="A34" s="42" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B34" s="40" t="n">
+      <c r="B34" s="43" t="n">
         <v>46272</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1266,19 +1266,19 @@
           <t>QA Engineer 2</t>
         </is>
       </c>
-      <c r="D34" s="41" t="inlineStr">
+      <c r="D34" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464097498/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="39" t="inlineStr">
+      <c r="A35" s="42" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B35" s="40" t="n">
+      <c r="B35" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1286,19 +1286,19 @@
           <t>Software Development Engineer 2</t>
         </is>
       </c>
-      <c r="D35" s="41" t="inlineStr">
+      <c r="D35" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453360435/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="39" t="inlineStr">
+      <c r="A36" s="42" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B36" s="40" t="n">
+      <c r="B36" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1306,19 +1306,19 @@
           <t>Senior Software Development Engineer</t>
         </is>
       </c>
-      <c r="D36" s="41" t="inlineStr">
+      <c r="D36" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453371096/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B37" s="40" t="n">
+      <c r="A37" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B37" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1326,19 +1326,19 @@
           <t>Sr SW Development Engineer</t>
         </is>
       </c>
-      <c r="D37" s="41" t="inlineStr">
+      <c r="D37" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463626373/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="39" t="inlineStr">
+      <c r="A38" s="42" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B38" s="40" t="n">
+      <c r="B38" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1346,19 +1346,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D38" s="41" t="inlineStr">
+      <c r="D38" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463633190/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="39" t="inlineStr">
+      <c r="A39" s="42" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B39" s="40" t="n">
+      <c r="B39" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1366,19 +1366,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D39" s="41" t="inlineStr">
+      <c r="D39" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463628391/</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="39" t="inlineStr">
+      <c r="A40" s="42" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B40" s="40" t="n">
+      <c r="B40" s="43" t="n">
         <v>46270</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1386,19 +1386,19 @@
           <t>Sr IT Project Manager</t>
         </is>
       </c>
-      <c r="D40" s="41" t="inlineStr">
+      <c r="D40" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436188818/</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B41" s="40" t="n">
+      <c r="A41" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B41" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1406,19 +1406,19 @@
           <t>Sr Software QA Engineer</t>
         </is>
       </c>
-      <c r="D41" s="41" t="inlineStr">
+      <c r="D41" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463370785/</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B42" s="40" t="n">
+      <c r="A42" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B42" s="43" t="n">
         <v>46270</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1426,19 +1426,19 @@
           <t>Material Handler 1 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D42" s="41" t="inlineStr">
+      <c r="D42" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455128356/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B43" s="40" t="n">
+      <c r="A43" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B43" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1446,19 +1446,19 @@
           <t>Principal Firmware Architect</t>
         </is>
       </c>
-      <c r="D43" s="41" t="inlineStr">
+      <c r="D43" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463626391/</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B44" s="40" t="n">
+      <c r="A44" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B44" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1466,19 +1466,19 @@
           <t>Software Development Engineer 1</t>
         </is>
       </c>
-      <c r="D44" s="41" t="inlineStr">
+      <c r="D44" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454097524/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="39" t="inlineStr">
+      <c r="A45" s="42" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B45" s="40" t="n">
+      <c r="B45" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1486,19 +1486,19 @@
           <t>Supervisor Customer Advocacy</t>
         </is>
       </c>
-      <c r="D45" s="41" t="inlineStr">
+      <c r="D45" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454022788/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="39" t="inlineStr">
+      <c r="A46" s="42" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B46" s="40" t="n">
+      <c r="B46" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1506,19 +1506,19 @@
           <t>Customer Service Representative (German-speaking)</t>
         </is>
       </c>
-      <c r="D46" s="41" t="inlineStr">
+      <c r="D46" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463120173/</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="39" t="inlineStr">
+      <c r="A47" s="42" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B47" s="40" t="n">
+      <c r="B47" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1526,19 +1526,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D47" s="41" t="inlineStr">
+      <c r="D47" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454019825/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="39" t="inlineStr">
+      <c r="A48" s="42" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B48" s="40" t="n">
+      <c r="B48" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1546,19 +1546,19 @@
           <t>Customer Service Representative, French Speaker</t>
         </is>
       </c>
-      <c r="D48" s="41" t="inlineStr">
+      <c r="D48" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462772822/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="39" t="inlineStr">
+      <c r="A49" s="42" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B49" s="40" t="n">
+      <c r="B49" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1566,19 +1566,19 @@
           <t>Intelligence Analyst - Geopolitical</t>
         </is>
       </c>
-      <c r="D49" s="41" t="inlineStr">
+      <c r="D49" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444046742/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="39" t="inlineStr">
+      <c r="A50" s="42" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B50" s="40" t="n">
+      <c r="B50" s="43" t="n">
         <v>46270</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1586,19 +1586,19 @@
           <t>GBS Engagement &amp; Service Management Lead</t>
         </is>
       </c>
-      <c r="D50" s="41" t="inlineStr">
+      <c r="D50" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427554137/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="39" t="inlineStr">
+      <c r="A51" s="42" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B51" s="40" t="n">
+      <c r="B51" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1606,19 +1606,19 @@
           <t>Contact Center Platform Analyst</t>
         </is>
       </c>
-      <c r="D51" s="41" t="inlineStr">
+      <c r="D51" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462857053/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="39" t="inlineStr">
+      <c r="A52" s="42" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B52" s="40" t="n">
+      <c r="B52" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -1626,19 +1626,19 @@
           <t>Program Manager - AI Initiatives</t>
         </is>
       </c>
-      <c r="D52" s="41" t="inlineStr">
+      <c r="D52" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435119512/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="39" t="inlineStr">
+      <c r="A53" s="42" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B53" s="40" t="n">
+      <c r="B53" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1646,19 +1646,19 @@
           <t>Senior Telecom Engineer (Genesys Cloud)</t>
         </is>
       </c>
-      <c r="D53" s="41" t="inlineStr">
+      <c r="D53" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463370784/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="39" t="inlineStr">
+      <c r="A54" s="42" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B54" s="40" t="n">
+      <c r="B54" s="43" t="n">
         <v>46272</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1666,19 +1666,19 @@
           <t>SW Development Engineer 1 - Android</t>
         </is>
       </c>
-      <c r="D54" s="41" t="inlineStr">
+      <c r="D54" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464353380/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="39" t="inlineStr">
+      <c r="A55" s="42" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B55" s="40" t="n">
+      <c r="B55" s="43" t="n">
         <v>46272</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1686,19 +1686,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D55" s="41" t="inlineStr">
+      <c r="D55" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464354416/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="39" t="inlineStr">
+      <c r="A56" s="42" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B56" s="40" t="n">
+      <c r="B56" s="43" t="n">
         <v>46272</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1706,19 +1706,19 @@
           <t>Staff Equipment Engineer</t>
         </is>
       </c>
-      <c r="D56" s="41" t="inlineStr">
+      <c r="D56" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455253909/</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="39" t="inlineStr">
+      <c r="A57" s="42" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B57" s="40" t="n">
+      <c r="B57" s="43" t="n">
         <v>46272</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1726,19 +1726,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D57" s="41" t="inlineStr">
+      <c r="D57" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464339507/</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B58" s="40" t="n">
+      <c r="A58" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B58" s="43" t="n">
         <v>46272</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1746,19 +1746,19 @@
           <t>Material Handler 2 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D58" s="41" t="inlineStr">
+      <c r="D58" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455289757/</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="39" t="inlineStr">
+      <c r="A59" s="42" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B59" s="40" t="n">
+      <c r="B59" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1766,19 +1766,19 @@
           <t>Territory Sales Manager - Galicia</t>
         </is>
       </c>
-      <c r="D59" s="41" t="inlineStr">
+      <c r="D59" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462835756/</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="39" t="inlineStr">
+      <c r="A60" s="42" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B60" s="40" t="n">
+      <c r="B60" s="43" t="n">
         <v>46272</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1786,19 +1786,19 @@
           <t>Desktop Support Specialist 3</t>
         </is>
       </c>
-      <c r="D60" s="41" t="inlineStr">
+      <c r="D60" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4445930979/</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B61" s="40" t="n">
+      <c r="A61" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B61" s="43" t="n">
         <v>46273</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1806,19 +1806,19 @@
           <t>Material Handler 4 ( 2B Thur-Sat, every other Wednesday, Can work anytime from 5pm-5am )</t>
         </is>
       </c>
-      <c r="D61" s="41" t="inlineStr">
+      <c r="D61" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464432288/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B62" s="40" t="n">
+      <c r="A62" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B62" s="43" t="n">
         <v>46273</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1826,19 +1826,19 @@
           <t>Sr. Staff Technical Program Manager - Stelo</t>
         </is>
       </c>
-      <c r="D62" s="41" t="inlineStr">
+      <c r="D62" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455370480/</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B63" s="40" t="n">
+      <c r="A63" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B63" s="43" t="n">
         <v>46273</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1846,19 +1846,19 @@
           <t>Sr Manager, Partnership Operations and Contracting</t>
         </is>
       </c>
-      <c r="D63" s="41" t="inlineStr">
+      <c r="D63" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464670623/</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B64" s="40" t="n">
+      <c r="A64" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B64" s="43" t="n">
         <v>46273</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1866,19 +1866,19 @@
           <t>Manager Quality Compliance</t>
         </is>
       </c>
-      <c r="D64" s="41" t="inlineStr">
+      <c r="D64" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464662874/</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B65" s="40" t="n">
+      <c r="A65" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B65" s="43" t="n">
         <v>46273</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1886,19 +1886,19 @@
           <t>Manager Systems Design Engineering</t>
         </is>
       </c>
-      <c r="D65" s="41" t="inlineStr">
+      <c r="D65" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464683405/</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B66" s="40" t="n">
+      <c r="A66" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B66" s="43" t="n">
         <v>46273</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1906,19 +1906,19 @@
           <t>Sr. Federal Clinical Educator - East</t>
         </is>
       </c>
-      <c r="D66" s="41" t="inlineStr">
+      <c r="D66" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455357586/</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B67" s="40" t="n">
+      <c r="A67" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B67" s="43" t="n">
         <v>46274</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1926,19 +1926,19 @@
           <t>Senior Staff Process Development Engineer</t>
         </is>
       </c>
-      <c r="D67" s="41" t="inlineStr">
+      <c r="D67" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464945232/</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B68" s="40" t="n">
+      <c r="A68" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B68" s="43" t="n">
         <v>46274</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1946,19 +1946,19 @@
           <t>Production Chemist 3</t>
         </is>
       </c>
-      <c r="D68" s="41" t="inlineStr">
+      <c r="D68" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464932915/</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B69" s="40" t="n">
+      <c r="A69" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B69" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1966,19 +1966,19 @@
           <t>SW Test Development Engineer 2</t>
         </is>
       </c>
-      <c r="D69" s="41" t="inlineStr">
+      <c r="D69" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436151688/</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B70" s="40" t="n">
+      <c r="A70" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B70" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1986,19 +1986,19 @@
           <t>Global Brand Marketing Manager (Stelo)</t>
         </is>
       </c>
-      <c r="D70" s="41" t="inlineStr">
+      <c r="D70" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435306708/</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="39" t="inlineStr">
+      <c r="A71" s="42" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B71" s="40" t="n">
+      <c r="B71" s="43" t="n">
         <v>46273</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -2006,19 +2006,19 @@
           <t>Manager, SW System &amp; Solution Dev Engineer</t>
         </is>
       </c>
-      <c r="D71" s="41" t="inlineStr">
+      <c r="D71" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464452799/</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B72" s="40" t="n">
+      <c r="A72" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B72" s="43" t="n">
         <v>46273</v>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -2026,19 +2026,19 @@
           <t>Software QA Engineer 2</t>
         </is>
       </c>
-      <c r="D72" s="41" t="inlineStr">
+      <c r="D72" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464606837/</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="39" t="inlineStr">
+      <c r="A73" s="42" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B73" s="40" t="n">
+      <c r="B73" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2046,19 +2046,19 @@
           <t>Sr Buyer</t>
         </is>
       </c>
-      <c r="D73" s="41" t="inlineStr">
+      <c r="D73" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454535222/</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="39" t="inlineStr">
+      <c r="A74" s="42" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B74" s="40" t="n">
+      <c r="B74" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -2066,19 +2066,19 @@
           <t>Planning Manager</t>
         </is>
       </c>
-      <c r="D74" s="41" t="inlineStr">
+      <c r="D74" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454556094/</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="39" t="inlineStr">
+      <c r="A75" s="42" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B75" s="40" t="n">
+      <c r="B75" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -2086,19 +2086,19 @@
           <t>Production Planner</t>
         </is>
       </c>
-      <c r="D75" s="41" t="inlineStr">
+      <c r="D75" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454538160/</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="39" t="inlineStr">
+      <c r="A76" s="42" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B76" s="40" t="n">
+      <c r="B76" s="43" t="n">
         <v>46273</v>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -2106,19 +2106,19 @@
           <t>Quality Technician 2 Back End Days</t>
         </is>
       </c>
-      <c r="D76" s="41" t="inlineStr">
+      <c r="D76" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464613132/</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="39" t="inlineStr">
+      <c r="A77" s="42" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B77" s="40" t="n">
+      <c r="B77" s="43" t="n">
         <v>46273</v>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -2126,19 +2126,19 @@
           <t>Process Technician 2 (Front End Night Shift)</t>
         </is>
       </c>
-      <c r="D77" s="41" t="inlineStr">
+      <c r="D77" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455755200/</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="39" t="inlineStr">
+      <c r="A78" s="42" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B78" s="40" t="n">
+      <c r="B78" s="43" t="n">
         <v>46272</v>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -2146,19 +2146,19 @@
           <t>Supervisor Process Engineering</t>
         </is>
       </c>
-      <c r="D78" s="41" t="inlineStr">
+      <c r="D78" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464338496/</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="39" t="inlineStr">
+      <c r="A79" s="42" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B79" s="40" t="n">
+      <c r="B79" s="43" t="n">
         <v>46272</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -2166,19 +2166,19 @@
           <t>Sr Production Supervisor (Front End Night Shift)</t>
         </is>
       </c>
-      <c r="D79" s="41" t="inlineStr">
+      <c r="D79" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455302580/</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="39" t="inlineStr">
+      <c r="A80" s="42" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B80" s="40" t="n">
+      <c r="B80" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -2186,19 +2186,19 @@
           <t>Engineering Technician 4 (Monday to Friday days)</t>
         </is>
       </c>
-      <c r="D80" s="41" t="inlineStr">
+      <c r="D80" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463368770/</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="39" t="inlineStr">
+      <c r="A81" s="42" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B81" s="40" t="n">
+      <c r="B81" s="43" t="n">
         <v>46270</v>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2206,19 +2206,19 @@
           <t>Engineering Technician 3 (Front End Day Shift)</t>
         </is>
       </c>
-      <c r="D81" s="41" t="inlineStr">
+      <c r="D81" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463698028/</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="39" t="inlineStr">
+      <c r="A82" s="42" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B82" s="40" t="n">
+      <c r="B82" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -2226,19 +2226,19 @@
           <t>QA Engineer Digital Systems</t>
         </is>
       </c>
-      <c r="D82" s="41" t="inlineStr">
+      <c r="D82" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444460213/</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="39" t="inlineStr">
+      <c r="A83" s="42" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B83" s="40" t="n">
+      <c r="B83" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2246,19 +2246,19 @@
           <t>Lab Supervisor (Manufacturing) - Back End Day Shift</t>
         </is>
       </c>
-      <c r="D83" s="41" t="inlineStr">
+      <c r="D83" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463359959/</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="39" t="inlineStr">
+      <c r="A84" s="42" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B84" s="40" t="n">
+      <c r="B84" s="43" t="n">
         <v>46270</v>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -2266,19 +2266,19 @@
           <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
         </is>
       </c>
-      <c r="D84" s="41" t="inlineStr">
+      <c r="D84" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463699027/</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="39" t="inlineStr">
+      <c r="A85" s="42" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B85" s="40" t="n">
+      <c r="B85" s="43" t="n">
         <v>46272</v>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2286,19 +2286,19 @@
           <t>Lab Technician 3 (Chemistry)</t>
         </is>
       </c>
-      <c r="D85" s="41" t="inlineStr">
+      <c r="D85" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464341469/</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="39" t="inlineStr">
+      <c r="A86" s="42" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="B86" s="40" t="n">
+      <c r="B86" s="43" t="n">
         <v>46272</v>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -2306,19 +2306,19 @@
           <t>Medical Representative MR 医療機器 糖尿病領域 営業職</t>
         </is>
       </c>
-      <c r="D86" s="41" t="inlineStr">
+      <c r="D86" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455248893/</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="39" t="inlineStr">
+      <c r="A87" s="42" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B87" s="40" t="n">
+      <c r="B87" s="43" t="n">
         <v>46271</v>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -2326,19 +2326,19 @@
           <t>UI Designer (Design System)</t>
         </is>
       </c>
-      <c r="D87" s="41" t="inlineStr">
+      <c r="D87" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427632128/</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="39" t="inlineStr">
+      <c r="A88" s="42" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B88" s="40" t="n">
+      <c r="B88" s="43" t="n">
         <v>46268</v>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -2346,19 +2346,19 @@
           <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
         </is>
       </c>
-      <c r="D88" s="41" t="inlineStr">
+      <c r="D88" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443109225/</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="39" t="inlineStr">
+      <c r="A89" s="42" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B89" s="40" t="n">
+      <c r="B89" s="43" t="n">
         <v>46269</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -2366,19 +2366,19 @@
           <t>Senior Warehouse Operative - Day Shift</t>
         </is>
       </c>
-      <c r="D89" s="41" t="inlineStr">
+      <c r="D89" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463635156/</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="39" t="inlineStr">
+      <c r="A90" s="42" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B90" s="40" t="n">
+      <c r="B90" s="43" t="n">
         <v>46273</v>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -2386,19 +2386,19 @@
           <t>Senior Accountant/Bilanzbuchhalter (m/w/d) - Healthcare</t>
         </is>
       </c>
-      <c r="D90" s="41" t="inlineStr">
+      <c r="D90" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455750299/</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="39" t="inlineStr">
+      <c r="A91" s="42" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="B91" s="40" t="n">
+      <c r="B91" s="43" t="n">
         <v>46272</v>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -2406,19 +2406,19 @@
           <t>Territory Business Manager</t>
         </is>
       </c>
-      <c r="D91" s="41" t="inlineStr">
+      <c r="D91" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464350389/</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="39" t="inlineStr">
+      <c r="A92" s="42" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B92" s="40" t="n">
+      <c r="B92" s="43" t="n">
         <v>46274</v>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -2426,19 +2426,19 @@
           <t>Sr Technical Writer</t>
         </is>
       </c>
-      <c r="D92" s="41" t="inlineStr">
+      <c r="D92" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465024024/</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="39" t="inlineStr">
+      <c r="A93" s="42" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B93" s="40" t="n">
+      <c r="B93" s="43" t="n">
         <v>46274</v>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -2446,19 +2446,19 @@
           <t>Sr SW Development Engineer - IOS</t>
         </is>
       </c>
-      <c r="D93" s="41" t="inlineStr">
+      <c r="D93" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465020025/</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B94" s="40" t="n">
+      <c r="A94" s="42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B94" s="43" t="n">
         <v>46272</v>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -2466,19 +2466,19 @@
           <t>Material Handler 2 ( RDC ) - Nights 2A and 2B</t>
         </is>
       </c>
-      <c r="D94" s="41" t="inlineStr">
+      <c r="D94" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455289751/</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="39" t="inlineStr">
+      <c r="A95" s="42" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B95" s="40" t="n">
+      <c r="B95" s="43" t="n">
         <v>46273</v>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -2486,19 +2486,19 @@
           <t>SW Development Engineer 2 - Android</t>
         </is>
       </c>
-      <c r="D95" s="41" t="inlineStr">
+      <c r="D95" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464610755/</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="39" t="inlineStr">
+      <c r="A96" s="42" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B96" s="40" t="n">
+      <c r="B96" s="43" t="n">
         <v>46273</v>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -2506,19 +2506,19 @@
           <t>Sr Enterprise Developer (Power Platform Developer)</t>
         </is>
       </c>
-      <c r="D96" s="41" t="inlineStr">
+      <c r="D96" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455767052/</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="39" t="inlineStr">
+      <c r="A97" s="42" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B97" s="40" t="n">
+      <c r="B97" s="43" t="n">
         <v>46274</v>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -2526,19 +2526,19 @@
           <t>SW Test Development Engineer 1</t>
         </is>
       </c>
-      <c r="D97" s="41" t="inlineStr">
+      <c r="D97" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465029007/</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="39" t="inlineStr">
+      <c r="A98" s="42" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B98" s="40" t="n">
+      <c r="B98" s="43" t="n">
         <v>46273</v>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -2546,19 +2546,19 @@
           <t>Sr. SW Test Development Engineer V&amp;V</t>
         </is>
       </c>
-      <c r="D98" s="41" t="inlineStr">
+      <c r="D98" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387839555/</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="39" t="inlineStr">
+      <c r="A99" s="42" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B99" s="40" t="n">
+      <c r="B99" s="43" t="n">
         <v>46273</v>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -2566,7 +2566,7 @@
           <t>Staff Software Test Development Engineer</t>
         </is>
       </c>
-      <c r="D99" s="41" t="inlineStr">
+      <c r="D99" s="44" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4388377406/</t>
         </is>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$156</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -581,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -619,116 +628,116 @@
         </is>
       </c>
       <c r="B2" s="43" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Senior Director, Lean</t>
+          <t>Document Control and Training Specialist 1</t>
         </is>
       </c>
       <c r="D2" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4462725850/</t>
+          <t>https://www.linkedin.com/jobs/view/4463157831/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B3" s="43" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Staff Quality Compliance Specialist</t>
+          <t>Sr Supply Chain Analyst</t>
         </is>
       </c>
       <c r="D3" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4462730823/</t>
+          <t>https://www.linkedin.com/jobs/view/4463169639/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B4" s="43" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>QC Inspector 4 - 1B Thur-Sat, every other Wednesday from 5am-5pm</t>
+          <t>IT Procurement Analyst</t>
         </is>
       </c>
       <c r="D4" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4462726839/</t>
+          <t>https://www.linkedin.com/jobs/view/4463313428/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Platform Security Engineer 2</t>
+          <t>IT Procurement Analyst</t>
         </is>
       </c>
       <c r="D5" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4462736772/</t>
+          <t>https://www.linkedin.com/jobs/view/4463314400/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="42" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B6" s="43" t="n">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>APAC FP&amp;A Manager</t>
+          <t>Staff Technical Program Manager - Innovation Ventures &amp; Sensor Technology</t>
         </is>
       </c>
       <c r="D6" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4462770899/</t>
+          <t>https://www.linkedin.com/jobs/view/4454853005/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="42" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B7" s="43" t="n">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Commercial Analytics &amp; Operations Associate</t>
+          <t>Project Manager 2</t>
         </is>
       </c>
       <c r="D7" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4462778751/</t>
+          <t>https://www.linkedin.com/jobs/view/4463687671/</t>
         </is>
       </c>
     </row>
@@ -743,92 +752,92 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Document Control and Training Specialist 1</t>
+          <t>Senior Medical Affairs Manager – Value, Evidence, and Outcomes</t>
         </is>
       </c>
       <c r="D8" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463157831/</t>
+          <t>https://www.linkedin.com/jobs/view/4443448275/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="42" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B9" s="43" t="n">
-        <v>46269</v>
+        <v>46271</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Sr Supply Chain Analyst</t>
+          <t>Staff QA Engineer</t>
         </is>
       </c>
       <c r="D9" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463169639/</t>
+          <t>https://www.linkedin.com/jobs/view/4436409441/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="42" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B10" s="43" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>IT Procurement Analyst</t>
+          <t>Distributor Manager - Channel Excellence (MedTech)</t>
         </is>
       </c>
       <c r="D10" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463313428/</t>
+          <t>https://www.linkedin.com/jobs/view/4463683762/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="42" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B11" s="43" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>IT Procurement Analyst</t>
+          <t>QA Inspector 2 ( Dobson ) - 1A Sun- Tues, every other Wednesday, Can work anytime from 5am-5pm</t>
         </is>
       </c>
       <c r="D11" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463314400/</t>
+          <t>https://www.linkedin.com/jobs/view/4463691655/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B12" s="43" t="n">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Product Manager, Patient Onboarding &amp; First Value</t>
+          <t>Distributor Manager - Channel Excellence (MedTech)</t>
         </is>
       </c>
       <c r="D12" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4453357502/</t>
+          <t>https://www.linkedin.com/jobs/view/4463684766/</t>
         </is>
       </c>
     </row>
@@ -839,36 +848,36 @@
         </is>
       </c>
       <c r="B13" s="43" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Staff Technical Program Manager - Innovation Ventures &amp; Sensor Technology</t>
+          <t>Sr. Clinical Customer Advocate</t>
         </is>
       </c>
       <c r="D13" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4454853005/</t>
+          <t>https://www.linkedin.com/jobs/view/4463625584/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B14" s="43" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Project Manager 2</t>
+          <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
       <c r="D14" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463687671/</t>
+          <t>https://www.linkedin.com/jobs/view/4463622979/</t>
         </is>
       </c>
     </row>
@@ -879,36 +888,36 @@
         </is>
       </c>
       <c r="B15" s="43" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Senior Medical Affairs Manager – Value, Evidence, and Outcomes</t>
+          <t>Hardware Engineer 2</t>
         </is>
       </c>
       <c r="D15" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4443448275/</t>
+          <t>https://www.linkedin.com/jobs/view/4454834815/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B16" s="43" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Director of Sensor Research</t>
+          <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
       <c r="D16" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4427088373/</t>
+          <t>https://www.linkedin.com/jobs/view/4463634192/</t>
         </is>
       </c>
     </row>
@@ -919,36 +928,36 @@
         </is>
       </c>
       <c r="B17" s="43" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Staff QA Engineer</t>
+          <t>Associate Customer Experience Manager</t>
         </is>
       </c>
       <c r="D17" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4436409441/</t>
+          <t>https://www.linkedin.com/jobs/view/4454599227/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="42" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B18" s="43" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Distributor Manager - Channel Excellence (MedTech)</t>
+          <t>Senior Forecasting Analyst</t>
         </is>
       </c>
       <c r="D18" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463683762/</t>
+          <t>https://www.linkedin.com/jobs/view/4463637144/</t>
         </is>
       </c>
     </row>
@@ -959,16 +968,16 @@
         </is>
       </c>
       <c r="B19" s="43" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Territory Business Manager - Erie Pennsylvania</t>
+          <t>Senior SW Development Engineer</t>
         </is>
       </c>
       <c r="D19" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4440304526/</t>
+          <t>https://www.linkedin.com/jobs/view/4454303425/</t>
         </is>
       </c>
     </row>
@@ -983,32 +992,32 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>QA Inspector 2 ( Dobson ) - 1A Sun- Tues, every other Wednesday, Can work anytime from 5am-5pm</t>
+          <t>Senior Staff Mechanical Engineer - Characterization Lead</t>
         </is>
       </c>
       <c r="D20" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463691655/</t>
+          <t>https://www.linkedin.com/jobs/view/4427645063/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="42" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B21" s="43" t="n">
-        <v>46270</v>
+        <v>46272</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Distributor Manager - Channel Excellence (MedTech)</t>
+          <t>QA Engineer 2</t>
         </is>
       </c>
       <c r="D21" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463684766/</t>
+          <t>https://www.linkedin.com/jobs/view/4464097498/</t>
         </is>
       </c>
     </row>
@@ -1023,39 +1032,39 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Sr. Clinical Customer Advocate</t>
+          <t>Sr SW Development Engineer</t>
         </is>
       </c>
       <c r="D22" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463625584/</t>
+          <t>https://www.linkedin.com/jobs/view/4463626373/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B23" s="43" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Staff Data Scientist</t>
+          <t>Senior Forecasting Analyst</t>
         </is>
       </c>
       <c r="D23" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463110275/</t>
+          <t>https://www.linkedin.com/jobs/view/4463633190/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="42" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B24" s="43" t="n">
@@ -1063,32 +1072,32 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Senior Forecasting Analyst – Healthcare - UK</t>
+          <t>Senior Forecasting Analyst</t>
         </is>
       </c>
       <c r="D24" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463622979/</t>
+          <t>https://www.linkedin.com/jobs/view/4463628391/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="42" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B25" s="43" t="n">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Bracknell, UK</t>
+          <t>Sr IT Project Manager</t>
         </is>
       </c>
       <c r="D25" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4462849233/</t>
+          <t>https://www.linkedin.com/jobs/view/4436188818/</t>
         </is>
       </c>
     </row>
@@ -1099,16 +1108,16 @@
         </is>
       </c>
       <c r="B26" s="43" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Hardware Engineer 2</t>
+          <t>Sr Software QA Engineer</t>
         </is>
       </c>
       <c r="D26" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4454834815/</t>
+          <t>https://www.linkedin.com/jobs/view/4463370785/</t>
         </is>
       </c>
     </row>
@@ -1119,23 +1128,23 @@
         </is>
       </c>
       <c r="B27" s="43" t="n">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Principal SW Development Engineer</t>
+          <t>Material Handler 1 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
       <c r="D27" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4453345730/</t>
+          <t>https://www.linkedin.com/jobs/view/4455128356/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="42" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B28" s="43" t="n">
@@ -1143,12 +1152,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Senior Forecasting Analyst – Healthcare - UK</t>
+          <t>Principal Firmware Architect</t>
         </is>
       </c>
       <c r="D28" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463634192/</t>
+          <t>https://www.linkedin.com/jobs/view/4463626391/</t>
         </is>
       </c>
     </row>
@@ -1159,63 +1168,63 @@
         </is>
       </c>
       <c r="B29" s="43" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Associate Customer Experience Manager</t>
+          <t>Software Development Engineer 1</t>
         </is>
       </c>
       <c r="D29" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4454599227/</t>
+          <t>https://www.linkedin.com/jobs/view/4454097524/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B30" s="43" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Sr Software QA Engineer</t>
+          <t>Intelligence Analyst - Geopolitical</t>
         </is>
       </c>
       <c r="D30" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4453636185/</t>
+          <t>https://www.linkedin.com/jobs/view/4444046742/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="42" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B31" s="43" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Senior Forecasting Analyst</t>
+          <t>GBS Engagement &amp; Service Management Lead</t>
         </is>
       </c>
       <c r="D31" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463637144/</t>
+          <t>https://www.linkedin.com/jobs/view/4427554137/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B32" s="43" t="n">
@@ -1223,39 +1232,39 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Senior SW Development Engineer</t>
+          <t>Senior Telecom Engineer (Genesys Cloud)</t>
         </is>
       </c>
       <c r="D32" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4454303425/</t>
+          <t>https://www.linkedin.com/jobs/view/4463370784/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B33" s="43" t="n">
-        <v>46270</v>
+        <v>46272</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Senior Staff Mechanical Engineer - Characterization Lead</t>
+          <t>SW Development Engineer 1 - Android</t>
         </is>
       </c>
       <c r="D33" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4427645063/</t>
+          <t>https://www.linkedin.com/jobs/view/4464353380/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="42" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B34" s="43" t="n">
@@ -1263,52 +1272,52 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer 2</t>
+          <t>Customer Advocacy Generalist</t>
         </is>
       </c>
       <c r="D34" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4464097498/</t>
+          <t>https://www.linkedin.com/jobs/view/4464354416/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="42" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B35" s="43" t="n">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Staff Equipment Engineer</t>
         </is>
       </c>
       <c r="D35" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4453360435/</t>
+          <t>https://www.linkedin.com/jobs/view/4455253909/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="42" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B36" s="43" t="n">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Customer Advocacy Generalist</t>
         </is>
       </c>
       <c r="D36" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4453371096/</t>
+          <t>https://www.linkedin.com/jobs/view/4464339507/</t>
         </is>
       </c>
     </row>
@@ -1319,76 +1328,76 @@
         </is>
       </c>
       <c r="B37" s="43" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Sr SW Development Engineer</t>
+          <t>Material Handler 2 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
       <c r="D37" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463626373/</t>
+          <t>https://www.linkedin.com/jobs/view/4455289757/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="42" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B38" s="43" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Senior Forecasting Analyst</t>
+          <t>Desktop Support Specialist 3</t>
         </is>
       </c>
       <c r="D38" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463633190/</t>
+          <t>https://www.linkedin.com/jobs/view/4445930979/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="42" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B39" s="43" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Senior Forecasting Analyst</t>
+          <t>Material Handler 4 ( 2B Thur-Sat, every other Wednesday, Can work anytime from 5pm-5am )</t>
         </is>
       </c>
       <c r="D39" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463628391/</t>
+          <t>https://www.linkedin.com/jobs/view/4464432288/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="42" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B40" s="43" t="n">
-        <v>46270</v>
+        <v>46273</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Sr IT Project Manager</t>
+          <t>Sr. Staff Technical Program Manager - Stelo</t>
         </is>
       </c>
       <c r="D40" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4436188818/</t>
+          <t>https://www.linkedin.com/jobs/view/4455370480/</t>
         </is>
       </c>
     </row>
@@ -1399,16 +1408,16 @@
         </is>
       </c>
       <c r="B41" s="43" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Sr Software QA Engineer</t>
+          <t>Sr Manager, Partnership Operations and Contracting</t>
         </is>
       </c>
       <c r="D41" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463370785/</t>
+          <t>https://www.linkedin.com/jobs/view/4464670623/</t>
         </is>
       </c>
     </row>
@@ -1419,16 +1428,16 @@
         </is>
       </c>
       <c r="B42" s="43" t="n">
-        <v>46270</v>
+        <v>46273</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Material Handler 1 ( RDC ) - Days 1A and 1B</t>
+          <t>Manager Quality Compliance</t>
         </is>
       </c>
       <c r="D42" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4455128356/</t>
+          <t>https://www.linkedin.com/jobs/view/4464662874/</t>
         </is>
       </c>
     </row>
@@ -1439,16 +1448,16 @@
         </is>
       </c>
       <c r="B43" s="43" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Principal Firmware Architect</t>
+          <t>Manager Systems Design Engineering</t>
         </is>
       </c>
       <c r="D43" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463626391/</t>
+          <t>https://www.linkedin.com/jobs/view/4464683405/</t>
         </is>
       </c>
     </row>
@@ -1459,223 +1468,223 @@
         </is>
       </c>
       <c r="B44" s="43" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Software Development Engineer 1</t>
+          <t>Sr. Federal Clinical Educator - East</t>
         </is>
       </c>
       <c r="D44" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4454097524/</t>
+          <t>https://www.linkedin.com/jobs/view/4455357586/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="42" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B45" s="43" t="n">
-        <v>46268</v>
+        <v>46274</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Supervisor Customer Advocacy</t>
+          <t>Senior Staff Process Development Engineer</t>
         </is>
       </c>
       <c r="D45" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4454022788/</t>
+          <t>https://www.linkedin.com/jobs/view/4464945232/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="42" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B46" s="43" t="n">
-        <v>46268</v>
+        <v>46274</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Customer Service Representative (German-speaking)</t>
+          <t>Production Chemist 3</t>
         </is>
       </c>
       <c r="D46" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463120173/</t>
+          <t>https://www.linkedin.com/jobs/view/4464932915/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="42" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B47" s="43" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Sr Cybersecurity Analyst - GRC</t>
+          <t>SW Test Development Engineer 2</t>
         </is>
       </c>
       <c r="D47" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4454019825/</t>
+          <t>https://www.linkedin.com/jobs/view/4436151688/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="42" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B48" s="43" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Customer Service Representative, French Speaker</t>
+          <t>Manager, SW System &amp; Solution Dev Engineer</t>
         </is>
       </c>
       <c r="D48" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4462772822/</t>
+          <t>https://www.linkedin.com/jobs/view/4464452799/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="42" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B49" s="43" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Intelligence Analyst - Geopolitical</t>
+          <t>Software QA Engineer 2</t>
         </is>
       </c>
       <c r="D49" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4444046742/</t>
+          <t>https://www.linkedin.com/jobs/view/4464606837/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="42" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B50" s="43" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>GBS Engagement &amp; Service Management Lead</t>
+          <t>Sr Buyer</t>
         </is>
       </c>
       <c r="D50" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4427554137/</t>
+          <t>https://www.linkedin.com/jobs/view/4454535222/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="42" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B51" s="43" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Contact Center Platform Analyst</t>
+          <t>Planning Manager</t>
         </is>
       </c>
       <c r="D51" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4462857053/</t>
+          <t>https://www.linkedin.com/jobs/view/4454556094/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="42" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B52" s="43" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Program Manager - AI Initiatives</t>
+          <t>Production Planner</t>
         </is>
       </c>
       <c r="D52" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4435119512/</t>
+          <t>https://www.linkedin.com/jobs/view/4454538160/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="42" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B53" s="43" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Senior Telecom Engineer (Genesys Cloud)</t>
+          <t>Quality Technician 2 Back End Days</t>
         </is>
       </c>
       <c r="D53" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463370784/</t>
+          <t>https://www.linkedin.com/jobs/view/4464613132/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="42" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B54" s="43" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>SW Development Engineer 1 - Android</t>
+          <t>Process Technician 2 (Front End Night Shift)</t>
         </is>
       </c>
       <c r="D54" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4464353380/</t>
+          <t>https://www.linkedin.com/jobs/view/4455755200/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="42" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B55" s="43" t="n">
@@ -1683,19 +1692,19 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Customer Advocacy Generalist</t>
+          <t>Supervisor Process Engineering</t>
         </is>
       </c>
       <c r="D55" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4464354416/</t>
+          <t>https://www.linkedin.com/jobs/view/4464338496/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="42" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B56" s="43" t="n">
@@ -1703,179 +1712,179 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Staff Equipment Engineer</t>
+          <t>Sr Production Supervisor (Front End Night Shift)</t>
         </is>
       </c>
       <c r="D56" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4455253909/</t>
+          <t>https://www.linkedin.com/jobs/view/4455302580/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="42" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B57" s="43" t="n">
-        <v>46272</v>
+        <v>46269</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Customer Advocacy Generalist</t>
+          <t>Engineering Technician 4 (Monday to Friday days)</t>
         </is>
       </c>
       <c r="D57" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4464339507/</t>
+          <t>https://www.linkedin.com/jobs/view/4463368770/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B58" s="43" t="n">
-        <v>46272</v>
+        <v>46270</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Material Handler 2 ( RDC ) - Days 1A and 1B</t>
+          <t>Engineering Technician 3 (Front End Day Shift)</t>
         </is>
       </c>
       <c r="D58" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4455289757/</t>
+          <t>https://www.linkedin.com/jobs/view/4463698028/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="42" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B59" s="43" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Territory Sales Manager - Galicia</t>
+          <t>Lab Supervisor (Manufacturing) - Back End Day Shift</t>
         </is>
       </c>
       <c r="D59" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4462835756/</t>
+          <t>https://www.linkedin.com/jobs/view/4463359959/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="42" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B60" s="43" t="n">
-        <v>46272</v>
+        <v>46270</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Desktop Support Specialist 3</t>
+          <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
         </is>
       </c>
       <c r="D60" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4445930979/</t>
+          <t>https://www.linkedin.com/jobs/view/4463699027/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B61" s="43" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Material Handler 4 ( 2B Thur-Sat, every other Wednesday, Can work anytime from 5pm-5am )</t>
+          <t>Lab Technician 3 (Chemistry)</t>
         </is>
       </c>
       <c r="D61" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4464432288/</t>
+          <t>https://www.linkedin.com/jobs/view/4464341469/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B62" s="43" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Sr. Staff Technical Program Manager - Stelo</t>
+          <t>Medical Representative MR 医療機器 糖尿病領域 営業職</t>
         </is>
       </c>
       <c r="D62" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4455370480/</t>
+          <t>https://www.linkedin.com/jobs/view/4455248893/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B63" s="43" t="n">
-        <v>46273</v>
+        <v>46271</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Sr Manager, Partnership Operations and Contracting</t>
+          <t>UI Designer (Design System)</t>
         </is>
       </c>
       <c r="D63" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4464670623/</t>
+          <t>https://www.linkedin.com/jobs/view/4427632128/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B64" s="43" t="n">
-        <v>46273</v>
+        <v>46269</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Manager Quality Compliance</t>
+          <t>Senior Warehouse Operative - Day Shift</t>
         </is>
       </c>
       <c r="D64" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4464662874/</t>
+          <t>https://www.linkedin.com/jobs/view/4463635156/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B65" s="43" t="n">
@@ -1883,39 +1892,39 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Manager Systems Design Engineering</t>
+          <t>Senior Accountant/Bilanzbuchhalter (m/w/d) - Healthcare</t>
         </is>
       </c>
       <c r="D65" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4464683405/</t>
+          <t>https://www.linkedin.com/jobs/view/4455750299/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B66" s="43" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Sr. Federal Clinical Educator - East</t>
+          <t>Territory Business Manager</t>
         </is>
       </c>
       <c r="D66" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4455357586/</t>
+          <t>https://www.linkedin.com/jobs/view/4464350389/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B67" s="43" t="n">
@@ -1923,19 +1932,19 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Senior Staff Process Development Engineer</t>
+          <t>Sr Technical Writer</t>
         </is>
       </c>
       <c r="D67" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4464945232/</t>
+          <t>https://www.linkedin.com/jobs/view/4465024024/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B68" s="43" t="n">
@@ -1943,12 +1952,12 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Production Chemist 3</t>
+          <t>Sr SW Development Engineer - IOS</t>
         </is>
       </c>
       <c r="D68" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4464932915/</t>
+          <t>https://www.linkedin.com/jobs/view/4465020025/</t>
         </is>
       </c>
     </row>
@@ -1959,43 +1968,43 @@
         </is>
       </c>
       <c r="B69" s="43" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>SW Test Development Engineer 2</t>
+          <t>Material Handler 2 ( RDC ) - Nights 2A and 2B</t>
         </is>
       </c>
       <c r="D69" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4436151688/</t>
+          <t>https://www.linkedin.com/jobs/view/4455289751/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B70" s="43" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Global Brand Marketing Manager (Stelo)</t>
+          <t>SW Development Engineer 2 - Android</t>
         </is>
       </c>
       <c r="D70" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4435306708/</t>
+          <t>https://www.linkedin.com/jobs/view/4464610755/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="42" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B71" s="43" t="n">
@@ -2003,777 +2012,1717 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Manager, SW System &amp; Solution Dev Engineer</t>
+          <t>Sr Enterprise Developer (Power Platform Developer)</t>
         </is>
       </c>
       <c r="D71" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4464452799/</t>
+          <t>https://www.linkedin.com/jobs/view/4455767052/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B72" s="43" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Software QA Engineer 2</t>
+          <t>SW Test Development Engineer 1</t>
         </is>
       </c>
       <c r="D72" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4464606837/</t>
+          <t>https://www.linkedin.com/jobs/view/4465029007/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="42" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B73" s="43" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Sr Buyer</t>
+          <t>Sr. SW Test Development Engineer V&amp;V</t>
         </is>
       </c>
       <c r="D73" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4454535222/</t>
+          <t>https://www.linkedin.com/jobs/view/4387839555/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="42" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B74" s="43" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Planning Manager</t>
+          <t>Staff Software Test Development Engineer</t>
         </is>
       </c>
       <c r="D74" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4454556094/</t>
+          <t>https://www.linkedin.com/jobs/view/4388377406/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="42" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B75" s="43" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Production Planner</t>
+          <t>Customer Service Representative (Italian-speaking)</t>
         </is>
       </c>
       <c r="D75" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4454538160/</t>
+          <t>https://www.linkedin.com/jobs/view/4446389046/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="42" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B76" s="43" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Quality Technician 2 Back End Days</t>
+          <t>Mitarbeiter:innen für den deutschsprachigen Produkt- und Kundendienst (m/w/d)</t>
         </is>
       </c>
       <c r="D76" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4464613132/</t>
+          <t>https://www.linkedin.com/jobs/view/4446570417/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="42" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B77" s="43" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Process Technician 2 (Front End Night Shift)</t>
+          <t>Senior Service Designer, Technical Support</t>
         </is>
       </c>
       <c r="D77" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4455755200/</t>
+          <t>https://www.linkedin.com/jobs/view/4455960251/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="42" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B78" s="43" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Supervisor Process Engineering</t>
+          <t>Sr Manager Regulatory Affairs</t>
         </is>
       </c>
       <c r="D78" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4464338496/</t>
+          <t>https://www.linkedin.com/jobs/view/4456106944/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="42" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B79" s="43" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Sr Production Supervisor (Front End Night Shift)</t>
+          <t>Territory Business Manager - South Island</t>
         </is>
       </c>
       <c r="D79" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4455302580/</t>
+          <t>https://www.linkedin.com/jobs/view/4456111920/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="42" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B80" s="43" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Engineering Technician 4 (Monday to Friday days)</t>
+          <t>HR Business Partner</t>
         </is>
       </c>
       <c r="D80" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463368770/</t>
+          <t>https://www.linkedin.com/jobs/view/4456322164/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="42" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B81" s="43" t="n">
-        <v>46270</v>
+        <v>46274</v>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Engineering Technician 3 (Front End Day Shift)</t>
+          <t>Engineering Technician 4</t>
         </is>
       </c>
       <c r="D81" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463698028/</t>
+          <t>https://www.linkedin.com/jobs/view/4456115187/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="42" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B82" s="43" t="n">
-        <v>46268</v>
+        <v>46274</v>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer Digital Systems</t>
+          <t>Staff Database Administrator</t>
         </is>
       </c>
       <c r="D82" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4444460213/</t>
+          <t>https://www.linkedin.com/jobs/view/4456322200/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="42" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B83" s="43" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Lab Supervisor (Manufacturing) - Back End Day Shift</t>
+          <t>Payroll Analyst (ANZ)</t>
         </is>
       </c>
       <c r="D83" s="44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4463359959/</t>
+          <t>https://www.linkedin.com/jobs/view/4456178209/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="42" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B84" s="43" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Staff SRE SW Development Engineer</t>
+        </is>
+      </c>
+      <c r="D84" s="44" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4387683946/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B85" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Associate Facilities Engineer (Building Maintenance)</t>
+        </is>
+      </c>
+      <c r="D85" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4459144568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="45" t="inlineStr">
+        <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B84" s="43" t="n">
-        <v>46270</v>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
-        </is>
-      </c>
-      <c r="D84" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463699027/</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="42" t="inlineStr">
+      <c r="B86" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Executive Assistant - Madrid</t>
+        </is>
+      </c>
+      <c r="D86" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448303180/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="45" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B87" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Benefits Analyst</t>
+        </is>
+      </c>
+      <c r="D87" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461581171/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="45" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B88" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Senior Manager Corporate Compliance - EMEA</t>
+        </is>
+      </c>
+      <c r="D88" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4429707112/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="45" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B89" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Customer Service Representative (German-speaking)</t>
+        </is>
+      </c>
+      <c r="D89" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463120173/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="45" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B90" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Sr Enterprise Privacy Analyst</t>
+        </is>
+      </c>
+      <c r="D90" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4387414194/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="45" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B91" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Customer Advocacy Generalist</t>
+        </is>
+      </c>
+      <c r="D91" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461765131/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="45" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B92" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>Customer Advocacy Generalist</t>
+        </is>
+      </c>
+      <c r="D92" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4459303523/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="45" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B93" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Associate Facilities Engineer</t>
+        </is>
+      </c>
+      <c r="D93" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448830718/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="45" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B94" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Sr Cybersecurity Analyst - GRC</t>
+        </is>
+      </c>
+      <c r="D94" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4454019825/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="45" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B95" s="46" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Sr Manager Human Resources</t>
+        </is>
+      </c>
+      <c r="D95" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4466052473/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="45" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B96" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Manager - Capability Leader, Sentiment Intelligence</t>
+        </is>
+      </c>
+      <c r="D96" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4459302533/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="45" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B97" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>Sr Cost Accountant</t>
+        </is>
+      </c>
+      <c r="D97" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4410011461/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B98" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>Sr Regulatory Affairs Specialist</t>
+        </is>
+      </c>
+      <c r="D98" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448601784/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="45" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B99" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Software Development Engineer 2</t>
+        </is>
+      </c>
+      <c r="D99" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453360435/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="45" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B100" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Sr Facilities Engineer</t>
+        </is>
+      </c>
+      <c r="D100" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446562908/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="45" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B101" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>Sr Cybersecurity Analyst - GRC</t>
+        </is>
+      </c>
+      <c r="D101" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453096131/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="45" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B102" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>Accountant - Healthcare - Edinburgh</t>
+        </is>
+      </c>
+      <c r="D102" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453144035/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="45" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B103" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Manager Finance</t>
+        </is>
+      </c>
+      <c r="D103" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4462145294/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B104" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>Regulatory Affairs Specialist</t>
+        </is>
+      </c>
+      <c r="D104" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448398864/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="45" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B105" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>Senior Manager Corporate Compliance - EMEA (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D105" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461752409/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B106" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>Director, QA - Product Development Processes</t>
+        </is>
+      </c>
+      <c r="D106" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456434433/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="45" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B107" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>Security and Privacy Compliance Analyst - Cybersecurity</t>
+        </is>
+      </c>
+      <c r="D107" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4257269392/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="45" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B108" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>Advanced Support Specialist 1</t>
+        </is>
+      </c>
+      <c r="D108" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4458769459/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="45" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B109" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>Sr Quality Assurance Analyst</t>
+        </is>
+      </c>
+      <c r="D109" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4451545592/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="45" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B110" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Manager-Vendor Management (Electronics)</t>
+        </is>
+      </c>
+      <c r="D110" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446726237/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="45" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B111" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Customer Success Associate</t>
+        </is>
+      </c>
+      <c r="D111" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447526678/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="45" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B112" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Supply Chain Analyst</t>
+        </is>
+      </c>
+      <c r="D112" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4433857606/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="45" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B113" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>Manager, APAC Business Development and Partnership</t>
+        </is>
+      </c>
+      <c r="D113" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453097086/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="45" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B114" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>Sr Quality Engineer, Supplier Quality Engineering</t>
+        </is>
+      </c>
+      <c r="D114" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4384568916/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B115" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>Sr QA Engineer</t>
+        </is>
+      </c>
+      <c r="D115" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465859501/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B116" s="46" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>Sr Workplace Solutions Analyst</t>
+        </is>
+      </c>
+      <c r="D116" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456322161/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B117" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>Staff Data Engineer</t>
+        </is>
+      </c>
+      <c r="D117" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446368700/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="45" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B118" s="46" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>Staff SW Development Engineer</t>
+        </is>
+      </c>
+      <c r="D118" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465323573/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="45" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B119" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>Senior Sustainability Specialist – Healthcare – Vilnius, Lithuania</t>
+        </is>
+      </c>
+      <c r="D119" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4459828416/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="45" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B120" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
+        </is>
+      </c>
+      <c r="D120" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453077256/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="45" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B121" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>Manager, APAC Business Development and Partnership</t>
+        </is>
+      </c>
+      <c r="D121" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453093132/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="45" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B122" s="46" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>Director, Business Program Management Office</t>
+        </is>
+      </c>
+      <c r="D122" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456105988/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="45" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B123" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>Sr Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D123" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4371263716/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="45" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B124" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>Customer Service Representative - French Speaker</t>
+        </is>
+      </c>
+      <c r="D124" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4460500502/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="45" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B125" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>Program Manager - AI Initiatives</t>
+        </is>
+      </c>
+      <c r="D125" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4435119512/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="45" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B126" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>Sr Sales Trainer Diabetes MEA</t>
+        </is>
+      </c>
+      <c r="D126" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4449635545/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="45" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B127" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>Territory Sales Manager (m/w/d) - Zentralschweiz : Luzern, Obwalden, Nidwalden, Uri, Chur</t>
+        </is>
+      </c>
+      <c r="D127" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453133160/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B128" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>Speaker Bureau and KOL Operations Manager</t>
+        </is>
+      </c>
+      <c r="D128" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4423312162/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B129" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>Process Development Engineer 2</t>
+        </is>
+      </c>
+      <c r="D129" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437873233/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="45" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B130" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
+        </is>
+      </c>
+      <c r="D130" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4459811610/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="45" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B131" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>Technical Support Representative 1</t>
+        </is>
+      </c>
+      <c r="D131" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4403461287/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B132" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>Sr Manager Regulatory Affairs- LATAM</t>
+        </is>
+      </c>
+      <c r="D132" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448606739/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="45" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B133" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
+        </is>
+      </c>
+      <c r="D133" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453075275/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="45" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B134" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>Customer Account Support Specialist 2</t>
+        </is>
+      </c>
+      <c r="D134" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450027435/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="45" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B135" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>Procurement Ops Manager (IC)</t>
+        </is>
+      </c>
+      <c r="D135" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453097103/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="45" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B136" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="D136" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453371096/</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="45" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B137" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>Technical Support Representative 1</t>
+        </is>
+      </c>
+      <c r="D137" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4403153694/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="45" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B138" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
+        </is>
+      </c>
+      <c r="D138" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453092177/</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="45" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B139" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>Graphic Designer 2</t>
+        </is>
+      </c>
+      <c r="D139" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456722826/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="45" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B85" s="43" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>Lab Technician 3 (Chemistry)</t>
-        </is>
-      </c>
-      <c r="D85" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464341469/</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="42" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="B86" s="43" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>Medical Representative MR 医療機器 糖尿病領域 営業職</t>
-        </is>
-      </c>
-      <c r="D86" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455248893/</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="42" t="inlineStr">
+      <c r="B140" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="D140" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4458283492/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="45" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B141" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing Associate 2</t>
+        </is>
+      </c>
+      <c r="D141" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456472809/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="45" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B142" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>Engineering Technician 2</t>
+        </is>
+      </c>
+      <c r="D142" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465624957/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="45" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B143" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>Engineering Technician 4</t>
+        </is>
+      </c>
+      <c r="D143" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438139166/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="45" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B144" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>Sr Cybersecurity Engineer</t>
+        </is>
+      </c>
+      <c r="D144" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4394381237/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B145" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Director, Consumer Software Applications</t>
+        </is>
+      </c>
+      <c r="D145" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456361869/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="45" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B146" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>Kundenservice Medizintechnik (m/w/d) - Mainz</t>
+        </is>
+      </c>
+      <c r="D146" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4462192923/</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B147" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>Global Brand Marketing Manager (Stelo)</t>
+        </is>
+      </c>
+      <c r="D147" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4435306708/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="45" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B148" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>Business Development Lead - India (Multiple Locations)</t>
+        </is>
+      </c>
+      <c r="D148" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456463987/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B149" s="46" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>Systems Design &amp; Test Engineer 2</t>
+        </is>
+      </c>
+      <c r="D149" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443989564/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B150" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>Sr Manager Medical Affairs</t>
+        </is>
+      </c>
+      <c r="D150" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461536483/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="45" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B151" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing Technician 3 (Weekend Day Shift)</t>
+        </is>
+      </c>
+      <c r="D151" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456731799/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B152" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>Staff Membrane Formulation Scientist</t>
+        </is>
+      </c>
+      <c r="D152" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438128497/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="45" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B87" s="43" t="n">
-        <v>46271</v>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>UI Designer (Design System)</t>
-        </is>
-      </c>
-      <c r="D87" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4427632128/</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="42" t="inlineStr">
-        <is>
-          <t>Lithuania</t>
-        </is>
-      </c>
-      <c r="B88" s="43" t="n">
-        <v>46268</v>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>IT Manager, Commercial Applications (Salesforce Sales Cloud O2C)</t>
-        </is>
-      </c>
-      <c r="D88" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4443109225/</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="42" t="inlineStr">
+      <c r="B153" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Advisor (Maternity cover)</t>
+        </is>
+      </c>
+      <c r="D153" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4459039247/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B154" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>Hardware Engineer 2</t>
+        </is>
+      </c>
+      <c r="D154" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4457567279/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="45" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B89" s="43" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>Senior Warehouse Operative - Day Shift</t>
-        </is>
-      </c>
-      <c r="D89" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463635156/</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="42" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B90" s="43" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>Senior Accountant/Bilanzbuchhalter (m/w/d) - Healthcare</t>
-        </is>
-      </c>
-      <c r="D90" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455750299/</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="42" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="B91" s="43" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>Territory Business Manager</t>
-        </is>
-      </c>
-      <c r="D91" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464350389/</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="42" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B92" s="43" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>Sr Technical Writer</t>
-        </is>
-      </c>
-      <c r="D92" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4465024024/</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="42" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B93" s="43" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>Sr SW Development Engineer - IOS</t>
-        </is>
-      </c>
-      <c r="D93" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4465020025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="42" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B94" s="43" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>Material Handler 2 ( RDC ) - Nights 2A and 2B</t>
-        </is>
-      </c>
-      <c r="D94" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455289751/</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="42" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B95" s="43" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>SW Development Engineer 2 - Android</t>
-        </is>
-      </c>
-      <c r="D95" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464610755/</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="42" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B96" s="43" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>Sr Enterprise Developer (Power Platform Developer)</t>
-        </is>
-      </c>
-      <c r="D96" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455767052/</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="42" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B97" s="43" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>SW Test Development Engineer 1</t>
-        </is>
-      </c>
-      <c r="D97" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4465029007/</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="42" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B98" s="43" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>Sr. SW Test Development Engineer V&amp;V</t>
-        </is>
-      </c>
-      <c r="D98" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4387839555/</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="42" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B99" s="43" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>Staff Software Test Development Engineer</t>
-        </is>
-      </c>
-      <c r="D99" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4388377406/</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="42" t="inlineStr">
-        <is>
-          <t>Lithuania</t>
-        </is>
-      </c>
-      <c r="B100" s="43" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>Customer Service Representative (Italian-speaking)</t>
-        </is>
-      </c>
-      <c r="D100" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4446389046/</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="42" t="inlineStr">
-        <is>
-          <t>Lithuania</t>
-        </is>
-      </c>
-      <c r="B101" s="43" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>Mitarbeiter:innen für den deutschsprachigen Produkt- und Kundendienst (m/w/d)</t>
-        </is>
-      </c>
-      <c r="D101" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4446570417/</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="42" t="inlineStr">
-        <is>
-          <t>Lithuania</t>
-        </is>
-      </c>
-      <c r="B102" s="43" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>Senior Service Designer, Technical Support</t>
-        </is>
-      </c>
-      <c r="D102" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455960251/</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="42" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="B103" s="43" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C103" s="4" t="inlineStr">
-        <is>
-          <t>Sr Manager Regulatory Affairs</t>
-        </is>
-      </c>
-      <c r="D103" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456106944/</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="42" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="B104" s="43" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t>Territory Business Manager - South Island</t>
-        </is>
-      </c>
-      <c r="D104" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456111920/</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="42" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B105" s="43" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>HR Business Partner</t>
-        </is>
-      </c>
-      <c r="D105" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456322164/</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="42" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B106" s="43" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>Engineering Technician 4</t>
-        </is>
-      </c>
-      <c r="D106" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456115187/</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="42" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B107" s="43" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>Staff Database Administrator</t>
-        </is>
-      </c>
-      <c r="D107" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456322200/</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="42" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B108" s="43" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>Payroll Analyst (ANZ)</t>
-        </is>
-      </c>
-      <c r="D108" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456178209/</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="42" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B109" s="43" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>Staff SRE SW Development Engineer</t>
-        </is>
-      </c>
-      <c r="D109" s="44" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4387683946/</t>
+      <c r="B155" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>Senior Warehouse Operative - Weekend Days</t>
+        </is>
+      </c>
+      <c r="D155" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461098658/</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="45" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B156" s="46" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
+        </is>
+      </c>
+      <c r="D156" s="47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453087192/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D109"/>
+  <autoFilter ref="A1:D156"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -2883,6 +3832,53 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId155"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$135</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -590,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1981,8 +1990,1328 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="48" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="B70" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Sr Market Access Manager</t>
+        </is>
+      </c>
+      <c r="D70" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465675855/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="48" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B71" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
+        </is>
+      </c>
+      <c r="D71" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4459816548/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="48" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B72" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Customer Advocacy Generalist</t>
+        </is>
+      </c>
+      <c r="D72" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464354416/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="48" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B73" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Customer Advocacy Generalist</t>
+        </is>
+      </c>
+      <c r="D73" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464339507/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="48" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B74" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Senior QA Manager (Quality Systems)</t>
+        </is>
+      </c>
+      <c r="D74" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4457509031/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="48" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B75" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Customer Service Representative (Italian-speaking)</t>
+        </is>
+      </c>
+      <c r="D75" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446389046/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="48" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B76" s="49" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Distributor Manager - Channel Excellence (MedTech)</t>
+        </is>
+      </c>
+      <c r="D76" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463683762/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="48" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B77" s="49" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Distributor Manager - Channel Excellence (MedTech)</t>
+        </is>
+      </c>
+      <c r="D77" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463684766/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="48" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B78" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Senior Forecasting Analyst</t>
+        </is>
+      </c>
+      <c r="D78" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463637144/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="48" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B79" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Sales/Inside Sales Trainer - Healthcare (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D79" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461765129/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="48" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B80" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Quality Technician 2 Back End Days</t>
+        </is>
+      </c>
+      <c r="D80" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464613132/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="48" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B81" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Mitarbeiter:innen für den deutschsprachigen Produkt- und Kundendienst (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D81" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446570417/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="48" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B82" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Senior Forecasting Analyst</t>
+        </is>
+      </c>
+      <c r="D82" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463633190/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="48" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B83" s="49" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Senior Service Designer, Technical Support</t>
+        </is>
+      </c>
+      <c r="D83" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455960251/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="48" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B84" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Sr Technical Program Manager FHIR APIs- 18 months fixed term</t>
+        </is>
+      </c>
+      <c r="D84" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450696746/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="48" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B85" s="49" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Process Technician 2 (Front End Night Shift)</t>
+        </is>
+      </c>
+      <c r="D85" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455755200/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="48" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B86" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Logistics Analyst</t>
+        </is>
+      </c>
+      <c r="D86" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461266744/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="48" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B87" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Senior Forecasting Analyst</t>
+        </is>
+      </c>
+      <c r="D87" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463628391/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="48" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B88" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Sr Business Process Analyst (m/w/d) - Healthcare</t>
+        </is>
+      </c>
+      <c r="D88" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4459309508/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="48" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B89" s="49" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Supervisor Process Engineering</t>
+        </is>
+      </c>
+      <c r="D89" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464338496/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="48" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B90" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Trade Marketing Manager - Pharmacy (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D90" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461770007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="48" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B91" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
+        </is>
+      </c>
+      <c r="D91" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453076276/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="48" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B92" s="49" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>Sr Production Supervisor (Front End Night Shift)</t>
+        </is>
+      </c>
+      <c r="D92" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455302580/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="48" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B93" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Bracknell, UK</t>
+        </is>
+      </c>
+      <c r="D93" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4462849233/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="48" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B94" s="49" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Engineering Technician 3 (Front End Day Shift)</t>
+        </is>
+      </c>
+      <c r="D94" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463698028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="48" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B95" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Sr Manager Regulatory Affairs</t>
+        </is>
+      </c>
+      <c r="D95" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456106944/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="48" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B96" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>QA Engineer Digital Systems</t>
+        </is>
+      </c>
+      <c r="D96" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444460213/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="48" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B97" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
+        </is>
+      </c>
+      <c r="D97" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453078274/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="48" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B98" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>Contract Administration Representative (French-speaking)</t>
+        </is>
+      </c>
+      <c r="D98" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461090763/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="48" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B99" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>GBS Engagement &amp; Service Management Lead</t>
+        </is>
+      </c>
+      <c r="D99" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4427554137/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="48" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B100" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Senior Forecasting Analyst – Healthcare - UK</t>
+        </is>
+      </c>
+      <c r="D100" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463622979/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="48" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B101" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
+        </is>
+      </c>
+      <c r="D101" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453089165/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="48" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B102" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>Senior Forecasting Analyst – Healthcare - UK</t>
+        </is>
+      </c>
+      <c r="D102" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463634192/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="48" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B103" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
+        </is>
+      </c>
+      <c r="D103" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453083196/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="48" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B104" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>Customer Service Representative, French Speaker</t>
+        </is>
+      </c>
+      <c r="D104" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4462772822/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="48" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B105" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
+        </is>
+      </c>
+      <c r="D105" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453082209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="48" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B106" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>Technical Support Representative 2</t>
+        </is>
+      </c>
+      <c r="D106" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438880089/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="48" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B107" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>Spanish Bilingual Customer Account Support Specialist 2</t>
+        </is>
+      </c>
+      <c r="D107" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4458704406/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="48" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B108" s="49" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>Territory Business Manager</t>
+        </is>
+      </c>
+      <c r="D108" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464350389/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="48" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B109" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>Spanish Bilingual TSR</t>
+        </is>
+      </c>
+      <c r="D109" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4407814543/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="48" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B110" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>Senior Medical Affairs Manager – Value, Evidence, and Outcomes</t>
+        </is>
+      </c>
+      <c r="D110" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443448275/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="48" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B111" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Sr Technical Writer</t>
+        </is>
+      </c>
+      <c r="D111" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465024024/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="48" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B112" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Production Chemist 3</t>
+        </is>
+      </c>
+      <c r="D112" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464932915/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="48" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B113" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>Lead Corporate Development Manager</t>
+        </is>
+      </c>
+      <c r="D113" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4462460922/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="48" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B114" s="49" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>Manager Systems Design Engineering</t>
+        </is>
+      </c>
+      <c r="D114" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464683405/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="48" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B115" s="49" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>Senior Staff Process Development Engineer</t>
+        </is>
+      </c>
+      <c r="D115" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464945232/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="48" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B116" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>Staff QA Engineer</t>
+        </is>
+      </c>
+      <c r="D116" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439353245/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="48" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B117" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>HR Business Partner</t>
+        </is>
+      </c>
+      <c r="D117" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456322164/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="48" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B118" s="49" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>Manager, SW System &amp; Solution Dev Engineer</t>
+        </is>
+      </c>
+      <c r="D118" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464452799/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="48" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B119" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>Procurement Ops Manager (IC)</t>
+        </is>
+      </c>
+      <c r="D119" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453082223/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="48" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B120" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>Business Process Analyst</t>
+        </is>
+      </c>
+      <c r="D120" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4414569192/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="48" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B121" s="49" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>Supervisor Manufacturing</t>
+        </is>
+      </c>
+      <c r="D121" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4428861138/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="48" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B122" s="49" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>Sr IT Project Manager</t>
+        </is>
+      </c>
+      <c r="D122" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436188818/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="48" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B123" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Director, Consumer Software Applications</t>
+        </is>
+      </c>
+      <c r="D123" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456380639/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="48" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B124" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Director, Consumer Software Applications</t>
+        </is>
+      </c>
+      <c r="D124" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456364824/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="48" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B125" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>Associate Marketing Manager</t>
+        </is>
+      </c>
+      <c r="D125" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4451399530/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="48" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B126" s="49" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>Staff Database Administrator</t>
+        </is>
+      </c>
+      <c r="D126" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456322200/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="48" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B127" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>Material Handler 1 ( RDC ) - Days 1A and 1B</t>
+        </is>
+      </c>
+      <c r="D127" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455128356/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="48" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B128" s="49" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>Payroll Analyst (ANZ)</t>
+        </is>
+      </c>
+      <c r="D128" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456178209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="48" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B129" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>Material Handler 4 ( 2B Thur-Sat, every other Wednesday, Can work anytime from 5pm-5am )</t>
+        </is>
+      </c>
+      <c r="D129" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464432288/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="48" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B130" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>Senior Sterilization Engineer</t>
+        </is>
+      </c>
+      <c r="D130" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4410980549/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="48" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B131" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>Accounts Payable Process Expert (Maternity Cover)</t>
+        </is>
+      </c>
+      <c r="D131" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4462464542/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="48" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B132" s="49" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>Senior Staff Mechanical Engineer - Characterization Lead</t>
+        </is>
+      </c>
+      <c r="D132" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4427645063/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="48" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B133" s="49" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>Sr Enterprise Developer (Power Platform Developer)</t>
+        </is>
+      </c>
+      <c r="D133" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455767052/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="48" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B134" s="49" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>Staff Software Test Development Engineer</t>
+        </is>
+      </c>
+      <c r="D134" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4388377406/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="48" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B135" s="49" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>Software QA Engineer 2</t>
+        </is>
+      </c>
+      <c r="D135" s="50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464606837/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D69"/>
+  <autoFilter ref="A1:D135"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -2052,6 +3381,72 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$154</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -599,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D135"/>
+  <dimension ref="A1:D154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -631,12 +640,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="48" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B2" s="46" t="n">
+      <c r="B2" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -644,19 +653,19 @@
           <t>Associate Facilities Engineer (Building Maintenance)</t>
         </is>
       </c>
-      <c r="D2" s="47" t="inlineStr">
+      <c r="D2" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459144568/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="45" t="inlineStr">
+      <c r="A3" s="48" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B3" s="46" t="n">
+      <c r="B3" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -664,19 +673,19 @@
           <t>Executive Assistant - Madrid</t>
         </is>
       </c>
-      <c r="D3" s="47" t="inlineStr">
+      <c r="D3" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448303180/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B4" s="46" t="n">
+      <c r="B4" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -684,19 +693,19 @@
           <t>Benefits Analyst</t>
         </is>
       </c>
-      <c r="D4" s="47" t="inlineStr">
+      <c r="D4" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461581171/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="48" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B5" s="46" t="n">
+      <c r="B5" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -704,19 +713,19 @@
           <t>Senior Manager Corporate Compliance - EMEA</t>
         </is>
       </c>
-      <c r="D5" s="47" t="inlineStr">
+      <c r="D5" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429707112/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="45" t="inlineStr">
+      <c r="A6" s="48" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B6" s="46" t="n">
+      <c r="B6" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -724,19 +733,19 @@
           <t>Customer Service Representative (German-speaking)</t>
         </is>
       </c>
-      <c r="D6" s="47" t="inlineStr">
+      <c r="D6" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463120173/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="45" t="inlineStr">
+      <c r="A7" s="48" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B7" s="46" t="n">
+      <c r="B7" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -744,19 +753,19 @@
           <t>Sr Enterprise Privacy Analyst</t>
         </is>
       </c>
-      <c r="D7" s="47" t="inlineStr">
+      <c r="D7" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387414194/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="45" t="inlineStr">
+      <c r="A8" s="48" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B8" s="46" t="n">
+      <c r="B8" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -764,19 +773,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D8" s="47" t="inlineStr">
+      <c r="D8" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765131/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="45" t="inlineStr">
+      <c r="A9" s="48" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B9" s="46" t="n">
+      <c r="B9" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -784,19 +793,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D9" s="47" t="inlineStr">
+      <c r="D9" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459303523/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="45" t="inlineStr">
+      <c r="A10" s="48" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B10" s="46" t="n">
+      <c r="B10" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -804,19 +813,19 @@
           <t>Associate Facilities Engineer</t>
         </is>
       </c>
-      <c r="D10" s="47" t="inlineStr">
+      <c r="D10" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448830718/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="45" t="inlineStr">
+      <c r="A11" s="48" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B11" s="46" t="n">
+      <c r="B11" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -824,19 +833,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D11" s="47" t="inlineStr">
+      <c r="D11" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454019825/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="45" t="inlineStr">
+      <c r="A12" s="48" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B12" s="46" t="n">
+      <c r="B12" s="49" t="n">
         <v>46276</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -844,19 +853,19 @@
           <t>Sr Manager Human Resources</t>
         </is>
       </c>
-      <c r="D12" s="47" t="inlineStr">
+      <c r="D12" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466052473/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="45" t="inlineStr">
+      <c r="A13" s="48" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B13" s="46" t="n">
+      <c r="B13" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -864,19 +873,19 @@
           <t>Sr. Manager - Capability Leader, Sentiment Intelligence</t>
         </is>
       </c>
-      <c r="D13" s="47" t="inlineStr">
+      <c r="D13" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459302533/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="45" t="inlineStr">
+      <c r="A14" s="48" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B14" s="46" t="n">
+      <c r="B14" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -884,19 +893,19 @@
           <t>Sr Cost Accountant</t>
         </is>
       </c>
-      <c r="D14" s="47" t="inlineStr">
+      <c r="D14" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4410011461/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="45" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B15" s="46" t="n">
+      <c r="B15" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -904,19 +913,19 @@
           <t>Sr Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="D15" s="47" t="inlineStr">
+      <c r="D15" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448601784/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="45" t="inlineStr">
+      <c r="A16" s="48" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B16" s="46" t="n">
+      <c r="B16" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -924,19 +933,19 @@
           <t>Software Development Engineer 2</t>
         </is>
       </c>
-      <c r="D16" s="47" t="inlineStr">
+      <c r="D16" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453360435/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="45" t="inlineStr">
+      <c r="A17" s="48" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B17" s="46" t="n">
+      <c r="B17" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -944,19 +953,19 @@
           <t>Sr Facilities Engineer</t>
         </is>
       </c>
-      <c r="D17" s="47" t="inlineStr">
+      <c r="D17" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446562908/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="45" t="inlineStr">
+      <c r="A18" s="48" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B18" s="46" t="n">
+      <c r="B18" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -964,19 +973,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D18" s="47" t="inlineStr">
+      <c r="D18" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453096131/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="45" t="inlineStr">
+      <c r="A19" s="48" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B19" s="46" t="n">
+      <c r="B19" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -984,19 +993,19 @@
           <t>Accountant - Healthcare - Edinburgh</t>
         </is>
       </c>
-      <c r="D19" s="47" t="inlineStr">
+      <c r="D19" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453144035/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="45" t="inlineStr">
+      <c r="A20" s="48" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="B20" s="46" t="n">
+      <c r="B20" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1004,19 +1013,19 @@
           <t>Manager Finance</t>
         </is>
       </c>
-      <c r="D20" s="47" t="inlineStr">
+      <c r="D20" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462145294/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="45" t="inlineStr">
+      <c r="A21" s="48" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B21" s="46" t="n">
+      <c r="B21" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1024,19 +1033,19 @@
           <t>Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="D21" s="47" t="inlineStr">
+      <c r="D21" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448398864/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="45" t="inlineStr">
+      <c r="A22" s="48" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B22" s="46" t="n">
+      <c r="B22" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1044,19 +1053,19 @@
           <t>Senior Manager Corporate Compliance - EMEA (m/w/d)</t>
         </is>
       </c>
-      <c r="D22" s="47" t="inlineStr">
+      <c r="D22" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461752409/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="45" t="inlineStr">
+      <c r="A23" s="48" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B23" s="46" t="n">
+      <c r="B23" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1064,19 +1073,19 @@
           <t>Director, QA - Product Development Processes</t>
         </is>
       </c>
-      <c r="D23" s="47" t="inlineStr">
+      <c r="D23" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456434433/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="45" t="inlineStr">
+      <c r="A24" s="48" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B24" s="46" t="n">
+      <c r="B24" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1084,19 +1093,19 @@
           <t>Security and Privacy Compliance Analyst - Cybersecurity</t>
         </is>
       </c>
-      <c r="D24" s="47" t="inlineStr">
+      <c r="D24" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4257269392/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="45" t="inlineStr">
+      <c r="A25" s="48" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B25" s="46" t="n">
+      <c r="B25" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1104,19 +1113,19 @@
           <t>Advanced Support Specialist 1</t>
         </is>
       </c>
-      <c r="D25" s="47" t="inlineStr">
+      <c r="D25" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458769459/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="45" t="inlineStr">
+      <c r="A26" s="48" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B26" s="46" t="n">
+      <c r="B26" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1124,19 +1133,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D26" s="47" t="inlineStr">
+      <c r="D26" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451545592/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="45" t="inlineStr">
+      <c r="A27" s="48" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B27" s="46" t="n">
+      <c r="B27" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1144,19 +1153,19 @@
           <t>Sr. Manager-Vendor Management (Electronics)</t>
         </is>
       </c>
-      <c r="D27" s="47" t="inlineStr">
+      <c r="D27" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446726237/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="45" t="inlineStr">
+      <c r="A28" s="48" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B28" s="46" t="n">
+      <c r="B28" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1164,19 +1173,19 @@
           <t>Customer Success Associate</t>
         </is>
       </c>
-      <c r="D28" s="47" t="inlineStr">
+      <c r="D28" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447526678/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="45" t="inlineStr">
+      <c r="A29" s="48" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B29" s="46" t="n">
+      <c r="B29" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1184,19 +1193,19 @@
           <t>Supply Chain Analyst</t>
         </is>
       </c>
-      <c r="D29" s="47" t="inlineStr">
+      <c r="D29" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433857606/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="45" t="inlineStr">
+      <c r="A30" s="48" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B30" s="46" t="n">
+      <c r="B30" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1204,19 +1213,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D30" s="47" t="inlineStr">
+      <c r="D30" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097086/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="45" t="inlineStr">
+      <c r="A31" s="48" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B31" s="46" t="n">
+      <c r="B31" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1224,19 +1233,19 @@
           <t>Sr Quality Engineer, Supplier Quality Engineering</t>
         </is>
       </c>
-      <c r="D31" s="47" t="inlineStr">
+      <c r="D31" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4384568916/</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="45" t="inlineStr">
+      <c r="A32" s="48" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B32" s="46" t="n">
+      <c r="B32" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1244,19 +1253,19 @@
           <t>Sr QA Engineer</t>
         </is>
       </c>
-      <c r="D32" s="47" t="inlineStr">
+      <c r="D32" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465859501/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="45" t="inlineStr">
+      <c r="A33" s="48" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B33" s="46" t="n">
+      <c r="B33" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1264,19 +1273,19 @@
           <t>Staff Data Engineer</t>
         </is>
       </c>
-      <c r="D33" s="47" t="inlineStr">
+      <c r="D33" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446368700/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="45" t="inlineStr">
+      <c r="A34" s="48" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B34" s="46" t="n">
+      <c r="B34" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1284,19 +1293,19 @@
           <t>Senior Sustainability Specialist – Healthcare – Vilnius, Lithuania</t>
         </is>
       </c>
-      <c r="D34" s="47" t="inlineStr">
+      <c r="D34" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459828416/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="45" t="inlineStr">
+      <c r="A35" s="48" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B35" s="46" t="n">
+      <c r="B35" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1304,19 +1313,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D35" s="47" t="inlineStr">
+      <c r="D35" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453077256/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="45" t="inlineStr">
+      <c r="A36" s="48" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B36" s="46" t="n">
+      <c r="B36" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1324,19 +1333,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D36" s="47" t="inlineStr">
+      <c r="D36" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453093132/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="45" t="inlineStr">
+      <c r="A37" s="48" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B37" s="46" t="n">
+      <c r="B37" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1344,19 +1353,19 @@
           <t>Sr Systems Engineer</t>
         </is>
       </c>
-      <c r="D37" s="47" t="inlineStr">
+      <c r="D37" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4371263716/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="45" t="inlineStr">
+      <c r="A38" s="48" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B38" s="46" t="n">
+      <c r="B38" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1364,19 +1373,19 @@
           <t>Customer Service Representative - French Speaker</t>
         </is>
       </c>
-      <c r="D38" s="47" t="inlineStr">
+      <c r="D38" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460500502/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="45" t="inlineStr">
+      <c r="A39" s="48" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B39" s="46" t="n">
+      <c r="B39" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1384,19 +1393,19 @@
           <t>Program Manager - AI Initiatives</t>
         </is>
       </c>
-      <c r="D39" s="47" t="inlineStr">
+      <c r="D39" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435119512/</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="45" t="inlineStr">
+      <c r="A40" s="48" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="B40" s="46" t="n">
+      <c r="B40" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1404,19 +1413,19 @@
           <t>Sr Sales Trainer Diabetes MEA</t>
         </is>
       </c>
-      <c r="D40" s="47" t="inlineStr">
+      <c r="D40" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4449635545/</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="45" t="inlineStr">
+      <c r="A41" s="48" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="B41" s="46" t="n">
+      <c r="B41" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1424,19 +1433,19 @@
           <t>Territory Sales Manager (m/w/d) - Zentralschweiz : Luzern, Obwalden, Nidwalden, Uri, Chur</t>
         </is>
       </c>
-      <c r="D41" s="47" t="inlineStr">
+      <c r="D41" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453133160/</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="45" t="inlineStr">
+      <c r="A42" s="48" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B42" s="46" t="n">
+      <c r="B42" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1444,19 +1453,19 @@
           <t>Speaker Bureau and KOL Operations Manager</t>
         </is>
       </c>
-      <c r="D42" s="47" t="inlineStr">
+      <c r="D42" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4423312162/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="45" t="inlineStr">
+      <c r="A43" s="48" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B43" s="46" t="n">
+      <c r="B43" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1464,19 +1473,19 @@
           <t>Process Development Engineer 2</t>
         </is>
       </c>
-      <c r="D43" s="47" t="inlineStr">
+      <c r="D43" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437873233/</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="45" t="inlineStr">
+      <c r="A44" s="48" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B44" s="46" t="n">
+      <c r="B44" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1484,19 +1493,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
         </is>
       </c>
-      <c r="D44" s="47" t="inlineStr">
+      <c r="D44" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459811610/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="45" t="inlineStr">
+      <c r="A45" s="48" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B45" s="46" t="n">
+      <c r="B45" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1504,19 +1513,19 @@
           <t>Technical Support Representative 1</t>
         </is>
       </c>
-      <c r="D45" s="47" t="inlineStr">
+      <c r="D45" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403461287/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="45" t="inlineStr">
+      <c r="A46" s="48" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B46" s="46" t="n">
+      <c r="B46" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1524,19 +1533,19 @@
           <t>Sr Manager Regulatory Affairs- LATAM</t>
         </is>
       </c>
-      <c r="D46" s="47" t="inlineStr">
+      <c r="D46" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448606739/</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="45" t="inlineStr">
+      <c r="A47" s="48" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B47" s="46" t="n">
+      <c r="B47" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1544,19 +1553,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D47" s="47" t="inlineStr">
+      <c r="D47" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453075275/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="45" t="inlineStr">
+      <c r="A48" s="48" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B48" s="46" t="n">
+      <c r="B48" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1564,19 +1573,19 @@
           <t>Customer Account Support Specialist 2</t>
         </is>
       </c>
-      <c r="D48" s="47" t="inlineStr">
+      <c r="D48" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450027435/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="45" t="inlineStr">
+      <c r="A49" s="48" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B49" s="46" t="n">
+      <c r="B49" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1584,19 +1593,19 @@
           <t>Procurement Ops Manager (IC)</t>
         </is>
       </c>
-      <c r="D49" s="47" t="inlineStr">
+      <c r="D49" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097103/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="45" t="inlineStr">
+      <c r="A50" s="48" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B50" s="46" t="n">
+      <c r="B50" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1604,19 +1613,19 @@
           <t>Senior Software Development Engineer</t>
         </is>
       </c>
-      <c r="D50" s="47" t="inlineStr">
+      <c r="D50" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453371096/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="45" t="inlineStr">
+      <c r="A51" s="48" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B51" s="46" t="n">
+      <c r="B51" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1624,19 +1633,19 @@
           <t>Technical Support Representative 1</t>
         </is>
       </c>
-      <c r="D51" s="47" t="inlineStr">
+      <c r="D51" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403153694/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="45" t="inlineStr">
+      <c r="A52" s="48" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B52" s="46" t="n">
+      <c r="B52" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -1644,19 +1653,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D52" s="47" t="inlineStr">
+      <c r="D52" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453092177/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="45" t="inlineStr">
+      <c r="A53" s="48" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B53" s="46" t="n">
+      <c r="B53" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1664,19 +1673,19 @@
           <t>Graphic Designer 2</t>
         </is>
       </c>
-      <c r="D53" s="47" t="inlineStr">
+      <c r="D53" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456722826/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="45" t="inlineStr">
+      <c r="A54" s="48" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B54" s="46" t="n">
+      <c r="B54" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1684,19 +1693,19 @@
           <t>Purchasing Manager</t>
         </is>
       </c>
-      <c r="D54" s="47" t="inlineStr">
+      <c r="D54" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458283492/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="45" t="inlineStr">
+      <c r="A55" s="48" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B55" s="46" t="n">
+      <c r="B55" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1704,19 +1713,19 @@
           <t>Manufacturing Associate 2</t>
         </is>
       </c>
-      <c r="D55" s="47" t="inlineStr">
+      <c r="D55" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456472809/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="45" t="inlineStr">
+      <c r="A56" s="48" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B56" s="46" t="n">
+      <c r="B56" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1724,19 +1733,19 @@
           <t>Engineering Technician 2</t>
         </is>
       </c>
-      <c r="D56" s="47" t="inlineStr">
+      <c r="D56" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465624957/</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="45" t="inlineStr">
+      <c r="A57" s="48" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B57" s="46" t="n">
+      <c r="B57" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1744,19 +1753,19 @@
           <t>Engineering Technician 4</t>
         </is>
       </c>
-      <c r="D57" s="47" t="inlineStr">
+      <c r="D57" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438139166/</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="45" t="inlineStr">
+      <c r="A58" s="48" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B58" s="46" t="n">
+      <c r="B58" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1764,19 +1773,19 @@
           <t>Sr Cybersecurity Engineer</t>
         </is>
       </c>
-      <c r="D58" s="47" t="inlineStr">
+      <c r="D58" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4394381237/</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="45" t="inlineStr">
+      <c r="A59" s="48" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B59" s="46" t="n">
+      <c r="B59" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1784,19 +1793,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D59" s="47" t="inlineStr">
+      <c r="D59" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456361869/</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="45" t="inlineStr">
+      <c r="A60" s="48" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B60" s="46" t="n">
+      <c r="B60" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1804,19 +1813,19 @@
           <t>Kundenservice Medizintechnik (m/w/d) - Mainz</t>
         </is>
       </c>
-      <c r="D60" s="47" t="inlineStr">
+      <c r="D60" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462192923/</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="45" t="inlineStr">
+      <c r="A61" s="48" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B61" s="46" t="n">
+      <c r="B61" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1824,19 +1833,19 @@
           <t>Global Brand Marketing Manager (Stelo)</t>
         </is>
       </c>
-      <c r="D61" s="47" t="inlineStr">
+      <c r="D61" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435306708/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="45" t="inlineStr">
+      <c r="A62" s="48" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B62" s="46" t="n">
+      <c r="B62" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1844,19 +1853,19 @@
           <t>Business Development Lead - India (Multiple Locations)</t>
         </is>
       </c>
-      <c r="D62" s="47" t="inlineStr">
+      <c r="D62" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456463987/</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="45" t="inlineStr">
+      <c r="A63" s="48" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B63" s="46" t="n">
+      <c r="B63" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1864,19 +1873,19 @@
           <t>Sr Manager Medical Affairs</t>
         </is>
       </c>
-      <c r="D63" s="47" t="inlineStr">
+      <c r="D63" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461536483/</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="45" t="inlineStr">
+      <c r="A64" s="48" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B64" s="46" t="n">
+      <c r="B64" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1884,19 +1893,19 @@
           <t>Manufacturing Technician 3 (Weekend Day Shift)</t>
         </is>
       </c>
-      <c r="D64" s="47" t="inlineStr">
+      <c r="D64" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456731799/</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="45" t="inlineStr">
+      <c r="A65" s="48" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B65" s="46" t="n">
+      <c r="B65" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1904,19 +1913,19 @@
           <t>Staff Membrane Formulation Scientist</t>
         </is>
       </c>
-      <c r="D65" s="47" t="inlineStr">
+      <c r="D65" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438128497/</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="45" t="inlineStr">
+      <c r="A66" s="48" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B66" s="46" t="n">
+      <c r="B66" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1924,19 +1933,19 @@
           <t>Talent Acquisition Advisor (Maternity cover)</t>
         </is>
       </c>
-      <c r="D66" s="47" t="inlineStr">
+      <c r="D66" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459039247/</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="45" t="inlineStr">
+      <c r="A67" s="48" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B67" s="46" t="n">
+      <c r="B67" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1944,19 +1953,19 @@
           <t>Hardware Engineer 2</t>
         </is>
       </c>
-      <c r="D67" s="47" t="inlineStr">
+      <c r="D67" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457567279/</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="45" t="inlineStr">
+      <c r="A68" s="48" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B68" s="46" t="n">
+      <c r="B68" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1964,19 +1973,19 @@
           <t>Senior Warehouse Operative - Weekend Days</t>
         </is>
       </c>
-      <c r="D68" s="47" t="inlineStr">
+      <c r="D68" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461098658/</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="45" t="inlineStr">
+      <c r="A69" s="48" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B69" s="46" t="n">
+      <c r="B69" s="49" t="n">
         <v>46275</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1984,7 +1993,7 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D69" s="47" t="inlineStr">
+      <c r="D69" s="50" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453087192/</t>
         </is>
@@ -3310,8 +3319,388 @@
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" s="51" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B136" s="52" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>SW Development Engineer 1 - Android</t>
+        </is>
+      </c>
+      <c r="D136" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464353380/</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="51" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B137" s="52" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>SW Test Development Engineer 1</t>
+        </is>
+      </c>
+      <c r="D137" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465029007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="51" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B138" s="52" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>SW Development Engineer 2 - Android</t>
+        </is>
+      </c>
+      <c r="D138" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464610755/</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B139" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>Manager Quality Compliance</t>
+        </is>
+      </c>
+      <c r="D139" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464662874/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="51" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B140" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>QA Engineer 2</t>
+        </is>
+      </c>
+      <c r="D140" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464097498/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B141" s="52" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>Sr Workplace Solutions Analyst</t>
+        </is>
+      </c>
+      <c r="D141" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456322161/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="51" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B142" s="52" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>Staff SW Development Engineer</t>
+        </is>
+      </c>
+      <c r="D142" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465323573/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B143" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>Staff QA Engineer</t>
+        </is>
+      </c>
+      <c r="D143" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436409441/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="51" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B144" s="52" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>Director, Business Program Management Office</t>
+        </is>
+      </c>
+      <c r="D144" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456105988/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="51" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B145" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>Staff Equipment Engineer</t>
+        </is>
+      </c>
+      <c r="D145" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455253909/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="51" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B146" s="52" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>Desktop Support Specialist 3</t>
+        </is>
+      </c>
+      <c r="D146" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4445930979/</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B147" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Staff Technical Program Manager - Stelo</t>
+        </is>
+      </c>
+      <c r="D147" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455370480/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="51" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B148" s="52" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>Engineering Technician 4</t>
+        </is>
+      </c>
+      <c r="D148" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456115187/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="51" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B149" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>Staff SRE SW Development Engineer</t>
+        </is>
+      </c>
+      <c r="D149" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4387683946/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B150" s="52" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>Systems Design &amp; Test Engineer 2</t>
+        </is>
+      </c>
+      <c r="D150" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443989564/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B151" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>Material Handler 2 ( RDC ) - Days 1A and 1B</t>
+        </is>
+      </c>
+      <c r="D151" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455289757/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B152" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>Material Handler 2 ( RDC ) - Nights 2A and 2B</t>
+        </is>
+      </c>
+      <c r="D152" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455289751/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="51" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B153" s="52" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>Sr. SW Test Development Engineer V&amp;V</t>
+        </is>
+      </c>
+      <c r="D153" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4387839555/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B154" s="52" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>QA Inspector 2 ( Dobson ) - 1A Sun- Tues, every other Wednesday, Can work anytime from 5am-5pm</t>
+        </is>
+      </c>
+      <c r="D154" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463691655/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D135"/>
+  <autoFilter ref="A1:D154"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -3447,6 +3836,25 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId153"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$154</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$126</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -608,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D154"/>
+  <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -640,12 +649,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="48" t="inlineStr">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B2" s="49" t="n">
+      <c r="B2" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -653,19 +662,19 @@
           <t>Associate Facilities Engineer (Building Maintenance)</t>
         </is>
       </c>
-      <c r="D2" s="50" t="inlineStr">
+      <c r="D2" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459144568/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="48" t="inlineStr">
+      <c r="A3" s="51" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B3" s="49" t="n">
+      <c r="B3" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -673,19 +682,19 @@
           <t>Executive Assistant - Madrid</t>
         </is>
       </c>
-      <c r="D3" s="50" t="inlineStr">
+      <c r="D3" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448303180/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B4" s="49" t="n">
+      <c r="B4" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -693,19 +702,19 @@
           <t>Benefits Analyst</t>
         </is>
       </c>
-      <c r="D4" s="50" t="inlineStr">
+      <c r="D4" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461581171/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n">
+      <c r="B5" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -713,19 +722,19 @@
           <t>Senior Manager Corporate Compliance - EMEA</t>
         </is>
       </c>
-      <c r="D5" s="50" t="inlineStr">
+      <c r="D5" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429707112/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B6" s="49" t="n">
+      <c r="B6" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -733,19 +742,19 @@
           <t>Customer Service Representative (German-speaking)</t>
         </is>
       </c>
-      <c r="D6" s="50" t="inlineStr">
+      <c r="D6" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463120173/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="48" t="inlineStr">
+      <c r="A7" s="51" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B7" s="49" t="n">
+      <c r="B7" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -753,19 +762,19 @@
           <t>Sr Enterprise Privacy Analyst</t>
         </is>
       </c>
-      <c r="D7" s="50" t="inlineStr">
+      <c r="D7" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387414194/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="48" t="inlineStr">
+      <c r="A8" s="51" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B8" s="49" t="n">
+      <c r="B8" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -773,19 +782,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D8" s="50" t="inlineStr">
+      <c r="D8" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765131/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="51" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B9" s="49" t="n">
+      <c r="B9" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -793,19 +802,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D9" s="50" t="inlineStr">
+      <c r="D9" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459303523/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="51" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B10" s="49" t="n">
+      <c r="B10" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -813,19 +822,19 @@
           <t>Associate Facilities Engineer</t>
         </is>
       </c>
-      <c r="D10" s="50" t="inlineStr">
+      <c r="D10" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448830718/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="48" t="inlineStr">
+      <c r="A11" s="51" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B11" s="49" t="n">
+      <c r="B11" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -833,19 +842,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D11" s="50" t="inlineStr">
+      <c r="D11" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454019825/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="48" t="inlineStr">
+      <c r="A12" s="51" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B12" s="49" t="n">
+      <c r="B12" s="52" t="n">
         <v>46276</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -853,19 +862,19 @@
           <t>Sr Manager Human Resources</t>
         </is>
       </c>
-      <c r="D12" s="50" t="inlineStr">
+      <c r="D12" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466052473/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="48" t="inlineStr">
+      <c r="A13" s="51" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B13" s="49" t="n">
+      <c r="B13" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -873,19 +882,19 @@
           <t>Sr. Manager - Capability Leader, Sentiment Intelligence</t>
         </is>
       </c>
-      <c r="D13" s="50" t="inlineStr">
+      <c r="D13" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459302533/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="48" t="inlineStr">
+      <c r="A14" s="51" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B14" s="49" t="n">
+      <c r="B14" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -893,19 +902,19 @@
           <t>Sr Cost Accountant</t>
         </is>
       </c>
-      <c r="D14" s="50" t="inlineStr">
+      <c r="D14" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4410011461/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="48" t="inlineStr">
+      <c r="A15" s="51" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B15" s="49" t="n">
+      <c r="B15" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -913,19 +922,19 @@
           <t>Sr Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="D15" s="50" t="inlineStr">
+      <c r="D15" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448601784/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="51" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B16" s="49" t="n">
+      <c r="B16" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -933,19 +942,19 @@
           <t>Software Development Engineer 2</t>
         </is>
       </c>
-      <c r="D16" s="50" t="inlineStr">
+      <c r="D16" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453360435/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="48" t="inlineStr">
+      <c r="A17" s="51" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B17" s="49" t="n">
+      <c r="B17" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -953,19 +962,19 @@
           <t>Sr Facilities Engineer</t>
         </is>
       </c>
-      <c r="D17" s="50" t="inlineStr">
+      <c r="D17" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446562908/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="48" t="inlineStr">
+      <c r="A18" s="51" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B18" s="49" t="n">
+      <c r="B18" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -973,19 +982,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D18" s="50" t="inlineStr">
+      <c r="D18" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453096131/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="48" t="inlineStr">
+      <c r="A19" s="51" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B19" s="49" t="n">
+      <c r="B19" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -993,19 +1002,19 @@
           <t>Accountant - Healthcare - Edinburgh</t>
         </is>
       </c>
-      <c r="D19" s="50" t="inlineStr">
+      <c r="D19" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453144035/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="48" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="B20" s="49" t="n">
+      <c r="B20" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1013,19 +1022,19 @@
           <t>Manager Finance</t>
         </is>
       </c>
-      <c r="D20" s="50" t="inlineStr">
+      <c r="D20" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462145294/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="48" t="inlineStr">
+      <c r="A21" s="51" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B21" s="49" t="n">
+      <c r="B21" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1033,19 +1042,19 @@
           <t>Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="D21" s="50" t="inlineStr">
+      <c r="D21" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448398864/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="48" t="inlineStr">
+      <c r="A22" s="51" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B22" s="49" t="n">
+      <c r="B22" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1053,19 +1062,19 @@
           <t>Senior Manager Corporate Compliance - EMEA (m/w/d)</t>
         </is>
       </c>
-      <c r="D22" s="50" t="inlineStr">
+      <c r="D22" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461752409/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="48" t="inlineStr">
+      <c r="A23" s="51" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B23" s="49" t="n">
+      <c r="B23" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1073,19 +1082,19 @@
           <t>Director, QA - Product Development Processes</t>
         </is>
       </c>
-      <c r="D23" s="50" t="inlineStr">
+      <c r="D23" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456434433/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="48" t="inlineStr">
+      <c r="A24" s="51" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B24" s="49" t="n">
+      <c r="B24" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1093,19 +1102,19 @@
           <t>Security and Privacy Compliance Analyst - Cybersecurity</t>
         </is>
       </c>
-      <c r="D24" s="50" t="inlineStr">
+      <c r="D24" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4257269392/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="48" t="inlineStr">
+      <c r="A25" s="51" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B25" s="49" t="n">
+      <c r="B25" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1113,19 +1122,19 @@
           <t>Advanced Support Specialist 1</t>
         </is>
       </c>
-      <c r="D25" s="50" t="inlineStr">
+      <c r="D25" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458769459/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="48" t="inlineStr">
+      <c r="A26" s="51" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B26" s="49" t="n">
+      <c r="B26" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1133,19 +1142,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D26" s="50" t="inlineStr">
+      <c r="D26" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451545592/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="48" t="inlineStr">
+      <c r="A27" s="51" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B27" s="49" t="n">
+      <c r="B27" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1153,19 +1162,19 @@
           <t>Sr. Manager-Vendor Management (Electronics)</t>
         </is>
       </c>
-      <c r="D27" s="50" t="inlineStr">
+      <c r="D27" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446726237/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="48" t="inlineStr">
+      <c r="A28" s="51" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B28" s="49" t="n">
+      <c r="B28" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1173,19 +1182,19 @@
           <t>Customer Success Associate</t>
         </is>
       </c>
-      <c r="D28" s="50" t="inlineStr">
+      <c r="D28" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447526678/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="48" t="inlineStr">
+      <c r="A29" s="51" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B29" s="49" t="n">
+      <c r="B29" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1193,19 +1202,19 @@
           <t>Supply Chain Analyst</t>
         </is>
       </c>
-      <c r="D29" s="50" t="inlineStr">
+      <c r="D29" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433857606/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="48" t="inlineStr">
+      <c r="A30" s="51" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B30" s="49" t="n">
+      <c r="B30" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1213,19 +1222,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D30" s="50" t="inlineStr">
+      <c r="D30" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097086/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="48" t="inlineStr">
+      <c r="A31" s="51" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B31" s="49" t="n">
+      <c r="B31" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1233,19 +1242,19 @@
           <t>Sr Quality Engineer, Supplier Quality Engineering</t>
         </is>
       </c>
-      <c r="D31" s="50" t="inlineStr">
+      <c r="D31" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4384568916/</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="48" t="inlineStr">
+      <c r="A32" s="51" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B32" s="49" t="n">
+      <c r="B32" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1253,19 +1262,19 @@
           <t>Sr QA Engineer</t>
         </is>
       </c>
-      <c r="D32" s="50" t="inlineStr">
+      <c r="D32" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465859501/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="48" t="inlineStr">
+      <c r="A33" s="51" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B33" s="49" t="n">
+      <c r="B33" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1273,19 +1282,19 @@
           <t>Staff Data Engineer</t>
         </is>
       </c>
-      <c r="D33" s="50" t="inlineStr">
+      <c r="D33" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446368700/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="48" t="inlineStr">
+      <c r="A34" s="51" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B34" s="49" t="n">
+      <c r="B34" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1293,19 +1302,19 @@
           <t>Senior Sustainability Specialist – Healthcare – Vilnius, Lithuania</t>
         </is>
       </c>
-      <c r="D34" s="50" t="inlineStr">
+      <c r="D34" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459828416/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="48" t="inlineStr">
+      <c r="A35" s="51" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B35" s="49" t="n">
+      <c r="B35" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1313,19 +1322,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D35" s="50" t="inlineStr">
+      <c r="D35" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453077256/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="48" t="inlineStr">
+      <c r="A36" s="51" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B36" s="49" t="n">
+      <c r="B36" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1333,19 +1342,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D36" s="50" t="inlineStr">
+      <c r="D36" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453093132/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="48" t="inlineStr">
+      <c r="A37" s="51" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B37" s="49" t="n">
+      <c r="B37" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1353,19 +1362,19 @@
           <t>Sr Systems Engineer</t>
         </is>
       </c>
-      <c r="D37" s="50" t="inlineStr">
+      <c r="D37" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4371263716/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="48" t="inlineStr">
+      <c r="A38" s="51" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B38" s="49" t="n">
+      <c r="B38" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1373,19 +1382,19 @@
           <t>Customer Service Representative - French Speaker</t>
         </is>
       </c>
-      <c r="D38" s="50" t="inlineStr">
+      <c r="D38" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460500502/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="48" t="inlineStr">
+      <c r="A39" s="51" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B39" s="49" t="n">
+      <c r="B39" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1393,19 +1402,19 @@
           <t>Program Manager - AI Initiatives</t>
         </is>
       </c>
-      <c r="D39" s="50" t="inlineStr">
+      <c r="D39" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435119512/</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="48" t="inlineStr">
+      <c r="A40" s="51" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="B40" s="49" t="n">
+      <c r="B40" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1413,19 +1422,19 @@
           <t>Sr Sales Trainer Diabetes MEA</t>
         </is>
       </c>
-      <c r="D40" s="50" t="inlineStr">
+      <c r="D40" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4449635545/</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="48" t="inlineStr">
+      <c r="A41" s="51" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="B41" s="49" t="n">
+      <c r="B41" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1433,19 +1442,19 @@
           <t>Territory Sales Manager (m/w/d) - Zentralschweiz : Luzern, Obwalden, Nidwalden, Uri, Chur</t>
         </is>
       </c>
-      <c r="D41" s="50" t="inlineStr">
+      <c r="D41" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453133160/</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="48" t="inlineStr">
+      <c r="A42" s="51" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B42" s="49" t="n">
+      <c r="B42" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1453,19 +1462,19 @@
           <t>Speaker Bureau and KOL Operations Manager</t>
         </is>
       </c>
-      <c r="D42" s="50" t="inlineStr">
+      <c r="D42" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4423312162/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="48" t="inlineStr">
+      <c r="A43" s="51" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B43" s="49" t="n">
+      <c r="B43" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1473,19 +1482,19 @@
           <t>Process Development Engineer 2</t>
         </is>
       </c>
-      <c r="D43" s="50" t="inlineStr">
+      <c r="D43" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437873233/</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="48" t="inlineStr">
+      <c r="A44" s="51" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B44" s="49" t="n">
+      <c r="B44" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1493,19 +1502,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
         </is>
       </c>
-      <c r="D44" s="50" t="inlineStr">
+      <c r="D44" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459811610/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="48" t="inlineStr">
+      <c r="A45" s="51" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B45" s="49" t="n">
+      <c r="B45" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1513,19 +1522,19 @@
           <t>Technical Support Representative 1</t>
         </is>
       </c>
-      <c r="D45" s="50" t="inlineStr">
+      <c r="D45" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403461287/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="48" t="inlineStr">
+      <c r="A46" s="51" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B46" s="49" t="n">
+      <c r="B46" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1533,19 +1542,19 @@
           <t>Sr Manager Regulatory Affairs- LATAM</t>
         </is>
       </c>
-      <c r="D46" s="50" t="inlineStr">
+      <c r="D46" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448606739/</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="48" t="inlineStr">
+      <c r="A47" s="51" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B47" s="49" t="n">
+      <c r="B47" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1553,19 +1562,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D47" s="50" t="inlineStr">
+      <c r="D47" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453075275/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="48" t="inlineStr">
+      <c r="A48" s="51" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B48" s="49" t="n">
+      <c r="B48" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1573,19 +1582,19 @@
           <t>Customer Account Support Specialist 2</t>
         </is>
       </c>
-      <c r="D48" s="50" t="inlineStr">
+      <c r="D48" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450027435/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="48" t="inlineStr">
+      <c r="A49" s="51" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B49" s="49" t="n">
+      <c r="B49" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1593,19 +1602,19 @@
           <t>Procurement Ops Manager (IC)</t>
         </is>
       </c>
-      <c r="D49" s="50" t="inlineStr">
+      <c r="D49" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097103/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="48" t="inlineStr">
+      <c r="A50" s="51" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B50" s="49" t="n">
+      <c r="B50" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1613,19 +1622,19 @@
           <t>Senior Software Development Engineer</t>
         </is>
       </c>
-      <c r="D50" s="50" t="inlineStr">
+      <c r="D50" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453371096/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="48" t="inlineStr">
+      <c r="A51" s="51" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B51" s="49" t="n">
+      <c r="B51" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1633,19 +1642,19 @@
           <t>Technical Support Representative 1</t>
         </is>
       </c>
-      <c r="D51" s="50" t="inlineStr">
+      <c r="D51" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403153694/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="48" t="inlineStr">
+      <c r="A52" s="51" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B52" s="49" t="n">
+      <c r="B52" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -1653,19 +1662,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D52" s="50" t="inlineStr">
+      <c r="D52" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453092177/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="48" t="inlineStr">
+      <c r="A53" s="51" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B53" s="49" t="n">
+      <c r="B53" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1673,19 +1682,19 @@
           <t>Graphic Designer 2</t>
         </is>
       </c>
-      <c r="D53" s="50" t="inlineStr">
+      <c r="D53" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456722826/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="48" t="inlineStr">
+      <c r="A54" s="51" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B54" s="49" t="n">
+      <c r="B54" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1693,19 +1702,19 @@
           <t>Purchasing Manager</t>
         </is>
       </c>
-      <c r="D54" s="50" t="inlineStr">
+      <c r="D54" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458283492/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="48" t="inlineStr">
+      <c r="A55" s="51" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B55" s="49" t="n">
+      <c r="B55" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1713,19 +1722,19 @@
           <t>Manufacturing Associate 2</t>
         </is>
       </c>
-      <c r="D55" s="50" t="inlineStr">
+      <c r="D55" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456472809/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="48" t="inlineStr">
+      <c r="A56" s="51" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B56" s="49" t="n">
+      <c r="B56" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1733,19 +1742,19 @@
           <t>Engineering Technician 2</t>
         </is>
       </c>
-      <c r="D56" s="50" t="inlineStr">
+      <c r="D56" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465624957/</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="48" t="inlineStr">
+      <c r="A57" s="51" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B57" s="49" t="n">
+      <c r="B57" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1753,19 +1762,19 @@
           <t>Engineering Technician 4</t>
         </is>
       </c>
-      <c r="D57" s="50" t="inlineStr">
+      <c r="D57" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438139166/</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="48" t="inlineStr">
+      <c r="A58" s="51" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B58" s="49" t="n">
+      <c r="B58" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1773,19 +1782,19 @@
           <t>Sr Cybersecurity Engineer</t>
         </is>
       </c>
-      <c r="D58" s="50" t="inlineStr">
+      <c r="D58" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4394381237/</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="48" t="inlineStr">
+      <c r="A59" s="51" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B59" s="49" t="n">
+      <c r="B59" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1793,19 +1802,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D59" s="50" t="inlineStr">
+      <c r="D59" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456361869/</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="48" t="inlineStr">
+      <c r="A60" s="51" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B60" s="49" t="n">
+      <c r="B60" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1813,19 +1822,19 @@
           <t>Kundenservice Medizintechnik (m/w/d) - Mainz</t>
         </is>
       </c>
-      <c r="D60" s="50" t="inlineStr">
+      <c r="D60" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462192923/</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="48" t="inlineStr">
+      <c r="A61" s="51" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B61" s="49" t="n">
+      <c r="B61" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1833,19 +1842,19 @@
           <t>Global Brand Marketing Manager (Stelo)</t>
         </is>
       </c>
-      <c r="D61" s="50" t="inlineStr">
+      <c r="D61" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435306708/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="48" t="inlineStr">
+      <c r="A62" s="51" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B62" s="49" t="n">
+      <c r="B62" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1853,19 +1862,19 @@
           <t>Business Development Lead - India (Multiple Locations)</t>
         </is>
       </c>
-      <c r="D62" s="50" t="inlineStr">
+      <c r="D62" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456463987/</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="48" t="inlineStr">
+      <c r="A63" s="51" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B63" s="49" t="n">
+      <c r="B63" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1873,19 +1882,19 @@
           <t>Sr Manager Medical Affairs</t>
         </is>
       </c>
-      <c r="D63" s="50" t="inlineStr">
+      <c r="D63" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461536483/</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="48" t="inlineStr">
+      <c r="A64" s="51" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B64" s="49" t="n">
+      <c r="B64" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1893,19 +1902,19 @@
           <t>Manufacturing Technician 3 (Weekend Day Shift)</t>
         </is>
       </c>
-      <c r="D64" s="50" t="inlineStr">
+      <c r="D64" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456731799/</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="48" t="inlineStr">
+      <c r="A65" s="51" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B65" s="49" t="n">
+      <c r="B65" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1913,19 +1922,19 @@
           <t>Staff Membrane Formulation Scientist</t>
         </is>
       </c>
-      <c r="D65" s="50" t="inlineStr">
+      <c r="D65" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438128497/</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="48" t="inlineStr">
+      <c r="A66" s="51" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B66" s="49" t="n">
+      <c r="B66" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1933,19 +1942,19 @@
           <t>Talent Acquisition Advisor (Maternity cover)</t>
         </is>
       </c>
-      <c r="D66" s="50" t="inlineStr">
+      <c r="D66" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459039247/</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="48" t="inlineStr">
+      <c r="A67" s="51" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B67" s="49" t="n">
+      <c r="B67" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1953,19 +1962,19 @@
           <t>Hardware Engineer 2</t>
         </is>
       </c>
-      <c r="D67" s="50" t="inlineStr">
+      <c r="D67" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457567279/</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="48" t="inlineStr">
+      <c r="A68" s="51" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B68" s="49" t="n">
+      <c r="B68" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1973,19 +1982,19 @@
           <t>Senior Warehouse Operative - Weekend Days</t>
         </is>
       </c>
-      <c r="D68" s="50" t="inlineStr">
+      <c r="D68" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461098658/</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="48" t="inlineStr">
+      <c r="A69" s="51" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B69" s="49" t="n">
+      <c r="B69" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1993,19 +2002,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D69" s="50" t="inlineStr">
+      <c r="D69" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453087192/</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="48" t="inlineStr">
+      <c r="A70" s="51" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="B70" s="49" t="n">
+      <c r="B70" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -2013,19 +2022,19 @@
           <t>Sr Market Access Manager</t>
         </is>
       </c>
-      <c r="D70" s="50" t="inlineStr">
+      <c r="D70" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465675855/</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="48" t="inlineStr">
+      <c r="A71" s="51" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B71" s="49" t="n">
+      <c r="B71" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -2033,19 +2042,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
         </is>
       </c>
-      <c r="D71" s="50" t="inlineStr">
+      <c r="D71" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459816548/</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="48" t="inlineStr">
+      <c r="A72" s="51" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B72" s="49" t="n">
+      <c r="B72" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -2053,19 +2062,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D72" s="50" t="inlineStr">
+      <c r="D72" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464354416/</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="48" t="inlineStr">
+      <c r="A73" s="51" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B73" s="49" t="n">
+      <c r="B73" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2073,19 +2082,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D73" s="50" t="inlineStr">
+      <c r="D73" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464339507/</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="48" t="inlineStr">
+      <c r="A74" s="51" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B74" s="49" t="n">
+      <c r="B74" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -2093,19 +2102,19 @@
           <t>Senior QA Manager (Quality Systems)</t>
         </is>
       </c>
-      <c r="D74" s="50" t="inlineStr">
+      <c r="D74" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457509031/</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="48" t="inlineStr">
+      <c r="A75" s="51" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B75" s="49" t="n">
+      <c r="B75" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -2113,1594 +2122,1034 @@
           <t>Customer Service Representative (Italian-speaking)</t>
         </is>
       </c>
-      <c r="D75" s="50" t="inlineStr">
+      <c r="D75" s="53" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446389046/</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="48" t="inlineStr">
+      <c r="A76" s="51" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B76" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Senior Forecasting Analyst</t>
+        </is>
+      </c>
+      <c r="D76" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463637144/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="51" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B77" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Sales/Inside Sales Trainer - Healthcare (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D77" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461765129/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="51" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B78" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Quality Technician 2 Back End Days</t>
+        </is>
+      </c>
+      <c r="D78" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464613132/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="51" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B79" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Mitarbeiter:innen für den deutschsprachigen Produkt- und Kundendienst (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D79" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446570417/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="51" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B80" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Senior Forecasting Analyst</t>
+        </is>
+      </c>
+      <c r="D80" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463633190/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="51" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B81" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Sr Technical Program Manager FHIR APIs- 18 months fixed term</t>
+        </is>
+      </c>
+      <c r="D81" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450696746/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="51" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B82" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Logistics Analyst</t>
+        </is>
+      </c>
+      <c r="D82" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461266744/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="51" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B83" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Senior Forecasting Analyst</t>
+        </is>
+      </c>
+      <c r="D83" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463628391/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="51" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B84" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Sr Business Process Analyst (m/w/d) - Healthcare</t>
+        </is>
+      </c>
+      <c r="D84" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4459309508/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="51" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B85" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Trade Marketing Manager - Pharmacy (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D85" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461770007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="51" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B76" s="49" t="n">
-        <v>46270</v>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>Distributor Manager - Channel Excellence (MedTech)</t>
-        </is>
-      </c>
-      <c r="D76" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463683762/</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="48" t="inlineStr">
+      <c r="B86" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
+        </is>
+      </c>
+      <c r="D86" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453076276/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="51" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B77" s="49" t="n">
-        <v>46270</v>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>Distributor Manager - Channel Excellence (MedTech)</t>
-        </is>
-      </c>
-      <c r="D77" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463684766/</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="48" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="B78" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>Senior Forecasting Analyst</t>
-        </is>
-      </c>
-      <c r="D78" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463637144/</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="48" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B79" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>Sales/Inside Sales Trainer - Healthcare (m/w/d)</t>
-        </is>
-      </c>
-      <c r="D79" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4461765129/</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="48" t="inlineStr">
+      <c r="B87" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Bracknell, UK</t>
+        </is>
+      </c>
+      <c r="D87" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4462849233/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="51" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B88" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Sr Manager Regulatory Affairs</t>
+        </is>
+      </c>
+      <c r="D88" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456106944/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="51" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B80" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>Quality Technician 2 Back End Days</t>
-        </is>
-      </c>
-      <c r="D80" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464613132/</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="48" t="inlineStr">
+      <c r="B89" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>QA Engineer Digital Systems</t>
+        </is>
+      </c>
+      <c r="D89" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444460213/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="51" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B90" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
+        </is>
+      </c>
+      <c r="D90" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453078274/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="51" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B81" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>Mitarbeiter:innen für den deutschsprachigen Produkt- und Kundendienst (m/w/d)</t>
-        </is>
-      </c>
-      <c r="D81" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4446570417/</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="48" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="B82" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>Senior Forecasting Analyst</t>
-        </is>
-      </c>
-      <c r="D82" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463633190/</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="48" t="inlineStr">
+      <c r="B91" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Contract Administration Representative (French-speaking)</t>
+        </is>
+      </c>
+      <c r="D91" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4461090763/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="51" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B83" s="49" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>Senior Service Designer, Technical Support</t>
-        </is>
-      </c>
-      <c r="D83" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455960251/</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="48" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B84" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>Sr Technical Program Manager FHIR APIs- 18 months fixed term</t>
-        </is>
-      </c>
-      <c r="D84" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4450696746/</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="48" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="B85" s="49" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>Process Technician 2 (Front End Night Shift)</t>
-        </is>
-      </c>
-      <c r="D85" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455755200/</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="48" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="B86" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>Logistics Analyst</t>
-        </is>
-      </c>
-      <c r="D86" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4461266744/</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="48" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="B87" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>Senior Forecasting Analyst</t>
-        </is>
-      </c>
-      <c r="D87" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463628391/</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="48" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B88" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>Sr Business Process Analyst (m/w/d) - Healthcare</t>
-        </is>
-      </c>
-      <c r="D88" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4459309508/</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="48" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="B89" s="49" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>Supervisor Process Engineering</t>
-        </is>
-      </c>
-      <c r="D89" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464338496/</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="48" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B90" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>Trade Marketing Manager - Pharmacy (m/w/d)</t>
-        </is>
-      </c>
-      <c r="D90" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4461770007/</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="48" t="inlineStr">
+      <c r="B92" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>GBS Engagement &amp; Service Management Lead</t>
+        </is>
+      </c>
+      <c r="D92" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4427554137/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="51" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B91" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="B93" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Senior Forecasting Analyst – Healthcare - UK</t>
+        </is>
+      </c>
+      <c r="D93" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463622979/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="51" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B94" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
+        </is>
+      </c>
+      <c r="D94" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453089165/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="51" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B95" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Senior Forecasting Analyst – Healthcare - UK</t>
+        </is>
+      </c>
+      <c r="D95" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463634192/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="51" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B96" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
+        </is>
+      </c>
+      <c r="D96" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453083196/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="51" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B97" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>Customer Service Representative, French Speaker</t>
+        </is>
+      </c>
+      <c r="D97" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4462772822/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="51" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B98" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D91" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4453076276/</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="48" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="B92" s="49" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>Sr Production Supervisor (Front End Night Shift)</t>
-        </is>
-      </c>
-      <c r="D92" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455302580/</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="48" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B93" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Bracknell, UK</t>
-        </is>
-      </c>
-      <c r="D93" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4462849233/</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="48" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="B94" s="49" t="n">
-        <v>46270</v>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>Engineering Technician 3 (Front End Day Shift)</t>
-        </is>
-      </c>
-      <c r="D94" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463698028/</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="48" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="B95" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>Sr Manager Regulatory Affairs</t>
-        </is>
-      </c>
-      <c r="D95" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456106944/</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="48" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="B96" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>QA Engineer Digital Systems</t>
-        </is>
-      </c>
-      <c r="D96" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4444460213/</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="48" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B97" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
-        </is>
-      </c>
-      <c r="D97" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4453078274/</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="48" t="inlineStr">
+      <c r="D98" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453082209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="51" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B99" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Technical Support Representative 2</t>
+        </is>
+      </c>
+      <c r="D99" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438880089/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="51" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B100" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Spanish Bilingual Customer Account Support Specialist 2</t>
+        </is>
+      </c>
+      <c r="D100" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4458704406/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="51" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B101" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>Spanish Bilingual TSR</t>
+        </is>
+      </c>
+      <c r="D101" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4407814543/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B102" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>Senior Medical Affairs Manager – Value, Evidence, and Outcomes</t>
+        </is>
+      </c>
+      <c r="D102" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443448275/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="51" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B103" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Sr Technical Writer</t>
+        </is>
+      </c>
+      <c r="D103" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465024024/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B104" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>Production Chemist 3</t>
+        </is>
+      </c>
+      <c r="D104" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464932915/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B105" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>Lead Corporate Development Manager</t>
+        </is>
+      </c>
+      <c r="D105" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4462460922/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B106" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>Staff QA Engineer</t>
+        </is>
+      </c>
+      <c r="D106" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439353245/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="51" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B107" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>HR Business Partner</t>
+        </is>
+      </c>
+      <c r="D107" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456322164/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="51" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B108" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>Procurement Ops Manager (IC)</t>
+        </is>
+      </c>
+      <c r="D108" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453082223/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="51" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B109" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>Business Process Analyst</t>
+        </is>
+      </c>
+      <c r="D109" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4414569192/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B110" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Director, Consumer Software Applications</t>
+        </is>
+      </c>
+      <c r="D110" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456380639/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B111" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Director, Consumer Software Applications</t>
+        </is>
+      </c>
+      <c r="D111" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456364824/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="51" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B112" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Associate Marketing Manager</t>
+        </is>
+      </c>
+      <c r="D112" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4451399530/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B113" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>Material Handler 1 ( RDC ) - Days 1A and 1B</t>
+        </is>
+      </c>
+      <c r="D113" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455128356/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B114" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>Material Handler 4 ( 2B Thur-Sat, every other Wednesday, Can work anytime from 5pm-5am )</t>
+        </is>
+      </c>
+      <c r="D114" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464432288/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="51" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B115" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>Senior Sterilization Engineer</t>
+        </is>
+      </c>
+      <c r="D115" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4410980549/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="51" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B98" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>Contract Administration Representative (French-speaking)</t>
-        </is>
-      </c>
-      <c r="D98" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4461090763/</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="48" t="inlineStr">
-        <is>
-          <t>Lithuania</t>
-        </is>
-      </c>
-      <c r="B99" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>GBS Engagement &amp; Service Management Lead</t>
-        </is>
-      </c>
-      <c r="D99" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4427554137/</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="48" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B100" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>Senior Forecasting Analyst – Healthcare - UK</t>
-        </is>
-      </c>
-      <c r="D100" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463622979/</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="48" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B101" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
-        </is>
-      </c>
-      <c r="D101" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4453089165/</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="48" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B102" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>Senior Forecasting Analyst – Healthcare - UK</t>
-        </is>
-      </c>
-      <c r="D102" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463634192/</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="48" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B103" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C103" s="4" t="inlineStr">
-        <is>
-          <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
-        </is>
-      </c>
-      <c r="D103" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4453083196/</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="48" t="inlineStr">
-        <is>
-          <t>Lithuania</t>
-        </is>
-      </c>
-      <c r="B104" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t>Customer Service Representative, French Speaker</t>
-        </is>
-      </c>
-      <c r="D104" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4462772822/</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="48" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B105" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
-        </is>
-      </c>
-      <c r="D105" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4453082209/</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="48" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B106" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>Technical Support Representative 2</t>
-        </is>
-      </c>
-      <c r="D106" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4438880089/</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="48" t="inlineStr">
+      <c r="B116" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>Accounts Payable Process Expert (Maternity Cover)</t>
+        </is>
+      </c>
+      <c r="D116" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4462464542/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="51" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B117" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>Staff Software Test Development Engineer</t>
+        </is>
+      </c>
+      <c r="D117" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4388377406/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B118" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>Manager Quality Compliance</t>
+        </is>
+      </c>
+      <c r="D118" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464662874/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="51" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B119" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>QA Engineer 2</t>
+        </is>
+      </c>
+      <c r="D119" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464097498/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B120" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>Staff QA Engineer</t>
+        </is>
+      </c>
+      <c r="D120" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436409441/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="51" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B121" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>Staff Equipment Engineer</t>
+        </is>
+      </c>
+      <c r="D121" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455253909/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B122" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Staff Technical Program Manager - Stelo</t>
+        </is>
+      </c>
+      <c r="D122" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455370480/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="51" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B123" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>Staff SRE SW Development Engineer</t>
+        </is>
+      </c>
+      <c r="D123" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4387683946/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B124" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>Material Handler 2 ( RDC ) - Days 1A and 1B</t>
+        </is>
+      </c>
+      <c r="D124" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455289757/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B125" s="52" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>Material Handler 2 ( RDC ) - Nights 2A and 2B</t>
+        </is>
+      </c>
+      <c r="D125" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455289751/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="54" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B107" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>Spanish Bilingual Customer Account Support Specialist 2</t>
-        </is>
-      </c>
-      <c r="D107" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4458704406/</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="48" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="B108" s="49" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>Territory Business Manager</t>
-        </is>
-      </c>
-      <c r="D108" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464350389/</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="48" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B109" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>Spanish Bilingual TSR</t>
-        </is>
-      </c>
-      <c r="D109" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4407814543/</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="48" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B110" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>Senior Medical Affairs Manager – Value, Evidence, and Outcomes</t>
-        </is>
-      </c>
-      <c r="D110" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4443448275/</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="48" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B111" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>Sr Technical Writer</t>
-        </is>
-      </c>
-      <c r="D111" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4465024024/</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="48" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B112" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C112" s="4" t="inlineStr">
-        <is>
-          <t>Production Chemist 3</t>
-        </is>
-      </c>
-      <c r="D112" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464932915/</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="48" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B113" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>Lead Corporate Development Manager</t>
-        </is>
-      </c>
-      <c r="D113" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4462460922/</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="48" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B114" s="49" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C114" s="4" t="inlineStr">
-        <is>
-          <t>Manager Systems Design Engineering</t>
-        </is>
-      </c>
-      <c r="D114" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464683405/</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="48" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B115" s="49" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>Senior Staff Process Development Engineer</t>
-        </is>
-      </c>
-      <c r="D115" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464945232/</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="48" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B116" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C116" s="4" t="inlineStr">
-        <is>
-          <t>Staff QA Engineer</t>
-        </is>
-      </c>
-      <c r="D116" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4439353245/</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="48" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B117" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C117" s="4" t="inlineStr">
-        <is>
-          <t>HR Business Partner</t>
-        </is>
-      </c>
-      <c r="D117" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456322164/</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="48" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B118" s="49" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C118" s="4" t="inlineStr">
-        <is>
-          <t>Manager, SW System &amp; Solution Dev Engineer</t>
-        </is>
-      </c>
-      <c r="D118" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464452799/</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="48" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B119" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C119" s="4" t="inlineStr">
-        <is>
-          <t>Procurement Ops Manager (IC)</t>
-        </is>
-      </c>
-      <c r="D119" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4453082223/</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="48" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B120" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>Business Process Analyst</t>
-        </is>
-      </c>
-      <c r="D120" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4414569192/</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="48" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B121" s="49" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>Supervisor Manufacturing</t>
-        </is>
-      </c>
-      <c r="D121" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4428861138/</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="48" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B122" s="49" t="n">
-        <v>46270</v>
-      </c>
-      <c r="C122" s="4" t="inlineStr">
-        <is>
-          <t>Sr IT Project Manager</t>
-        </is>
-      </c>
-      <c r="D122" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4436188818/</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="48" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B123" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C123" s="4" t="inlineStr">
-        <is>
-          <t>Sr. Director, Consumer Software Applications</t>
-        </is>
-      </c>
-      <c r="D123" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456380639/</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="48" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B124" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C124" s="4" t="inlineStr">
-        <is>
-          <t>Sr. Director, Consumer Software Applications</t>
-        </is>
-      </c>
-      <c r="D124" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456364824/</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="48" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="B125" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C125" s="4" t="inlineStr">
-        <is>
-          <t>Associate Marketing Manager</t>
-        </is>
-      </c>
-      <c r="D125" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4451399530/</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="48" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B126" s="49" t="n">
-        <v>46274</v>
+      <c r="B126" s="55" t="n">
+        <v>46276</v>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Staff Database Administrator</t>
-        </is>
-      </c>
-      <c r="D126" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456322200/</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="48" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B127" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>Material Handler 1 ( RDC ) - Days 1A and 1B</t>
-        </is>
-      </c>
-      <c r="D127" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455128356/</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="48" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B128" s="49" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>Payroll Analyst (ANZ)</t>
-        </is>
-      </c>
-      <c r="D128" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456178209/</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="48" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B129" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C129" s="4" t="inlineStr">
-        <is>
-          <t>Material Handler 4 ( 2B Thur-Sat, every other Wednesday, Can work anytime from 5pm-5am )</t>
-        </is>
-      </c>
-      <c r="D129" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464432288/</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="48" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B130" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>Senior Sterilization Engineer</t>
-        </is>
-      </c>
-      <c r="D130" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4410980549/</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="48" t="inlineStr">
-        <is>
-          <t>Lithuania</t>
-        </is>
-      </c>
-      <c r="B131" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>Accounts Payable Process Expert (Maternity Cover)</t>
-        </is>
-      </c>
-      <c r="D131" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4462464542/</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="48" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B132" s="49" t="n">
-        <v>46270</v>
-      </c>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>Senior Staff Mechanical Engineer - Characterization Lead</t>
-        </is>
-      </c>
-      <c r="D132" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4427645063/</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="48" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B133" s="49" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>Sr Enterprise Developer (Power Platform Developer)</t>
-        </is>
-      </c>
-      <c r="D133" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455767052/</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="48" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B134" s="49" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C134" s="4" t="inlineStr">
-        <is>
-          <t>Staff Software Test Development Engineer</t>
-        </is>
-      </c>
-      <c r="D134" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4388377406/</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="48" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B135" s="49" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C135" s="4" t="inlineStr">
-        <is>
-          <t>Software QA Engineer 2</t>
-        </is>
-      </c>
-      <c r="D135" s="50" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464606837/</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="51" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B136" s="52" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C136" s="4" t="inlineStr">
-        <is>
-          <t>SW Development Engineer 1 - Android</t>
-        </is>
-      </c>
-      <c r="D136" s="53" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464353380/</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="51" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B137" s="52" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C137" s="4" t="inlineStr">
-        <is>
-          <t>SW Test Development Engineer 1</t>
-        </is>
-      </c>
-      <c r="D137" s="53" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4465029007/</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="51" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B138" s="52" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>SW Development Engineer 2 - Android</t>
-        </is>
-      </c>
-      <c r="D138" s="53" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464610755/</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="51" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B139" s="52" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C139" s="4" t="inlineStr">
-        <is>
-          <t>Manager Quality Compliance</t>
-        </is>
-      </c>
-      <c r="D139" s="53" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464662874/</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="51" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B140" s="52" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C140" s="4" t="inlineStr">
-        <is>
-          <t>QA Engineer 2</t>
-        </is>
-      </c>
-      <c r="D140" s="53" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4464097498/</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="51" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B141" s="52" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>Sr Workplace Solutions Analyst</t>
-        </is>
-      </c>
-      <c r="D141" s="53" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456322161/</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="51" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B142" s="52" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C142" s="4" t="inlineStr">
-        <is>
-          <t>Staff SW Development Engineer</t>
-        </is>
-      </c>
-      <c r="D142" s="53" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4465323573/</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="51" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B143" s="52" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>Staff QA Engineer</t>
-        </is>
-      </c>
-      <c r="D143" s="53" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4436409441/</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="51" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B144" s="52" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C144" s="4" t="inlineStr">
-        <is>
-          <t>Director, Business Program Management Office</t>
-        </is>
-      </c>
-      <c r="D144" s="53" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456105988/</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="51" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B145" s="52" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C145" s="4" t="inlineStr">
-        <is>
-          <t>Staff Equipment Engineer</t>
-        </is>
-      </c>
-      <c r="D145" s="53" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455253909/</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="51" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B146" s="52" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>Desktop Support Specialist 3</t>
-        </is>
-      </c>
-      <c r="D146" s="53" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4445930979/</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="51" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B147" s="52" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C147" s="4" t="inlineStr">
-        <is>
-          <t>Sr. Staff Technical Program Manager - Stelo</t>
-        </is>
-      </c>
-      <c r="D147" s="53" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455370480/</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="51" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B148" s="52" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C148" s="4" t="inlineStr">
-        <is>
-          <t>Engineering Technician 4</t>
-        </is>
-      </c>
-      <c r="D148" s="53" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4456115187/</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="51" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B149" s="52" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C149" s="4" t="inlineStr">
-        <is>
-          <t>Staff SRE SW Development Engineer</t>
-        </is>
-      </c>
-      <c r="D149" s="53" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4387683946/</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="51" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B150" s="52" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C150" s="4" t="inlineStr">
-        <is>
-          <t>Systems Design &amp; Test Engineer 2</t>
-        </is>
-      </c>
-      <c r="D150" s="53" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4443989564/</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="51" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B151" s="52" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>Material Handler 2 ( RDC ) - Days 1A and 1B</t>
-        </is>
-      </c>
-      <c r="D151" s="53" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455289757/</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="51" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B152" s="52" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C152" s="4" t="inlineStr">
-        <is>
-          <t>Material Handler 2 ( RDC ) - Nights 2A and 2B</t>
-        </is>
-      </c>
-      <c r="D152" s="53" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4455289751/</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="51" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B153" s="52" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>Sr. SW Test Development Engineer V&amp;V</t>
-        </is>
-      </c>
-      <c r="D153" s="53" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4387839555/</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="51" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B154" s="52" t="n">
-        <v>46270</v>
-      </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>QA Inspector 2 ( Dobson ) - 1A Sun- Tues, every other Wednesday, Can work anytime from 5am-5pm</t>
-        </is>
-      </c>
-      <c r="D154" s="53" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4463691655/</t>
+          <t>Third Party Risk and Supplier Onboarding Manager</t>
+        </is>
+      </c>
+      <c r="D126" s="56" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4466048486/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D154"/>
+  <autoFilter ref="A1:D126"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -3827,34 +3276,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId153"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -617,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D126"/>
+  <dimension ref="A1:D144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -649,12 +658,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="51" t="inlineStr">
+      <c r="A2" s="54" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B2" s="52" t="n">
+      <c r="B2" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -662,19 +671,19 @@
           <t>Associate Facilities Engineer (Building Maintenance)</t>
         </is>
       </c>
-      <c r="D2" s="53" t="inlineStr">
+      <c r="D2" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459144568/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="51" t="inlineStr">
+      <c r="A3" s="54" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B3" s="52" t="n">
+      <c r="B3" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -682,19 +691,19 @@
           <t>Executive Assistant - Madrid</t>
         </is>
       </c>
-      <c r="D3" s="53" t="inlineStr">
+      <c r="D3" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448303180/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B4" s="52" t="n">
+      <c r="B4" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -702,19 +711,19 @@
           <t>Benefits Analyst</t>
         </is>
       </c>
-      <c r="D4" s="53" t="inlineStr">
+      <c r="D4" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461581171/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="51" t="inlineStr">
+      <c r="A5" s="54" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B5" s="52" t="n">
+      <c r="B5" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -722,19 +731,19 @@
           <t>Senior Manager Corporate Compliance - EMEA</t>
         </is>
       </c>
-      <c r="D5" s="53" t="inlineStr">
+      <c r="D5" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429707112/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="51" t="inlineStr">
+      <c r="A6" s="54" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B6" s="52" t="n">
+      <c r="B6" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -742,19 +751,19 @@
           <t>Customer Service Representative (German-speaking)</t>
         </is>
       </c>
-      <c r="D6" s="53" t="inlineStr">
+      <c r="D6" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463120173/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="51" t="inlineStr">
+      <c r="A7" s="54" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B7" s="52" t="n">
+      <c r="B7" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -762,19 +771,19 @@
           <t>Sr Enterprise Privacy Analyst</t>
         </is>
       </c>
-      <c r="D7" s="53" t="inlineStr">
+      <c r="D7" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387414194/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="51" t="inlineStr">
+      <c r="A8" s="54" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B8" s="52" t="n">
+      <c r="B8" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -782,19 +791,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D8" s="53" t="inlineStr">
+      <c r="D8" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765131/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="51" t="inlineStr">
+      <c r="A9" s="54" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B9" s="52" t="n">
+      <c r="B9" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -802,19 +811,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D9" s="53" t="inlineStr">
+      <c r="D9" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459303523/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="51" t="inlineStr">
+      <c r="A10" s="54" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B10" s="52" t="n">
+      <c r="B10" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -822,19 +831,19 @@
           <t>Associate Facilities Engineer</t>
         </is>
       </c>
-      <c r="D10" s="53" t="inlineStr">
+      <c r="D10" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448830718/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="51" t="inlineStr">
+      <c r="A11" s="54" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B11" s="52" t="n">
+      <c r="B11" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -842,19 +851,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D11" s="53" t="inlineStr">
+      <c r="D11" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454019825/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="51" t="inlineStr">
+      <c r="A12" s="54" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B12" s="52" t="n">
+      <c r="B12" s="55" t="n">
         <v>46276</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -862,19 +871,19 @@
           <t>Sr Manager Human Resources</t>
         </is>
       </c>
-      <c r="D12" s="53" t="inlineStr">
+      <c r="D12" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466052473/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="51" t="inlineStr">
+      <c r="A13" s="54" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B13" s="52" t="n">
+      <c r="B13" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -882,19 +891,19 @@
           <t>Sr. Manager - Capability Leader, Sentiment Intelligence</t>
         </is>
       </c>
-      <c r="D13" s="53" t="inlineStr">
+      <c r="D13" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459302533/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="51" t="inlineStr">
+      <c r="A14" s="54" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B14" s="52" t="n">
+      <c r="B14" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -902,19 +911,19 @@
           <t>Sr Cost Accountant</t>
         </is>
       </c>
-      <c r="D14" s="53" t="inlineStr">
+      <c r="D14" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4410011461/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="51" t="inlineStr">
+      <c r="A15" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B15" s="52" t="n">
+      <c r="B15" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -922,19 +931,19 @@
           <t>Sr Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="D15" s="53" t="inlineStr">
+      <c r="D15" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448601784/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="51" t="inlineStr">
+      <c r="A16" s="54" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B16" s="52" t="n">
+      <c r="B16" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -942,19 +951,19 @@
           <t>Software Development Engineer 2</t>
         </is>
       </c>
-      <c r="D16" s="53" t="inlineStr">
+      <c r="D16" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453360435/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="51" t="inlineStr">
+      <c r="A17" s="54" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B17" s="52" t="n">
+      <c r="B17" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -962,19 +971,19 @@
           <t>Sr Facilities Engineer</t>
         </is>
       </c>
-      <c r="D17" s="53" t="inlineStr">
+      <c r="D17" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446562908/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="51" t="inlineStr">
+      <c r="A18" s="54" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B18" s="52" t="n">
+      <c r="B18" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -982,19 +991,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D18" s="53" t="inlineStr">
+      <c r="D18" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453096131/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="51" t="inlineStr">
+      <c r="A19" s="54" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B19" s="52" t="n">
+      <c r="B19" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1002,19 +1011,19 @@
           <t>Accountant - Healthcare - Edinburgh</t>
         </is>
       </c>
-      <c r="D19" s="53" t="inlineStr">
+      <c r="D19" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453144035/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="51" t="inlineStr">
+      <c r="A20" s="54" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="B20" s="52" t="n">
+      <c r="B20" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1022,19 +1031,19 @@
           <t>Manager Finance</t>
         </is>
       </c>
-      <c r="D20" s="53" t="inlineStr">
+      <c r="D20" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462145294/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="51" t="inlineStr">
+      <c r="A21" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B21" s="52" t="n">
+      <c r="B21" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1042,19 +1051,19 @@
           <t>Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="D21" s="53" t="inlineStr">
+      <c r="D21" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448398864/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="51" t="inlineStr">
+      <c r="A22" s="54" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B22" s="52" t="n">
+      <c r="B22" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1062,19 +1071,19 @@
           <t>Senior Manager Corporate Compliance - EMEA (m/w/d)</t>
         </is>
       </c>
-      <c r="D22" s="53" t="inlineStr">
+      <c r="D22" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461752409/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="51" t="inlineStr">
+      <c r="A23" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B23" s="52" t="n">
+      <c r="B23" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1082,19 +1091,19 @@
           <t>Director, QA - Product Development Processes</t>
         </is>
       </c>
-      <c r="D23" s="53" t="inlineStr">
+      <c r="D23" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456434433/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="51" t="inlineStr">
+      <c r="A24" s="54" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B24" s="52" t="n">
+      <c r="B24" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1102,19 +1111,19 @@
           <t>Security and Privacy Compliance Analyst - Cybersecurity</t>
         </is>
       </c>
-      <c r="D24" s="53" t="inlineStr">
+      <c r="D24" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4257269392/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="51" t="inlineStr">
+      <c r="A25" s="54" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B25" s="52" t="n">
+      <c r="B25" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1122,19 +1131,19 @@
           <t>Advanced Support Specialist 1</t>
         </is>
       </c>
-      <c r="D25" s="53" t="inlineStr">
+      <c r="D25" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458769459/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="51" t="inlineStr">
+      <c r="A26" s="54" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B26" s="52" t="n">
+      <c r="B26" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1142,19 +1151,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D26" s="53" t="inlineStr">
+      <c r="D26" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451545592/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="51" t="inlineStr">
+      <c r="A27" s="54" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B27" s="52" t="n">
+      <c r="B27" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1162,19 +1171,19 @@
           <t>Sr. Manager-Vendor Management (Electronics)</t>
         </is>
       </c>
-      <c r="D27" s="53" t="inlineStr">
+      <c r="D27" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446726237/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="51" t="inlineStr">
+      <c r="A28" s="54" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B28" s="52" t="n">
+      <c r="B28" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1182,19 +1191,19 @@
           <t>Customer Success Associate</t>
         </is>
       </c>
-      <c r="D28" s="53" t="inlineStr">
+      <c r="D28" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447526678/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="51" t="inlineStr">
+      <c r="A29" s="54" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B29" s="52" t="n">
+      <c r="B29" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1202,19 +1211,19 @@
           <t>Supply Chain Analyst</t>
         </is>
       </c>
-      <c r="D29" s="53" t="inlineStr">
+      <c r="D29" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433857606/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="51" t="inlineStr">
+      <c r="A30" s="54" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B30" s="52" t="n">
+      <c r="B30" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1222,19 +1231,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D30" s="53" t="inlineStr">
+      <c r="D30" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097086/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="51" t="inlineStr">
+      <c r="A31" s="54" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B31" s="52" t="n">
+      <c r="B31" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1242,19 +1251,19 @@
           <t>Sr Quality Engineer, Supplier Quality Engineering</t>
         </is>
       </c>
-      <c r="D31" s="53" t="inlineStr">
+      <c r="D31" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4384568916/</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="51" t="inlineStr">
+      <c r="A32" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B32" s="52" t="n">
+      <c r="B32" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1262,19 +1271,19 @@
           <t>Sr QA Engineer</t>
         </is>
       </c>
-      <c r="D32" s="53" t="inlineStr">
+      <c r="D32" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465859501/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="51" t="inlineStr">
+      <c r="A33" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B33" s="52" t="n">
+      <c r="B33" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1282,19 +1291,19 @@
           <t>Staff Data Engineer</t>
         </is>
       </c>
-      <c r="D33" s="53" t="inlineStr">
+      <c r="D33" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446368700/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="51" t="inlineStr">
+      <c r="A34" s="54" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B34" s="52" t="n">
+      <c r="B34" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1302,19 +1311,19 @@
           <t>Senior Sustainability Specialist – Healthcare – Vilnius, Lithuania</t>
         </is>
       </c>
-      <c r="D34" s="53" t="inlineStr">
+      <c r="D34" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459828416/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="51" t="inlineStr">
+      <c r="A35" s="54" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B35" s="52" t="n">
+      <c r="B35" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1322,19 +1331,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D35" s="53" t="inlineStr">
+      <c r="D35" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453077256/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="51" t="inlineStr">
+      <c r="A36" s="54" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B36" s="52" t="n">
+      <c r="B36" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1342,19 +1351,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D36" s="53" t="inlineStr">
+      <c r="D36" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453093132/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="51" t="inlineStr">
+      <c r="A37" s="54" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B37" s="52" t="n">
+      <c r="B37" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1362,19 +1371,19 @@
           <t>Sr Systems Engineer</t>
         </is>
       </c>
-      <c r="D37" s="53" t="inlineStr">
+      <c r="D37" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4371263716/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="51" t="inlineStr">
+      <c r="A38" s="54" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B38" s="52" t="n">
+      <c r="B38" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1382,19 +1391,19 @@
           <t>Customer Service Representative - French Speaker</t>
         </is>
       </c>
-      <c r="D38" s="53" t="inlineStr">
+      <c r="D38" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460500502/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="51" t="inlineStr">
+      <c r="A39" s="54" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B39" s="52" t="n">
+      <c r="B39" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1402,19 +1411,19 @@
           <t>Program Manager - AI Initiatives</t>
         </is>
       </c>
-      <c r="D39" s="53" t="inlineStr">
+      <c r="D39" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435119512/</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="51" t="inlineStr">
+      <c r="A40" s="54" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="B40" s="52" t="n">
+      <c r="B40" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1422,19 +1431,19 @@
           <t>Sr Sales Trainer Diabetes MEA</t>
         </is>
       </c>
-      <c r="D40" s="53" t="inlineStr">
+      <c r="D40" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4449635545/</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="51" t="inlineStr">
+      <c r="A41" s="54" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="B41" s="52" t="n">
+      <c r="B41" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1442,19 +1451,19 @@
           <t>Territory Sales Manager (m/w/d) - Zentralschweiz : Luzern, Obwalden, Nidwalden, Uri, Chur</t>
         </is>
       </c>
-      <c r="D41" s="53" t="inlineStr">
+      <c r="D41" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453133160/</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="51" t="inlineStr">
+      <c r="A42" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B42" s="52" t="n">
+      <c r="B42" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1462,19 +1471,19 @@
           <t>Speaker Bureau and KOL Operations Manager</t>
         </is>
       </c>
-      <c r="D42" s="53" t="inlineStr">
+      <c r="D42" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4423312162/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="51" t="inlineStr">
+      <c r="A43" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B43" s="52" t="n">
+      <c r="B43" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1482,19 +1491,19 @@
           <t>Process Development Engineer 2</t>
         </is>
       </c>
-      <c r="D43" s="53" t="inlineStr">
+      <c r="D43" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437873233/</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="51" t="inlineStr">
+      <c r="A44" s="54" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B44" s="52" t="n">
+      <c r="B44" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1502,19 +1511,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
         </is>
       </c>
-      <c r="D44" s="53" t="inlineStr">
+      <c r="D44" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459811610/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="51" t="inlineStr">
+      <c r="A45" s="54" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B45" s="52" t="n">
+      <c r="B45" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1522,19 +1531,19 @@
           <t>Technical Support Representative 1</t>
         </is>
       </c>
-      <c r="D45" s="53" t="inlineStr">
+      <c r="D45" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403461287/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="51" t="inlineStr">
+      <c r="A46" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B46" s="52" t="n">
+      <c r="B46" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1542,19 +1551,19 @@
           <t>Sr Manager Regulatory Affairs- LATAM</t>
         </is>
       </c>
-      <c r="D46" s="53" t="inlineStr">
+      <c r="D46" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448606739/</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="51" t="inlineStr">
+      <c r="A47" s="54" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B47" s="52" t="n">
+      <c r="B47" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1562,19 +1571,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D47" s="53" t="inlineStr">
+      <c r="D47" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453075275/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="51" t="inlineStr">
+      <c r="A48" s="54" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B48" s="52" t="n">
+      <c r="B48" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1582,19 +1591,19 @@
           <t>Customer Account Support Specialist 2</t>
         </is>
       </c>
-      <c r="D48" s="53" t="inlineStr">
+      <c r="D48" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450027435/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="51" t="inlineStr">
+      <c r="A49" s="54" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B49" s="52" t="n">
+      <c r="B49" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1602,19 +1611,19 @@
           <t>Procurement Ops Manager (IC)</t>
         </is>
       </c>
-      <c r="D49" s="53" t="inlineStr">
+      <c r="D49" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097103/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="51" t="inlineStr">
+      <c r="A50" s="54" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B50" s="52" t="n">
+      <c r="B50" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1622,19 +1631,19 @@
           <t>Senior Software Development Engineer</t>
         </is>
       </c>
-      <c r="D50" s="53" t="inlineStr">
+      <c r="D50" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453371096/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="51" t="inlineStr">
+      <c r="A51" s="54" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B51" s="52" t="n">
+      <c r="B51" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1642,19 +1651,19 @@
           <t>Technical Support Representative 1</t>
         </is>
       </c>
-      <c r="D51" s="53" t="inlineStr">
+      <c r="D51" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403153694/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="51" t="inlineStr">
+      <c r="A52" s="54" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B52" s="52" t="n">
+      <c r="B52" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -1662,19 +1671,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D52" s="53" t="inlineStr">
+      <c r="D52" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453092177/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="51" t="inlineStr">
+      <c r="A53" s="54" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B53" s="52" t="n">
+      <c r="B53" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1682,19 +1691,19 @@
           <t>Graphic Designer 2</t>
         </is>
       </c>
-      <c r="D53" s="53" t="inlineStr">
+      <c r="D53" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456722826/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="51" t="inlineStr">
+      <c r="A54" s="54" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B54" s="52" t="n">
+      <c r="B54" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1702,19 +1711,19 @@
           <t>Purchasing Manager</t>
         </is>
       </c>
-      <c r="D54" s="53" t="inlineStr">
+      <c r="D54" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458283492/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="51" t="inlineStr">
+      <c r="A55" s="54" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B55" s="52" t="n">
+      <c r="B55" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1722,19 +1731,19 @@
           <t>Manufacturing Associate 2</t>
         </is>
       </c>
-      <c r="D55" s="53" t="inlineStr">
+      <c r="D55" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456472809/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="51" t="inlineStr">
+      <c r="A56" s="54" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B56" s="52" t="n">
+      <c r="B56" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1742,19 +1751,19 @@
           <t>Engineering Technician 2</t>
         </is>
       </c>
-      <c r="D56" s="53" t="inlineStr">
+      <c r="D56" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465624957/</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="51" t="inlineStr">
+      <c r="A57" s="54" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B57" s="52" t="n">
+      <c r="B57" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1762,19 +1771,19 @@
           <t>Engineering Technician 4</t>
         </is>
       </c>
-      <c r="D57" s="53" t="inlineStr">
+      <c r="D57" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438139166/</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="51" t="inlineStr">
+      <c r="A58" s="54" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B58" s="52" t="n">
+      <c r="B58" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1782,19 +1791,19 @@
           <t>Sr Cybersecurity Engineer</t>
         </is>
       </c>
-      <c r="D58" s="53" t="inlineStr">
+      <c r="D58" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4394381237/</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="51" t="inlineStr">
+      <c r="A59" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B59" s="52" t="n">
+      <c r="B59" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1802,19 +1811,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D59" s="53" t="inlineStr">
+      <c r="D59" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456361869/</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="51" t="inlineStr">
+      <c r="A60" s="54" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B60" s="52" t="n">
+      <c r="B60" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1822,19 +1831,19 @@
           <t>Kundenservice Medizintechnik (m/w/d) - Mainz</t>
         </is>
       </c>
-      <c r="D60" s="53" t="inlineStr">
+      <c r="D60" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462192923/</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="51" t="inlineStr">
+      <c r="A61" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B61" s="52" t="n">
+      <c r="B61" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1842,19 +1851,19 @@
           <t>Global Brand Marketing Manager (Stelo)</t>
         </is>
       </c>
-      <c r="D61" s="53" t="inlineStr">
+      <c r="D61" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435306708/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="51" t="inlineStr">
+      <c r="A62" s="54" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B62" s="52" t="n">
+      <c r="B62" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1862,19 +1871,19 @@
           <t>Business Development Lead - India (Multiple Locations)</t>
         </is>
       </c>
-      <c r="D62" s="53" t="inlineStr">
+      <c r="D62" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456463987/</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="51" t="inlineStr">
+      <c r="A63" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B63" s="52" t="n">
+      <c r="B63" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1882,19 +1891,19 @@
           <t>Sr Manager Medical Affairs</t>
         </is>
       </c>
-      <c r="D63" s="53" t="inlineStr">
+      <c r="D63" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461536483/</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="51" t="inlineStr">
+      <c r="A64" s="54" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B64" s="52" t="n">
+      <c r="B64" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1902,19 +1911,19 @@
           <t>Manufacturing Technician 3 (Weekend Day Shift)</t>
         </is>
       </c>
-      <c r="D64" s="53" t="inlineStr">
+      <c r="D64" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456731799/</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="51" t="inlineStr">
+      <c r="A65" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B65" s="52" t="n">
+      <c r="B65" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1922,19 +1931,19 @@
           <t>Staff Membrane Formulation Scientist</t>
         </is>
       </c>
-      <c r="D65" s="53" t="inlineStr">
+      <c r="D65" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438128497/</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="51" t="inlineStr">
+      <c r="A66" s="54" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B66" s="52" t="n">
+      <c r="B66" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1942,19 +1951,19 @@
           <t>Talent Acquisition Advisor (Maternity cover)</t>
         </is>
       </c>
-      <c r="D66" s="53" t="inlineStr">
+      <c r="D66" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459039247/</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="51" t="inlineStr">
+      <c r="A67" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B67" s="52" t="n">
+      <c r="B67" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1962,19 +1971,19 @@
           <t>Hardware Engineer 2</t>
         </is>
       </c>
-      <c r="D67" s="53" t="inlineStr">
+      <c r="D67" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457567279/</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="51" t="inlineStr">
+      <c r="A68" s="54" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B68" s="52" t="n">
+      <c r="B68" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1982,19 +1991,19 @@
           <t>Senior Warehouse Operative - Weekend Days</t>
         </is>
       </c>
-      <c r="D68" s="53" t="inlineStr">
+      <c r="D68" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461098658/</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="51" t="inlineStr">
+      <c r="A69" s="54" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B69" s="52" t="n">
+      <c r="B69" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -2002,19 +2011,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D69" s="53" t="inlineStr">
+      <c r="D69" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453087192/</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="51" t="inlineStr">
+      <c r="A70" s="54" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="B70" s="52" t="n">
+      <c r="B70" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -2022,19 +2031,19 @@
           <t>Sr Market Access Manager</t>
         </is>
       </c>
-      <c r="D70" s="53" t="inlineStr">
+      <c r="D70" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465675855/</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="51" t="inlineStr">
+      <c r="A71" s="54" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B71" s="52" t="n">
+      <c r="B71" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -2042,19 +2051,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
         </is>
       </c>
-      <c r="D71" s="53" t="inlineStr">
+      <c r="D71" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459816548/</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="51" t="inlineStr">
+      <c r="A72" s="54" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B72" s="52" t="n">
+      <c r="B72" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -2062,19 +2071,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D72" s="53" t="inlineStr">
+      <c r="D72" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464354416/</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="51" t="inlineStr">
+      <c r="A73" s="54" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B73" s="52" t="n">
+      <c r="B73" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2082,19 +2091,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D73" s="53" t="inlineStr">
+      <c r="D73" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464339507/</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="51" t="inlineStr">
+      <c r="A74" s="54" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B74" s="52" t="n">
+      <c r="B74" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -2102,19 +2111,19 @@
           <t>Senior QA Manager (Quality Systems)</t>
         </is>
       </c>
-      <c r="D74" s="53" t="inlineStr">
+      <c r="D74" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457509031/</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="51" t="inlineStr">
+      <c r="A75" s="54" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B75" s="52" t="n">
+      <c r="B75" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -2122,19 +2131,19 @@
           <t>Customer Service Representative (Italian-speaking)</t>
         </is>
       </c>
-      <c r="D75" s="53" t="inlineStr">
+      <c r="D75" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446389046/</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="51" t="inlineStr">
+      <c r="A76" s="54" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B76" s="52" t="n">
+      <c r="B76" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -2142,19 +2151,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D76" s="53" t="inlineStr">
+      <c r="D76" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463637144/</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="51" t="inlineStr">
+      <c r="A77" s="54" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B77" s="52" t="n">
+      <c r="B77" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -2162,19 +2171,19 @@
           <t>Sales/Inside Sales Trainer - Healthcare (m/w/d)</t>
         </is>
       </c>
-      <c r="D77" s="53" t="inlineStr">
+      <c r="D77" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765129/</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="51" t="inlineStr">
+      <c r="A78" s="54" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B78" s="52" t="n">
+      <c r="B78" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -2182,19 +2191,19 @@
           <t>Quality Technician 2 Back End Days</t>
         </is>
       </c>
-      <c r="D78" s="53" t="inlineStr">
+      <c r="D78" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464613132/</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="51" t="inlineStr">
+      <c r="A79" s="54" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B79" s="52" t="n">
+      <c r="B79" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -2202,19 +2211,19 @@
           <t>Mitarbeiter:innen für den deutschsprachigen Produkt- und Kundendienst (m/w/d)</t>
         </is>
       </c>
-      <c r="D79" s="53" t="inlineStr">
+      <c r="D79" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446570417/</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="51" t="inlineStr">
+      <c r="A80" s="54" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B80" s="52" t="n">
+      <c r="B80" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -2222,19 +2231,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D80" s="53" t="inlineStr">
+      <c r="D80" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463633190/</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="51" t="inlineStr">
+      <c r="A81" s="54" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="B81" s="52" t="n">
+      <c r="B81" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2242,19 +2251,19 @@
           <t>Sr Technical Program Manager FHIR APIs- 18 months fixed term</t>
         </is>
       </c>
-      <c r="D81" s="53" t="inlineStr">
+      <c r="D81" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450696746/</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="51" t="inlineStr">
+      <c r="A82" s="54" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B82" s="52" t="n">
+      <c r="B82" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -2262,19 +2271,19 @@
           <t>Logistics Analyst</t>
         </is>
       </c>
-      <c r="D82" s="53" t="inlineStr">
+      <c r="D82" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461266744/</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="51" t="inlineStr">
+      <c r="A83" s="54" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B83" s="52" t="n">
+      <c r="B83" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2282,19 +2291,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D83" s="53" t="inlineStr">
+      <c r="D83" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463628391/</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="51" t="inlineStr">
+      <c r="A84" s="54" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B84" s="52" t="n">
+      <c r="B84" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -2302,19 +2311,19 @@
           <t>Sr Business Process Analyst (m/w/d) - Healthcare</t>
         </is>
       </c>
-      <c r="D84" s="53" t="inlineStr">
+      <c r="D84" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459309508/</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="51" t="inlineStr">
+      <c r="A85" s="54" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B85" s="52" t="n">
+      <c r="B85" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2322,19 +2331,19 @@
           <t>Trade Marketing Manager - Pharmacy (m/w/d)</t>
         </is>
       </c>
-      <c r="D85" s="53" t="inlineStr">
+      <c r="D85" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461770007/</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="51" t="inlineStr">
+      <c r="A86" s="54" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B86" s="52" t="n">
+      <c r="B86" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -2342,19 +2351,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D86" s="53" t="inlineStr">
+      <c r="D86" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453076276/</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="51" t="inlineStr">
+      <c r="A87" s="54" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B87" s="52" t="n">
+      <c r="B87" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -2362,19 +2371,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Bracknell, UK</t>
         </is>
       </c>
-      <c r="D87" s="53" t="inlineStr">
+      <c r="D87" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462849233/</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="51" t="inlineStr">
+      <c r="A88" s="54" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B88" s="52" t="n">
+      <c r="B88" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -2382,19 +2391,19 @@
           <t>Sr Manager Regulatory Affairs</t>
         </is>
       </c>
-      <c r="D88" s="53" t="inlineStr">
+      <c r="D88" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456106944/</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="51" t="inlineStr">
+      <c r="A89" s="54" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B89" s="52" t="n">
+      <c r="B89" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -2402,19 +2411,19 @@
           <t>QA Engineer Digital Systems</t>
         </is>
       </c>
-      <c r="D89" s="53" t="inlineStr">
+      <c r="D89" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444460213/</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="51" t="inlineStr">
+      <c r="A90" s="54" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B90" s="52" t="n">
+      <c r="B90" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -2422,19 +2431,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D90" s="53" t="inlineStr">
+      <c r="D90" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453078274/</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="51" t="inlineStr">
+      <c r="A91" s="54" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B91" s="52" t="n">
+      <c r="B91" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -2442,19 +2451,19 @@
           <t>Contract Administration Representative (French-speaking)</t>
         </is>
       </c>
-      <c r="D91" s="53" t="inlineStr">
+      <c r="D91" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461090763/</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="51" t="inlineStr">
+      <c r="A92" s="54" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B92" s="52" t="n">
+      <c r="B92" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -2462,19 +2471,19 @@
           <t>GBS Engagement &amp; Service Management Lead</t>
         </is>
       </c>
-      <c r="D92" s="53" t="inlineStr">
+      <c r="D92" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427554137/</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="51" t="inlineStr">
+      <c r="A93" s="54" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B93" s="52" t="n">
+      <c r="B93" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -2482,19 +2491,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D93" s="53" t="inlineStr">
+      <c r="D93" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463622979/</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="51" t="inlineStr">
+      <c r="A94" s="54" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B94" s="52" t="n">
+      <c r="B94" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -2502,19 +2511,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D94" s="53" t="inlineStr">
+      <c r="D94" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453089165/</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="51" t="inlineStr">
+      <c r="A95" s="54" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B95" s="52" t="n">
+      <c r="B95" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -2522,19 +2531,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D95" s="53" t="inlineStr">
+      <c r="D95" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463634192/</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="51" t="inlineStr">
+      <c r="A96" s="54" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B96" s="52" t="n">
+      <c r="B96" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -2542,19 +2551,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D96" s="53" t="inlineStr">
+      <c r="D96" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453083196/</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="51" t="inlineStr">
+      <c r="A97" s="54" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B97" s="52" t="n">
+      <c r="B97" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -2562,19 +2571,19 @@
           <t>Customer Service Representative, French Speaker</t>
         </is>
       </c>
-      <c r="D97" s="53" t="inlineStr">
+      <c r="D97" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462772822/</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="51" t="inlineStr">
+      <c r="A98" s="54" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B98" s="52" t="n">
+      <c r="B98" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -2582,19 +2591,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D98" s="53" t="inlineStr">
+      <c r="D98" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082209/</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="51" t="inlineStr">
+      <c r="A99" s="54" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="B99" s="52" t="n">
+      <c r="B99" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -2602,19 +2611,19 @@
           <t>Technical Support Representative 2</t>
         </is>
       </c>
-      <c r="D99" s="53" t="inlineStr">
+      <c r="D99" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438880089/</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="51" t="inlineStr">
+      <c r="A100" s="54" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B100" s="52" t="n">
+      <c r="B100" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -2622,19 +2631,19 @@
           <t>Spanish Bilingual Customer Account Support Specialist 2</t>
         </is>
       </c>
-      <c r="D100" s="53" t="inlineStr">
+      <c r="D100" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458704406/</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="51" t="inlineStr">
+      <c r="A101" s="54" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B101" s="52" t="n">
+      <c r="B101" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -2642,19 +2651,19 @@
           <t>Spanish Bilingual TSR</t>
         </is>
       </c>
-      <c r="D101" s="53" t="inlineStr">
+      <c r="D101" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4407814543/</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="51" t="inlineStr">
+      <c r="A102" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B102" s="52" t="n">
+      <c r="B102" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -2662,19 +2671,19 @@
           <t>Senior Medical Affairs Manager – Value, Evidence, and Outcomes</t>
         </is>
       </c>
-      <c r="D102" s="53" t="inlineStr">
+      <c r="D102" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443448275/</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="51" t="inlineStr">
+      <c r="A103" s="54" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B103" s="52" t="n">
+      <c r="B103" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -2682,19 +2691,19 @@
           <t>Sr Technical Writer</t>
         </is>
       </c>
-      <c r="D103" s="53" t="inlineStr">
+      <c r="D103" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465024024/</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="51" t="inlineStr">
+      <c r="A104" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B104" s="52" t="n">
+      <c r="B104" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -2702,19 +2711,19 @@
           <t>Production Chemist 3</t>
         </is>
       </c>
-      <c r="D104" s="53" t="inlineStr">
+      <c r="D104" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464932915/</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="51" t="inlineStr">
+      <c r="A105" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B105" s="52" t="n">
+      <c r="B105" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -2722,19 +2731,19 @@
           <t>Lead Corporate Development Manager</t>
         </is>
       </c>
-      <c r="D105" s="53" t="inlineStr">
+      <c r="D105" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462460922/</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="51" t="inlineStr">
+      <c r="A106" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B106" s="52" t="n">
+      <c r="B106" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -2742,19 +2751,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D106" s="53" t="inlineStr">
+      <c r="D106" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439353245/</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="51" t="inlineStr">
+      <c r="A107" s="54" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B107" s="52" t="n">
+      <c r="B107" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -2762,19 +2771,19 @@
           <t>HR Business Partner</t>
         </is>
       </c>
-      <c r="D107" s="53" t="inlineStr">
+      <c r="D107" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456322164/</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="51" t="inlineStr">
+      <c r="A108" s="54" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B108" s="52" t="n">
+      <c r="B108" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -2782,19 +2791,19 @@
           <t>Procurement Ops Manager (IC)</t>
         </is>
       </c>
-      <c r="D108" s="53" t="inlineStr">
+      <c r="D108" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082223/</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="51" t="inlineStr">
+      <c r="A109" s="54" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B109" s="52" t="n">
+      <c r="B109" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -2802,19 +2811,19 @@
           <t>Business Process Analyst</t>
         </is>
       </c>
-      <c r="D109" s="53" t="inlineStr">
+      <c r="D109" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4414569192/</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="51" t="inlineStr">
+      <c r="A110" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B110" s="52" t="n">
+      <c r="B110" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -2822,19 +2831,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D110" s="53" t="inlineStr">
+      <c r="D110" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456380639/</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="51" t="inlineStr">
+      <c r="A111" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B111" s="52" t="n">
+      <c r="B111" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -2842,19 +2851,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D111" s="53" t="inlineStr">
+      <c r="D111" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456364824/</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="51" t="inlineStr">
+      <c r="A112" s="54" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="B112" s="52" t="n">
+      <c r="B112" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -2862,19 +2871,19 @@
           <t>Associate Marketing Manager</t>
         </is>
       </c>
-      <c r="D112" s="53" t="inlineStr">
+      <c r="D112" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451399530/</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="51" t="inlineStr">
+      <c r="A113" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B113" s="52" t="n">
+      <c r="B113" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -2882,19 +2891,19 @@
           <t>Material Handler 1 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D113" s="53" t="inlineStr">
+      <c r="D113" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455128356/</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="51" t="inlineStr">
+      <c r="A114" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B114" s="52" t="n">
+      <c r="B114" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -2902,19 +2911,19 @@
           <t>Material Handler 4 ( 2B Thur-Sat, every other Wednesday, Can work anytime from 5pm-5am )</t>
         </is>
       </c>
-      <c r="D114" s="53" t="inlineStr">
+      <c r="D114" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464432288/</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="51" t="inlineStr">
+      <c r="A115" s="54" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B115" s="52" t="n">
+      <c r="B115" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -2922,19 +2931,19 @@
           <t>Senior Sterilization Engineer</t>
         </is>
       </c>
-      <c r="D115" s="53" t="inlineStr">
+      <c r="D115" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4410980549/</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="51" t="inlineStr">
+      <c r="A116" s="54" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B116" s="52" t="n">
+      <c r="B116" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -2942,19 +2951,19 @@
           <t>Accounts Payable Process Expert (Maternity Cover)</t>
         </is>
       </c>
-      <c r="D116" s="53" t="inlineStr">
+      <c r="D116" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462464542/</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="51" t="inlineStr">
+      <c r="A117" s="54" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B117" s="52" t="n">
+      <c r="B117" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -2962,19 +2971,19 @@
           <t>Staff Software Test Development Engineer</t>
         </is>
       </c>
-      <c r="D117" s="53" t="inlineStr">
+      <c r="D117" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4388377406/</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="51" t="inlineStr">
+      <c r="A118" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B118" s="52" t="n">
+      <c r="B118" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -2982,19 +2991,19 @@
           <t>Manager Quality Compliance</t>
         </is>
       </c>
-      <c r="D118" s="53" t="inlineStr">
+      <c r="D118" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464662874/</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="51" t="inlineStr">
+      <c r="A119" s="54" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B119" s="52" t="n">
+      <c r="B119" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -3002,19 +3011,19 @@
           <t>QA Engineer 2</t>
         </is>
       </c>
-      <c r="D119" s="53" t="inlineStr">
+      <c r="D119" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464097498/</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="51" t="inlineStr">
+      <c r="A120" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B120" s="52" t="n">
+      <c r="B120" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -3022,19 +3031,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D120" s="53" t="inlineStr">
+      <c r="D120" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436409441/</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="51" t="inlineStr">
+      <c r="A121" s="54" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B121" s="52" t="n">
+      <c r="B121" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -3042,19 +3051,19 @@
           <t>Staff Equipment Engineer</t>
         </is>
       </c>
-      <c r="D121" s="53" t="inlineStr">
+      <c r="D121" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455253909/</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="51" t="inlineStr">
+      <c r="A122" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B122" s="52" t="n">
+      <c r="B122" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -3062,19 +3071,19 @@
           <t>Sr. Staff Technical Program Manager - Stelo</t>
         </is>
       </c>
-      <c r="D122" s="53" t="inlineStr">
+      <c r="D122" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455370480/</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="51" t="inlineStr">
+      <c r="A123" s="54" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B123" s="52" t="n">
+      <c r="B123" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -3082,19 +3091,19 @@
           <t>Staff SRE SW Development Engineer</t>
         </is>
       </c>
-      <c r="D123" s="53" t="inlineStr">
+      <c r="D123" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387683946/</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="51" t="inlineStr">
+      <c r="A124" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B124" s="52" t="n">
+      <c r="B124" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -3102,19 +3111,19 @@
           <t>Material Handler 2 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D124" s="53" t="inlineStr">
+      <c r="D124" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455289757/</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="51" t="inlineStr">
+      <c r="A125" s="54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B125" s="52" t="n">
+      <c r="B125" s="55" t="n">
         <v>46275</v>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -3122,7 +3131,7 @@
           <t>Material Handler 2 ( RDC ) - Nights 2A and 2B</t>
         </is>
       </c>
-      <c r="D125" s="53" t="inlineStr">
+      <c r="D125" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455289751/</t>
         </is>
@@ -3148,8 +3157,368 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="57" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B127" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>Distributor Manager - Channel Excellence (MedTech)</t>
+        </is>
+      </c>
+      <c r="D127" s="59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463683762/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="57" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B128" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>Distributor Manager - Channel Excellence (MedTech)</t>
+        </is>
+      </c>
+      <c r="D128" s="59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463684766/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="57" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B129" s="58" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>Senior Service Designer, Technical Support</t>
+        </is>
+      </c>
+      <c r="D129" s="59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455960251/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="57" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B130" s="58" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>Process Technician 2 (Front End Night Shift)</t>
+        </is>
+      </c>
+      <c r="D130" s="59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455755200/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="57" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B131" s="58" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>Supervisor Process Engineering</t>
+        </is>
+      </c>
+      <c r="D131" s="59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464338496/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="57" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B132" s="58" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>Sr Production Supervisor (Front End Night Shift)</t>
+        </is>
+      </c>
+      <c r="D132" s="59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455302580/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="57" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B133" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>Engineering Technician 3 (Front End Day Shift)</t>
+        </is>
+      </c>
+      <c r="D133" s="59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463698028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="57" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B134" s="58" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>Territory Business Manager</t>
+        </is>
+      </c>
+      <c r="D134" s="59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464350389/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="57" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B135" s="58" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>Manager Systems Design Engineering</t>
+        </is>
+      </c>
+      <c r="D135" s="59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464683405/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="57" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B136" s="58" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>Senior Staff Process Development Engineer</t>
+        </is>
+      </c>
+      <c r="D136" s="59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464945232/</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="57" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B137" s="58" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>Manager, SW System &amp; Solution Dev Engineer</t>
+        </is>
+      </c>
+      <c r="D137" s="59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464452799/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="57" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B138" s="58" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>Supervisor Manufacturing</t>
+        </is>
+      </c>
+      <c r="D138" s="59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4428861138/</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="57" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B139" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>Sr IT Project Manager</t>
+        </is>
+      </c>
+      <c r="D139" s="59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436188818/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="57" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B140" s="58" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>Staff Database Administrator</t>
+        </is>
+      </c>
+      <c r="D140" s="59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456322200/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="57" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B141" s="58" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>Payroll Analyst (ANZ)</t>
+        </is>
+      </c>
+      <c r="D141" s="59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456178209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="57" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B142" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>Senior Staff Mechanical Engineer - Characterization Lead</t>
+        </is>
+      </c>
+      <c r="D142" s="59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4427645063/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="57" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B143" s="58" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>Sr Enterprise Developer (Power Platform Developer)</t>
+        </is>
+      </c>
+      <c r="D143" s="59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455767052/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="57" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B144" s="58" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>Software QA Engineer 2</t>
+        </is>
+      </c>
+      <c r="D144" s="59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464606837/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D126"/>
+  <autoFilter ref="A1:D144"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -3276,6 +3645,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId143"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dexcom_Job_Tracker.xlsx
+++ b/Dexcom_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dexcom Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dexcom Job Tracker'!$A$1:$D$157</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +95,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -626,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D144"/>
+  <dimension ref="A1:D157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -658,12 +667,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="57" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B2" s="55" t="n">
+      <c r="B2" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -671,19 +680,19 @@
           <t>Associate Facilities Engineer (Building Maintenance)</t>
         </is>
       </c>
-      <c r="D2" s="56" t="inlineStr">
+      <c r="D2" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459144568/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="54" t="inlineStr">
+      <c r="A3" s="57" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B3" s="55" t="n">
+      <c r="B3" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -691,19 +700,19 @@
           <t>Executive Assistant - Madrid</t>
         </is>
       </c>
-      <c r="D3" s="56" t="inlineStr">
+      <c r="D3" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448303180/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="54" t="inlineStr">
+      <c r="A4" s="57" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B4" s="55" t="n">
+      <c r="B4" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -711,19 +720,19 @@
           <t>Benefits Analyst</t>
         </is>
       </c>
-      <c r="D4" s="56" t="inlineStr">
+      <c r="D4" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461581171/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="54" t="inlineStr">
+      <c r="A5" s="57" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B5" s="55" t="n">
+      <c r="B5" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -731,19 +740,19 @@
           <t>Senior Manager Corporate Compliance - EMEA</t>
         </is>
       </c>
-      <c r="D5" s="56" t="inlineStr">
+      <c r="D5" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429707112/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="54" t="inlineStr">
+      <c r="A6" s="57" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B6" s="55" t="n">
+      <c r="B6" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -751,19 +760,19 @@
           <t>Customer Service Representative (German-speaking)</t>
         </is>
       </c>
-      <c r="D6" s="56" t="inlineStr">
+      <c r="D6" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463120173/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="54" t="inlineStr">
+      <c r="A7" s="57" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B7" s="55" t="n">
+      <c r="B7" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -771,19 +780,19 @@
           <t>Sr Enterprise Privacy Analyst</t>
         </is>
       </c>
-      <c r="D7" s="56" t="inlineStr">
+      <c r="D7" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387414194/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="54" t="inlineStr">
+      <c r="A8" s="57" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B8" s="55" t="n">
+      <c r="B8" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -791,19 +800,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D8" s="56" t="inlineStr">
+      <c r="D8" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765131/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="54" t="inlineStr">
+      <c r="A9" s="57" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B9" s="55" t="n">
+      <c r="B9" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -811,19 +820,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D9" s="56" t="inlineStr">
+      <c r="D9" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459303523/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="54" t="inlineStr">
+      <c r="A10" s="57" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B10" s="55" t="n">
+      <c r="B10" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -831,19 +840,19 @@
           <t>Associate Facilities Engineer</t>
         </is>
       </c>
-      <c r="D10" s="56" t="inlineStr">
+      <c r="D10" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448830718/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="54" t="inlineStr">
+      <c r="A11" s="57" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B11" s="55" t="n">
+      <c r="B11" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -851,19 +860,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D11" s="56" t="inlineStr">
+      <c r="D11" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4454019825/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="54" t="inlineStr">
+      <c r="A12" s="57" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B12" s="55" t="n">
+      <c r="B12" s="58" t="n">
         <v>46276</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -871,19 +880,19 @@
           <t>Sr Manager Human Resources</t>
         </is>
       </c>
-      <c r="D12" s="56" t="inlineStr">
+      <c r="D12" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466052473/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="54" t="inlineStr">
+      <c r="A13" s="57" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B13" s="55" t="n">
+      <c r="B13" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -891,19 +900,19 @@
           <t>Sr. Manager - Capability Leader, Sentiment Intelligence</t>
         </is>
       </c>
-      <c r="D13" s="56" t="inlineStr">
+      <c r="D13" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459302533/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="54" t="inlineStr">
+      <c r="A14" s="57" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B14" s="55" t="n">
+      <c r="B14" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -911,19 +920,19 @@
           <t>Sr Cost Accountant</t>
         </is>
       </c>
-      <c r="D14" s="56" t="inlineStr">
+      <c r="D14" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4410011461/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="54" t="inlineStr">
+      <c r="A15" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B15" s="55" t="n">
+      <c r="B15" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -931,19 +940,19 @@
           <t>Sr Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="D15" s="56" t="inlineStr">
+      <c r="D15" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448601784/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="54" t="inlineStr">
+      <c r="A16" s="57" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B16" s="55" t="n">
+      <c r="B16" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -951,19 +960,19 @@
           <t>Software Development Engineer 2</t>
         </is>
       </c>
-      <c r="D16" s="56" t="inlineStr">
+      <c r="D16" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453360435/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="54" t="inlineStr">
+      <c r="A17" s="57" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B17" s="55" t="n">
+      <c r="B17" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -971,19 +980,19 @@
           <t>Sr Facilities Engineer</t>
         </is>
       </c>
-      <c r="D17" s="56" t="inlineStr">
+      <c r="D17" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446562908/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="54" t="inlineStr">
+      <c r="A18" s="57" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B18" s="55" t="n">
+      <c r="B18" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -991,19 +1000,19 @@
           <t>Sr Cybersecurity Analyst - GRC</t>
         </is>
       </c>
-      <c r="D18" s="56" t="inlineStr">
+      <c r="D18" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453096131/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="54" t="inlineStr">
+      <c r="A19" s="57" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B19" s="55" t="n">
+      <c r="B19" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1011,19 +1020,19 @@
           <t>Accountant - Healthcare - Edinburgh</t>
         </is>
       </c>
-      <c r="D19" s="56" t="inlineStr">
+      <c r="D19" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453144035/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="54" t="inlineStr">
+      <c r="A20" s="57" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="B20" s="55" t="n">
+      <c r="B20" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1031,19 +1040,19 @@
           <t>Manager Finance</t>
         </is>
       </c>
-      <c r="D20" s="56" t="inlineStr">
+      <c r="D20" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462145294/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="54" t="inlineStr">
+      <c r="A21" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B21" s="55" t="n">
+      <c r="B21" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1051,19 +1060,19 @@
           <t>Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="D21" s="56" t="inlineStr">
+      <c r="D21" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448398864/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="54" t="inlineStr">
+      <c r="A22" s="57" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B22" s="55" t="n">
+      <c r="B22" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1071,19 +1080,19 @@
           <t>Senior Manager Corporate Compliance - EMEA (m/w/d)</t>
         </is>
       </c>
-      <c r="D22" s="56" t="inlineStr">
+      <c r="D22" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461752409/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="54" t="inlineStr">
+      <c r="A23" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B23" s="55" t="n">
+      <c r="B23" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1091,19 +1100,19 @@
           <t>Director, QA - Product Development Processes</t>
         </is>
       </c>
-      <c r="D23" s="56" t="inlineStr">
+      <c r="D23" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456434433/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="54" t="inlineStr">
+      <c r="A24" s="57" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B24" s="55" t="n">
+      <c r="B24" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1111,19 +1120,19 @@
           <t>Security and Privacy Compliance Analyst - Cybersecurity</t>
         </is>
       </c>
-      <c r="D24" s="56" t="inlineStr">
+      <c r="D24" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4257269392/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="54" t="inlineStr">
+      <c r="A25" s="57" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B25" s="55" t="n">
+      <c r="B25" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1131,19 +1140,19 @@
           <t>Advanced Support Specialist 1</t>
         </is>
       </c>
-      <c r="D25" s="56" t="inlineStr">
+      <c r="D25" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458769459/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="54" t="inlineStr">
+      <c r="A26" s="57" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B26" s="55" t="n">
+      <c r="B26" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1151,19 +1160,19 @@
           <t>Sr Quality Assurance Analyst</t>
         </is>
       </c>
-      <c r="D26" s="56" t="inlineStr">
+      <c r="D26" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451545592/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="54" t="inlineStr">
+      <c r="A27" s="57" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B27" s="55" t="n">
+      <c r="B27" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1171,19 +1180,19 @@
           <t>Sr. Manager-Vendor Management (Electronics)</t>
         </is>
       </c>
-      <c r="D27" s="56" t="inlineStr">
+      <c r="D27" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446726237/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="54" t="inlineStr">
+      <c r="A28" s="57" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B28" s="55" t="n">
+      <c r="B28" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1191,19 +1200,19 @@
           <t>Customer Success Associate</t>
         </is>
       </c>
-      <c r="D28" s="56" t="inlineStr">
+      <c r="D28" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447526678/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="54" t="inlineStr">
+      <c r="A29" s="57" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B29" s="55" t="n">
+      <c r="B29" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1211,19 +1220,19 @@
           <t>Supply Chain Analyst</t>
         </is>
       </c>
-      <c r="D29" s="56" t="inlineStr">
+      <c r="D29" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433857606/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="54" t="inlineStr">
+      <c r="A30" s="57" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B30" s="55" t="n">
+      <c r="B30" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1231,19 +1240,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D30" s="56" t="inlineStr">
+      <c r="D30" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097086/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="54" t="inlineStr">
+      <c r="A31" s="57" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B31" s="55" t="n">
+      <c r="B31" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1251,19 +1260,19 @@
           <t>Sr Quality Engineer, Supplier Quality Engineering</t>
         </is>
       </c>
-      <c r="D31" s="56" t="inlineStr">
+      <c r="D31" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4384568916/</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="54" t="inlineStr">
+      <c r="A32" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B32" s="55" t="n">
+      <c r="B32" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1271,19 +1280,19 @@
           <t>Sr QA Engineer</t>
         </is>
       </c>
-      <c r="D32" s="56" t="inlineStr">
+      <c r="D32" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465859501/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="54" t="inlineStr">
+      <c r="A33" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B33" s="55" t="n">
+      <c r="B33" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1291,19 +1300,19 @@
           <t>Staff Data Engineer</t>
         </is>
       </c>
-      <c r="D33" s="56" t="inlineStr">
+      <c r="D33" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446368700/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="54" t="inlineStr">
+      <c r="A34" s="57" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B34" s="55" t="n">
+      <c r="B34" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1311,19 +1320,19 @@
           <t>Senior Sustainability Specialist – Healthcare – Vilnius, Lithuania</t>
         </is>
       </c>
-      <c r="D34" s="56" t="inlineStr">
+      <c r="D34" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459828416/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="54" t="inlineStr">
+      <c r="A35" s="57" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B35" s="55" t="n">
+      <c r="B35" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1331,19 +1340,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D35" s="56" t="inlineStr">
+      <c r="D35" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453077256/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="54" t="inlineStr">
+      <c r="A36" s="57" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B36" s="55" t="n">
+      <c r="B36" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1351,19 +1360,19 @@
           <t>Manager, APAC Business Development and Partnership</t>
         </is>
       </c>
-      <c r="D36" s="56" t="inlineStr">
+      <c r="D36" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453093132/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="54" t="inlineStr">
+      <c r="A37" s="57" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B37" s="55" t="n">
+      <c r="B37" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1371,19 +1380,19 @@
           <t>Sr Systems Engineer</t>
         </is>
       </c>
-      <c r="D37" s="56" t="inlineStr">
+      <c r="D37" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4371263716/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="54" t="inlineStr">
+      <c r="A38" s="57" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B38" s="55" t="n">
+      <c r="B38" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1391,19 +1400,19 @@
           <t>Customer Service Representative - French Speaker</t>
         </is>
       </c>
-      <c r="D38" s="56" t="inlineStr">
+      <c r="D38" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4460500502/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="54" t="inlineStr">
+      <c r="A39" s="57" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B39" s="55" t="n">
+      <c r="B39" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1411,19 +1420,19 @@
           <t>Program Manager - AI Initiatives</t>
         </is>
       </c>
-      <c r="D39" s="56" t="inlineStr">
+      <c r="D39" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435119512/</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="54" t="inlineStr">
+      <c r="A40" s="57" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="B40" s="55" t="n">
+      <c r="B40" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1431,19 +1440,19 @@
           <t>Sr Sales Trainer Diabetes MEA</t>
         </is>
       </c>
-      <c r="D40" s="56" t="inlineStr">
+      <c r="D40" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4449635545/</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="54" t="inlineStr">
+      <c r="A41" s="57" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="B41" s="55" t="n">
+      <c r="B41" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1451,19 +1460,19 @@
           <t>Territory Sales Manager (m/w/d) - Zentralschweiz : Luzern, Obwalden, Nidwalden, Uri, Chur</t>
         </is>
       </c>
-      <c r="D41" s="56" t="inlineStr">
+      <c r="D41" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453133160/</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="54" t="inlineStr">
+      <c r="A42" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B42" s="55" t="n">
+      <c r="B42" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1471,19 +1480,19 @@
           <t>Speaker Bureau and KOL Operations Manager</t>
         </is>
       </c>
-      <c r="D42" s="56" t="inlineStr">
+      <c r="D42" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4423312162/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="54" t="inlineStr">
+      <c r="A43" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B43" s="55" t="n">
+      <c r="B43" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1491,19 +1500,19 @@
           <t>Process Development Engineer 2</t>
         </is>
       </c>
-      <c r="D43" s="56" t="inlineStr">
+      <c r="D43" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437873233/</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="54" t="inlineStr">
+      <c r="A44" s="57" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B44" s="55" t="n">
+      <c r="B44" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1511,19 +1520,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
         </is>
       </c>
-      <c r="D44" s="56" t="inlineStr">
+      <c r="D44" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459811610/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="54" t="inlineStr">
+      <c r="A45" s="57" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B45" s="55" t="n">
+      <c r="B45" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1531,19 +1540,19 @@
           <t>Technical Support Representative 1</t>
         </is>
       </c>
-      <c r="D45" s="56" t="inlineStr">
+      <c r="D45" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403461287/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="54" t="inlineStr">
+      <c r="A46" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B46" s="55" t="n">
+      <c r="B46" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1551,19 +1560,19 @@
           <t>Sr Manager Regulatory Affairs- LATAM</t>
         </is>
       </c>
-      <c r="D46" s="56" t="inlineStr">
+      <c r="D46" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448606739/</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="54" t="inlineStr">
+      <c r="A47" s="57" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B47" s="55" t="n">
+      <c r="B47" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1571,19 +1580,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D47" s="56" t="inlineStr">
+      <c r="D47" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453075275/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="54" t="inlineStr">
+      <c r="A48" s="57" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B48" s="55" t="n">
+      <c r="B48" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1591,19 +1600,19 @@
           <t>Customer Account Support Specialist 2</t>
         </is>
       </c>
-      <c r="D48" s="56" t="inlineStr">
+      <c r="D48" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450027435/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="54" t="inlineStr">
+      <c r="A49" s="57" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B49" s="55" t="n">
+      <c r="B49" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1611,19 +1620,19 @@
           <t>Procurement Ops Manager (IC)</t>
         </is>
       </c>
-      <c r="D49" s="56" t="inlineStr">
+      <c r="D49" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453097103/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="54" t="inlineStr">
+      <c r="A50" s="57" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B50" s="55" t="n">
+      <c r="B50" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1631,19 +1640,19 @@
           <t>Senior Software Development Engineer</t>
         </is>
       </c>
-      <c r="D50" s="56" t="inlineStr">
+      <c r="D50" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453371096/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="54" t="inlineStr">
+      <c r="A51" s="57" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B51" s="55" t="n">
+      <c r="B51" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1651,19 +1660,19 @@
           <t>Technical Support Representative 1</t>
         </is>
       </c>
-      <c r="D51" s="56" t="inlineStr">
+      <c r="D51" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403153694/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="54" t="inlineStr">
+      <c r="A52" s="57" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B52" s="55" t="n">
+      <c r="B52" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -1671,19 +1680,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D52" s="56" t="inlineStr">
+      <c r="D52" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453092177/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="54" t="inlineStr">
+      <c r="A53" s="57" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B53" s="55" t="n">
+      <c r="B53" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1691,19 +1700,19 @@
           <t>Graphic Designer 2</t>
         </is>
       </c>
-      <c r="D53" s="56" t="inlineStr">
+      <c r="D53" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456722826/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="54" t="inlineStr">
+      <c r="A54" s="57" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B54" s="55" t="n">
+      <c r="B54" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1711,19 +1720,19 @@
           <t>Purchasing Manager</t>
         </is>
       </c>
-      <c r="D54" s="56" t="inlineStr">
+      <c r="D54" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458283492/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="54" t="inlineStr">
+      <c r="A55" s="57" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B55" s="55" t="n">
+      <c r="B55" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1731,19 +1740,19 @@
           <t>Manufacturing Associate 2</t>
         </is>
       </c>
-      <c r="D55" s="56" t="inlineStr">
+      <c r="D55" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456472809/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="54" t="inlineStr">
+      <c r="A56" s="57" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B56" s="55" t="n">
+      <c r="B56" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1751,19 +1760,19 @@
           <t>Engineering Technician 2</t>
         </is>
       </c>
-      <c r="D56" s="56" t="inlineStr">
+      <c r="D56" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465624957/</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="54" t="inlineStr">
+      <c r="A57" s="57" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B57" s="55" t="n">
+      <c r="B57" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1771,19 +1780,19 @@
           <t>Engineering Technician 4</t>
         </is>
       </c>
-      <c r="D57" s="56" t="inlineStr">
+      <c r="D57" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438139166/</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="54" t="inlineStr">
+      <c r="A58" s="57" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B58" s="55" t="n">
+      <c r="B58" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1791,19 +1800,19 @@
           <t>Sr Cybersecurity Engineer</t>
         </is>
       </c>
-      <c r="D58" s="56" t="inlineStr">
+      <c r="D58" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4394381237/</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="54" t="inlineStr">
+      <c r="A59" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B59" s="55" t="n">
+      <c r="B59" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1811,19 +1820,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D59" s="56" t="inlineStr">
+      <c r="D59" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456361869/</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="54" t="inlineStr">
+      <c r="A60" s="57" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B60" s="55" t="n">
+      <c r="B60" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1831,19 +1840,19 @@
           <t>Kundenservice Medizintechnik (m/w/d) - Mainz</t>
         </is>
       </c>
-      <c r="D60" s="56" t="inlineStr">
+      <c r="D60" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462192923/</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="54" t="inlineStr">
+      <c r="A61" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B61" s="55" t="n">
+      <c r="B61" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1851,19 +1860,19 @@
           <t>Global Brand Marketing Manager (Stelo)</t>
         </is>
       </c>
-      <c r="D61" s="56" t="inlineStr">
+      <c r="D61" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435306708/</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="54" t="inlineStr">
+      <c r="A62" s="57" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B62" s="55" t="n">
+      <c r="B62" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1871,19 +1880,19 @@
           <t>Business Development Lead - India (Multiple Locations)</t>
         </is>
       </c>
-      <c r="D62" s="56" t="inlineStr">
+      <c r="D62" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456463987/</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="54" t="inlineStr">
+      <c r="A63" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B63" s="55" t="n">
+      <c r="B63" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1891,19 +1900,19 @@
           <t>Sr Manager Medical Affairs</t>
         </is>
       </c>
-      <c r="D63" s="56" t="inlineStr">
+      <c r="D63" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461536483/</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="54" t="inlineStr">
+      <c r="A64" s="57" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B64" s="55" t="n">
+      <c r="B64" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1911,19 +1920,19 @@
           <t>Manufacturing Technician 3 (Weekend Day Shift)</t>
         </is>
       </c>
-      <c r="D64" s="56" t="inlineStr">
+      <c r="D64" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456731799/</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="54" t="inlineStr">
+      <c r="A65" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B65" s="55" t="n">
+      <c r="B65" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1931,19 +1940,19 @@
           <t>Staff Membrane Formulation Scientist</t>
         </is>
       </c>
-      <c r="D65" s="56" t="inlineStr">
+      <c r="D65" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438128497/</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="54" t="inlineStr">
+      <c r="A66" s="57" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B66" s="55" t="n">
+      <c r="B66" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1951,19 +1960,19 @@
           <t>Talent Acquisition Advisor (Maternity cover)</t>
         </is>
       </c>
-      <c r="D66" s="56" t="inlineStr">
+      <c r="D66" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459039247/</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="54" t="inlineStr">
+      <c r="A67" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B67" s="55" t="n">
+      <c r="B67" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1971,19 +1980,19 @@
           <t>Hardware Engineer 2</t>
         </is>
       </c>
-      <c r="D67" s="56" t="inlineStr">
+      <c r="D67" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457567279/</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="54" t="inlineStr">
+      <c r="A68" s="57" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B68" s="55" t="n">
+      <c r="B68" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1991,19 +2000,19 @@
           <t>Senior Warehouse Operative - Weekend Days</t>
         </is>
       </c>
-      <c r="D68" s="56" t="inlineStr">
+      <c r="D68" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461098658/</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="54" t="inlineStr">
+      <c r="A69" s="57" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B69" s="55" t="n">
+      <c r="B69" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -2011,19 +2020,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D69" s="56" t="inlineStr">
+      <c r="D69" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453087192/</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="54" t="inlineStr">
+      <c r="A70" s="57" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="B70" s="55" t="n">
+      <c r="B70" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -2031,19 +2040,19 @@
           <t>Sr Market Access Manager</t>
         </is>
       </c>
-      <c r="D70" s="56" t="inlineStr">
+      <c r="D70" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465675855/</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="54" t="inlineStr">
+      <c r="A71" s="57" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B71" s="55" t="n">
+      <c r="B71" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -2051,19 +2060,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Barcelona, Spain</t>
         </is>
       </c>
-      <c r="D71" s="56" t="inlineStr">
+      <c r="D71" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459816548/</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="54" t="inlineStr">
+      <c r="A72" s="57" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B72" s="55" t="n">
+      <c r="B72" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -2071,19 +2080,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D72" s="56" t="inlineStr">
+      <c r="D72" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464354416/</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="54" t="inlineStr">
+      <c r="A73" s="57" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B73" s="55" t="n">
+      <c r="B73" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2091,19 +2100,19 @@
           <t>Customer Advocacy Generalist</t>
         </is>
       </c>
-      <c r="D73" s="56" t="inlineStr">
+      <c r="D73" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464339507/</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="54" t="inlineStr">
+      <c r="A74" s="57" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B74" s="55" t="n">
+      <c r="B74" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -2111,19 +2120,19 @@
           <t>Senior QA Manager (Quality Systems)</t>
         </is>
       </c>
-      <c r="D74" s="56" t="inlineStr">
+      <c r="D74" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4457509031/</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="54" t="inlineStr">
+      <c r="A75" s="57" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B75" s="55" t="n">
+      <c r="B75" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -2131,19 +2140,19 @@
           <t>Customer Service Representative (Italian-speaking)</t>
         </is>
       </c>
-      <c r="D75" s="56" t="inlineStr">
+      <c r="D75" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446389046/</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="54" t="inlineStr">
+      <c r="A76" s="57" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B76" s="55" t="n">
+      <c r="B76" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -2151,19 +2160,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D76" s="56" t="inlineStr">
+      <c r="D76" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463637144/</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="54" t="inlineStr">
+      <c r="A77" s="57" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B77" s="55" t="n">
+      <c r="B77" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -2171,19 +2180,19 @@
           <t>Sales/Inside Sales Trainer - Healthcare (m/w/d)</t>
         </is>
       </c>
-      <c r="D77" s="56" t="inlineStr">
+      <c r="D77" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461765129/</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="54" t="inlineStr">
+      <c r="A78" s="57" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B78" s="55" t="n">
+      <c r="B78" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -2191,19 +2200,19 @@
           <t>Quality Technician 2 Back End Days</t>
         </is>
       </c>
-      <c r="D78" s="56" t="inlineStr">
+      <c r="D78" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464613132/</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="54" t="inlineStr">
+      <c r="A79" s="57" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B79" s="55" t="n">
+      <c r="B79" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -2211,19 +2220,19 @@
           <t>Mitarbeiter:innen für den deutschsprachigen Produkt- und Kundendienst (m/w/d)</t>
         </is>
       </c>
-      <c r="D79" s="56" t="inlineStr">
+      <c r="D79" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446570417/</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="54" t="inlineStr">
+      <c r="A80" s="57" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B80" s="55" t="n">
+      <c r="B80" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -2231,19 +2240,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D80" s="56" t="inlineStr">
+      <c r="D80" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463633190/</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="54" t="inlineStr">
+      <c r="A81" s="57" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="B81" s="55" t="n">
+      <c r="B81" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2251,19 +2260,19 @@
           <t>Sr Technical Program Manager FHIR APIs- 18 months fixed term</t>
         </is>
       </c>
-      <c r="D81" s="56" t="inlineStr">
+      <c r="D81" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450696746/</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="54" t="inlineStr">
+      <c r="A82" s="57" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B82" s="55" t="n">
+      <c r="B82" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -2271,19 +2280,19 @@
           <t>Logistics Analyst</t>
         </is>
       </c>
-      <c r="D82" s="56" t="inlineStr">
+      <c r="D82" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461266744/</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="54" t="inlineStr">
+      <c r="A83" s="57" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B83" s="55" t="n">
+      <c r="B83" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2291,19 +2300,19 @@
           <t>Senior Forecasting Analyst</t>
         </is>
       </c>
-      <c r="D83" s="56" t="inlineStr">
+      <c r="D83" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463628391/</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="54" t="inlineStr">
+      <c r="A84" s="57" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B84" s="55" t="n">
+      <c r="B84" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -2311,19 +2320,19 @@
           <t>Sr Business Process Analyst (m/w/d) - Healthcare</t>
         </is>
       </c>
-      <c r="D84" s="56" t="inlineStr">
+      <c r="D84" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4459309508/</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="54" t="inlineStr">
+      <c r="A85" s="57" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B85" s="55" t="n">
+      <c r="B85" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2331,19 +2340,19 @@
           <t>Trade Marketing Manager - Pharmacy (m/w/d)</t>
         </is>
       </c>
-      <c r="D85" s="56" t="inlineStr">
+      <c r="D85" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461770007/</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="54" t="inlineStr">
+      <c r="A86" s="57" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B86" s="55" t="n">
+      <c r="B86" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -2351,19 +2360,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D86" s="56" t="inlineStr">
+      <c r="D86" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453076276/</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="54" t="inlineStr">
+      <c r="A87" s="57" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B87" s="55" t="n">
+      <c r="B87" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -2371,19 +2380,19 @@
           <t>Marketing Manager Education Consumer Products EMEA – Healthcare – Bracknell, UK</t>
         </is>
       </c>
-      <c r="D87" s="56" t="inlineStr">
+      <c r="D87" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462849233/</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="54" t="inlineStr">
+      <c r="A88" s="57" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B88" s="55" t="n">
+      <c r="B88" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -2391,19 +2400,19 @@
           <t>Sr Manager Regulatory Affairs</t>
         </is>
       </c>
-      <c r="D88" s="56" t="inlineStr">
+      <c r="D88" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456106944/</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="54" t="inlineStr">
+      <c r="A89" s="57" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B89" s="55" t="n">
+      <c r="B89" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -2411,19 +2420,19 @@
           <t>QA Engineer Digital Systems</t>
         </is>
       </c>
-      <c r="D89" s="56" t="inlineStr">
+      <c r="D89" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444460213/</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="54" t="inlineStr">
+      <c r="A90" s="57" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B90" s="55" t="n">
+      <c r="B90" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -2431,19 +2440,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D90" s="56" t="inlineStr">
+      <c r="D90" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453078274/</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="54" t="inlineStr">
+      <c r="A91" s="57" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B91" s="55" t="n">
+      <c r="B91" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -2451,19 +2460,19 @@
           <t>Contract Administration Representative (French-speaking)</t>
         </is>
       </c>
-      <c r="D91" s="56" t="inlineStr">
+      <c r="D91" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4461090763/</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="54" t="inlineStr">
+      <c r="A92" s="57" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B92" s="55" t="n">
+      <c r="B92" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -2471,19 +2480,19 @@
           <t>GBS Engagement &amp; Service Management Lead</t>
         </is>
       </c>
-      <c r="D92" s="56" t="inlineStr">
+      <c r="D92" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427554137/</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="54" t="inlineStr">
+      <c r="A93" s="57" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B93" s="55" t="n">
+      <c r="B93" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -2491,19 +2500,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D93" s="56" t="inlineStr">
+      <c r="D93" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463622979/</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="54" t="inlineStr">
+      <c r="A94" s="57" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B94" s="55" t="n">
+      <c r="B94" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -2511,19 +2520,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D94" s="56" t="inlineStr">
+      <c r="D94" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453089165/</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="54" t="inlineStr">
+      <c r="A95" s="57" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B95" s="55" t="n">
+      <c r="B95" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -2531,19 +2540,19 @@
           <t>Senior Forecasting Analyst – Healthcare - UK</t>
         </is>
       </c>
-      <c r="D95" s="56" t="inlineStr">
+      <c r="D95" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4463634192/</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="54" t="inlineStr">
+      <c r="A96" s="57" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B96" s="55" t="n">
+      <c r="B96" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -2551,19 +2560,19 @@
           <t>Junior Territory Sales Manager - Healthcare - Hertfordshire &amp; Essex</t>
         </is>
       </c>
-      <c r="D96" s="56" t="inlineStr">
+      <c r="D96" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453083196/</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="54" t="inlineStr">
+      <c r="A97" s="57" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B97" s="55" t="n">
+      <c r="B97" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -2571,19 +2580,19 @@
           <t>Customer Service Representative, French Speaker</t>
         </is>
       </c>
-      <c r="D97" s="56" t="inlineStr">
+      <c r="D97" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462772822/</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="54" t="inlineStr">
+      <c r="A98" s="57" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B98" s="55" t="n">
+      <c r="B98" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -2591,19 +2600,19 @@
           <t>Associate Territory Sales Manager - Healthcare - Leicestershire &amp; Lincolnshire</t>
         </is>
       </c>
-      <c r="D98" s="56" t="inlineStr">
+      <c r="D98" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082209/</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="54" t="inlineStr">
+      <c r="A99" s="57" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="B99" s="55" t="n">
+      <c r="B99" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -2611,19 +2620,19 @@
           <t>Technical Support Representative 2</t>
         </is>
       </c>
-      <c r="D99" s="56" t="inlineStr">
+      <c r="D99" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438880089/</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="54" t="inlineStr">
+      <c r="A100" s="57" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B100" s="55" t="n">
+      <c r="B100" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -2631,19 +2640,19 @@
           <t>Spanish Bilingual Customer Account Support Specialist 2</t>
         </is>
       </c>
-      <c r="D100" s="56" t="inlineStr">
+      <c r="D100" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4458704406/</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="54" t="inlineStr">
+      <c r="A101" s="57" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B101" s="55" t="n">
+      <c r="B101" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -2651,19 +2660,19 @@
           <t>Spanish Bilingual TSR</t>
         </is>
       </c>
-      <c r="D101" s="56" t="inlineStr">
+      <c r="D101" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4407814543/</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="54" t="inlineStr">
+      <c r="A102" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B102" s="55" t="n">
+      <c r="B102" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -2671,19 +2680,19 @@
           <t>Senior Medical Affairs Manager – Value, Evidence, and Outcomes</t>
         </is>
       </c>
-      <c r="D102" s="56" t="inlineStr">
+      <c r="D102" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443448275/</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="54" t="inlineStr">
+      <c r="A103" s="57" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B103" s="55" t="n">
+      <c r="B103" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -2691,19 +2700,19 @@
           <t>Sr Technical Writer</t>
         </is>
       </c>
-      <c r="D103" s="56" t="inlineStr">
+      <c r="D103" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4465024024/</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="54" t="inlineStr">
+      <c r="A104" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B104" s="55" t="n">
+      <c r="B104" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -2711,19 +2720,19 @@
           <t>Production Chemist 3</t>
         </is>
       </c>
-      <c r="D104" s="56" t="inlineStr">
+      <c r="D104" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464932915/</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="54" t="inlineStr">
+      <c r="A105" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B105" s="55" t="n">
+      <c r="B105" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -2731,19 +2740,19 @@
           <t>Lead Corporate Development Manager</t>
         </is>
       </c>
-      <c r="D105" s="56" t="inlineStr">
+      <c r="D105" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462460922/</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="54" t="inlineStr">
+      <c r="A106" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B106" s="55" t="n">
+      <c r="B106" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -2751,19 +2760,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D106" s="56" t="inlineStr">
+      <c r="D106" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439353245/</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="54" t="inlineStr">
+      <c r="A107" s="57" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B107" s="55" t="n">
+      <c r="B107" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -2771,19 +2780,19 @@
           <t>HR Business Partner</t>
         </is>
       </c>
-      <c r="D107" s="56" t="inlineStr">
+      <c r="D107" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456322164/</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="54" t="inlineStr">
+      <c r="A108" s="57" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B108" s="55" t="n">
+      <c r="B108" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -2791,19 +2800,19 @@
           <t>Procurement Ops Manager (IC)</t>
         </is>
       </c>
-      <c r="D108" s="56" t="inlineStr">
+      <c r="D108" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4453082223/</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="54" t="inlineStr">
+      <c r="A109" s="57" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B109" s="55" t="n">
+      <c r="B109" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -2811,19 +2820,19 @@
           <t>Business Process Analyst</t>
         </is>
       </c>
-      <c r="D109" s="56" t="inlineStr">
+      <c r="D109" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4414569192/</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="54" t="inlineStr">
+      <c r="A110" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B110" s="55" t="n">
+      <c r="B110" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -2831,19 +2840,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D110" s="56" t="inlineStr">
+      <c r="D110" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456380639/</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="54" t="inlineStr">
+      <c r="A111" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B111" s="55" t="n">
+      <c r="B111" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -2851,19 +2860,19 @@
           <t>Sr. Director, Consumer Software Applications</t>
         </is>
       </c>
-      <c r="D111" s="56" t="inlineStr">
+      <c r="D111" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4456364824/</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="54" t="inlineStr">
+      <c r="A112" s="57" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="B112" s="55" t="n">
+      <c r="B112" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -2871,19 +2880,19 @@
           <t>Associate Marketing Manager</t>
         </is>
       </c>
-      <c r="D112" s="56" t="inlineStr">
+      <c r="D112" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451399530/</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="54" t="inlineStr">
+      <c r="A113" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B113" s="55" t="n">
+      <c r="B113" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -2891,19 +2900,19 @@
           <t>Material Handler 1 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D113" s="56" t="inlineStr">
+      <c r="D113" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455128356/</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="54" t="inlineStr">
+      <c r="A114" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B114" s="55" t="n">
+      <c r="B114" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -2911,19 +2920,19 @@
           <t>Material Handler 4 ( 2B Thur-Sat, every other Wednesday, Can work anytime from 5pm-5am )</t>
         </is>
       </c>
-      <c r="D114" s="56" t="inlineStr">
+      <c r="D114" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464432288/</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="54" t="inlineStr">
+      <c r="A115" s="57" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B115" s="55" t="n">
+      <c r="B115" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -2931,19 +2940,19 @@
           <t>Senior Sterilization Engineer</t>
         </is>
       </c>
-      <c r="D115" s="56" t="inlineStr">
+      <c r="D115" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4410980549/</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="54" t="inlineStr">
+      <c r="A116" s="57" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B116" s="55" t="n">
+      <c r="B116" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -2951,19 +2960,19 @@
           <t>Accounts Payable Process Expert (Maternity Cover)</t>
         </is>
       </c>
-      <c r="D116" s="56" t="inlineStr">
+      <c r="D116" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4462464542/</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="54" t="inlineStr">
+      <c r="A117" s="57" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B117" s="55" t="n">
+      <c r="B117" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -2971,19 +2980,19 @@
           <t>Staff Software Test Development Engineer</t>
         </is>
       </c>
-      <c r="D117" s="56" t="inlineStr">
+      <c r="D117" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4388377406/</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="54" t="inlineStr">
+      <c r="A118" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B118" s="55" t="n">
+      <c r="B118" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -2991,19 +3000,19 @@
           <t>Manager Quality Compliance</t>
         </is>
       </c>
-      <c r="D118" s="56" t="inlineStr">
+      <c r="D118" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464662874/</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="54" t="inlineStr">
+      <c r="A119" s="57" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B119" s="55" t="n">
+      <c r="B119" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -3011,19 +3020,19 @@
           <t>QA Engineer 2</t>
         </is>
       </c>
-      <c r="D119" s="56" t="inlineStr">
+      <c r="D119" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4464097498/</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="54" t="inlineStr">
+      <c r="A120" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B120" s="55" t="n">
+      <c r="B120" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -3031,19 +3040,19 @@
           <t>Staff QA Engineer</t>
         </is>
       </c>
-      <c r="D120" s="56" t="inlineStr">
+      <c r="D120" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436409441/</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="54" t="inlineStr">
+      <c r="A121" s="57" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B121" s="55" t="n">
+      <c r="B121" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -3051,19 +3060,19 @@
           <t>Staff Equipment Engineer</t>
         </is>
       </c>
-      <c r="D121" s="56" t="inlineStr">
+      <c r="D121" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455253909/</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="54" t="inlineStr">
+      <c r="A122" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B122" s="55" t="n">
+      <c r="B122" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -3071,19 +3080,19 @@
           <t>Sr. Staff Technical Program Manager - Stelo</t>
         </is>
       </c>
-      <c r="D122" s="56" t="inlineStr">
+      <c r="D122" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455370480/</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="54" t="inlineStr">
+      <c r="A123" s="57" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B123" s="55" t="n">
+      <c r="B123" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -3091,19 +3100,19 @@
           <t>Staff SRE SW Development Engineer</t>
         </is>
       </c>
-      <c r="D123" s="56" t="inlineStr">
+      <c r="D123" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4387683946/</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="54" t="inlineStr">
+      <c r="A124" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B124" s="55" t="n">
+      <c r="B124" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -3111,19 +3120,19 @@
           <t>Material Handler 2 ( RDC ) - Days 1A and 1B</t>
         </is>
       </c>
-      <c r="D124" s="56" t="inlineStr">
+      <c r="D124" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455289757/</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="54" t="inlineStr">
+      <c r="A125" s="57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B125" s="55" t="n">
+      <c r="B125" s="58" t="n">
         <v>46275</v>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -3131,19 +3140,19 @@
           <t>Material Handler 2 ( RDC ) - Nights 2A and 2B</t>
         </is>
       </c>
-      <c r="D125" s="56" t="inlineStr">
+      <c r="D125" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4455289751/</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="54" t="inlineStr">
+      <c r="A126" s="57" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B126" s="55" t="n">
+      <c r="B126" s="58" t="n">
         <v>46276</v>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -3151,7 +3160,7 @@
           <t>Third Party Risk and Supplier Onboarding Manager</t>
         </is>
       </c>
-      <c r="D126" s="56" t="inlineStr">
+      <c r="D126" s="59" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4466048486/</t>
         </is>
@@ -3517,8 +3526,268 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="60" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B145" s="61" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>SW Development Engineer 1 - Android</t>
+        </is>
+      </c>
+      <c r="D145" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464353380/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="60" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B146" s="61" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>SW Test Development Engineer 1</t>
+        </is>
+      </c>
+      <c r="D146" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465029007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="60" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B147" s="61" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>SW Development Engineer 2 - Android</t>
+        </is>
+      </c>
+      <c r="D147" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464610755/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B148" s="61" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>Sr Workplace Solutions Analyst</t>
+        </is>
+      </c>
+      <c r="D148" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456322161/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="60" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B149" s="61" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>Staff SW Development Engineer</t>
+        </is>
+      </c>
+      <c r="D149" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465323573/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="60" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B150" s="61" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>Director, Business Program Management Office</t>
+        </is>
+      </c>
+      <c r="D150" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456105988/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="60" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B151" s="61" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>Desktop Support Specialist 3</t>
+        </is>
+      </c>
+      <c r="D151" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4445930979/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="60" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B152" s="61" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>Engineering Technician 4</t>
+        </is>
+      </c>
+      <c r="D152" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4456115187/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B153" s="61" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>Systems Design &amp; Test Engineer 2</t>
+        </is>
+      </c>
+      <c r="D153" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443989564/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B154" s="61" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Staff Technical Program Manager - Sensor Technology</t>
+        </is>
+      </c>
+      <c r="D154" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439394782/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="60" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B155" s="61" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>Sr. SW Test Development Engineer V&amp;V</t>
+        </is>
+      </c>
+      <c r="D155" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4387839555/</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B156" s="61" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>QA Inspector 2 ( Dobson ) - 1A Sun- Tues, every other Wednesday, Can work anytime from 5am-5pm</t>
+        </is>
+      </c>
+      <c r="D156" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4463691655/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="60" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B157" s="61" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>Lab Technician 3 (Chemistry) Back End Days</t>
+        </is>
+      </c>
+      <c r="D157" s="62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4464341469/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D144"/>
+  <autoFilter ref="A1:D157"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -3663,6 +3932,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId156"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
